--- a/채용비율.xlsx
+++ b/채용비율.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="R41bb03fe005d4ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R209673bbce4348c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R2156c8fdc3f74c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="R4f44f782cf04441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="Ra39f5e6b27b14541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="Rdf02fbc35ae74c02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="Rdc648a3dac7a47f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="Rcb8e7fda0fd74fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R708485327fb24042"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="Rdebf075fddaa429f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="R327db8af94624522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="Rc8b70911f15b46cb"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="가평군">#REF!</x:definedName>
@@ -229,253 +229,88 @@
     <x:t xml:space="preserve">화성능동 A-1BL 공공지원 민간임대리츠</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">남부지부 소계</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">남서</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">남양우미린</x:t>
+    <x:t xml:space="preserve">3.타워(렌탈)사별 점유 현황 (통계제외 제외)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">타워사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">현장수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">한노점유율</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주식회사 비엠케이</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">벽산중기산업주식회사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)한백산업</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)규람타워렌탈</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주식회사 화성건기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)신화중공업</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주식회사 가람타워</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)야후건기</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">뉴월드타워 주식회사</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">화성비봉 지역주택조합 아파트 신축공사</x:t>
+    <x:t xml:space="preserve">(주)우리기계산업</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)진성타워</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주식회사 한불타워</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)무기타워렌탈</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)타워링</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(주)타워랜드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">신우개발(주)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">주식회사 삼진타워</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">오산세교2지구 M1블록 민간임대 주상복합 신축공사</x:t>
+    <x:t xml:space="preserve">(주)한진</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">주식회사 필웍스</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">(주)남산공영</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">오산 AMK R&amp;D</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">신우개발(주)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">오산세교우미린레이크시티</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">남서지부 소계</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">동부</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">이천한양</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">현성</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">통계제외</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">요진건설</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">홍문2지구 공동주택</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)한진</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">이천 증포5지구 칸타빌 에듀파크 신축공사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경안2지구 도시개발사업 주상복합 신축공사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">동부지부 소계</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">서부</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">안산프로젝트팀부크(현대건설)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주식회사 한불타워</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">안산글로벌클라우드(삼성물산)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">하중지구 한신공영</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)신화중공업</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">하중지구 양우건설</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)진성타워</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시흥거모지구 S-2BL,B-2BL(대방산업개발)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">배곧서울대학교병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)타워링</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시흥하중 A-1BL 공동주택 건설공사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)규람타워렌탈</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시흥시 거모지구 B-1블록 공동주택 신축공사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주식회사 필웍스</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시흥거모 B-6BL 모아엘가&amp;대광로제비앙 공동주택 신축공사</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">(주)금강건기</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">시화MTV 지하주차장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)우리기계산업</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">원청사: 강산건설(주)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">서부지부 소계</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">북서</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">군포시 SGC건설</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)한백산업</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">관양동 DL이앤씨</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">벽산중기산업주식회사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">의왕청계 시티건설</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">과천 태왕</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주식회사 비엠케이</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">과천 주암동 디에이치 아델스타(현대건설)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">안양 샘병원</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주식회사 가람타워</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">안양 박달동 신안아파트 재건축(현대산업개발)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">안양역세권지구 재개발정비사업(현대산업개발)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">관양동 오피스텔 신축공사</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">(주)유건설 (단종계약)</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">북서지부 소계</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">용인</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">양지 대우 원클러스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">양지 SM경남 아너스빌</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">역북 푸르지오 클루센트(대우건설)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">고림 대광로제비앙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">백암 오뚜기물류센타</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">마평동 여성복지회관</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)무기타워렌탈</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">용인 라온프라이빗</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">용인덕성 AI데이터센터 신축공사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)타워랜드</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">용인클러스터 상생협력시설(기숙사 1차)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">원철규(미정3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">수지자이에디시온</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기흥변전소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">한양립스</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">(주)제이에스글로벌산업</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3.타워(렌탈)사별 점유 현황 (통계제외 제외)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">타워사</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">현장수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">한노점유율</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주식회사 화성건기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">(주)야후건기</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">반도체 현장 타워크레인 설치 및 노조별 대수 현황</x:t>
@@ -626,6 +461,9 @@
     <x:t xml:space="preserve">강산건설(주)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">시화MTV 지하주차장</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">농심엔지니어링(주)</x:t>
   </x:si>
   <x:si>
@@ -758,15 +596,24 @@
     <x:t xml:space="preserve">고덕종합건설</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">기흥변전소</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">(주)한양건설</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">한양립스</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">8월 채용 현황</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">안양역센트럴아이파크수자인</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">배곧서울대학교병원</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">동원건설산업(주)</x:t>
   </x:si>
   <x:si>
@@ -818,6 +665,9 @@
     <x:t xml:space="preserve">동부건설(주)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">용인클러스터 상생협력시설(기숙사 1차)</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">미정 3대 (배정 미확정)</x:t>
   </x:si>
   <x:si>
@@ -830,6 +680,9 @@
     <x:t xml:space="preserve">(주)서희건설</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">화성비봉 지역주택조합 아파트 신축공사</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">기타(비고에 작성)</x:t>
   </x:si>
   <x:si>
@@ -839,9 +692,15 @@
     <x:t xml:space="preserve">지에스건설(주)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">수지자이에디시온</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">삼성이앤에이(주)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">오산 AMK R&amp;D</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">※ 미정 12대 아직 미반영 (인력 확정 시 비율 변동)</x:t>
   </x:si>
   <x:si>
@@ -851,13 +710,22 @@
     <x:t xml:space="preserve">(주)모아주택산업, (주)로제비앙건설</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">시흥거모 B-6BL 모아엘가&amp;대광로제비앙 공동주택 신축공사</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">주식회사 필윅스</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">(주)호반건설</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">시흥시 거모지구 B-1블록 공동주택 신축공사</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">(주)대원</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이천 증포5지구 칸타빌 에듀파크 신축공사</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -892,13 +760,22 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">오산세교2지구 M1블록 민간임대 주상복합 신축공사</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">대보건설(주)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">제일건설(주)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">오산세교우미린레이크시티</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">효성중공업(주)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경안2지구 도시개발사업 주상복합 신축공사</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1653,7 +1530,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="545">
+  <x:cellXfs count="568">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -3247,6 +3124,75 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="40" fillId="28" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="46" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="47" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="48" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="58" fillId="25" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="32" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="49" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="49" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="49" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="45" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="45" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="5" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="45" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -3474,7 +3420,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf889433dd999411e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8f220ef0ecd44016"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3723,27 +3669,27 @@
       <x:c r="A3" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B3" s="127" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C3" s="127">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D3" s="127">
+      <x:c r="B3" s="567" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C3" s="567" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D3" s="567" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E3" s="127">
+      <x:c r="E3" s="567" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="127">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G3" s="127">
+      <x:c r="F3" s="567" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G3" s="567" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H3" s="127" t="n">
+      <x:c r="H3" s="567" t="n">
         <x:f>SUM(B3:G3)</x:f>
-        <x:v>242</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="I3" s="9" t="s">
         <x:v>11</x:v>
@@ -3754,28 +3700,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="32" t="n">
-        <x:f t="shared" ref="B4:G4" si="0">B3/$H$3</x:f>
-        <x:v>0.2892561983471074</x:v>
+        <x:f t="shared" ref="B4:G4" si="0">IF($H$3=0,0,B3/$H$3)</x:f>
+        <x:v>0.2886178861788618</x:v>
       </x:c>
       <x:c r="C4" s="32" t="n">
-        <x:f t="shared" si="0">C3/$H$3</x:f>
-        <x:v>0.4132231404958678</x:v>
+        <x:f t="shared" si="0">IF($H$3=0,0,C3/$H$3)</x:f>
+        <x:v>0.4146341463414634</x:v>
       </x:c>
       <x:c r="D4" s="32" t="n">
-        <x:f t="shared" si="0">D3/$H$3</x:f>
-        <x:v>0.03305785123966942</x:v>
+        <x:f t="shared" si="0">IF($H$3=0,0,D3/$H$3)</x:f>
+        <x:v>0.032520325203252036</x:v>
       </x:c>
       <x:c r="E4" s="32" t="n">
-        <x:f t="shared" si="0">E3/$H$3</x:f>
-        <x:v>0.04132231404958678</x:v>
+        <x:f t="shared" si="0">IF($H$3=0,0,E3/$H$3)</x:f>
+        <x:v>0.04065040650406504</x:v>
       </x:c>
       <x:c r="F4" s="32" t="n">
-        <x:f t="shared" si="0">F3/$H$3</x:f>
-        <x:v>0.1652892561983471</x:v>
+        <x:f t="shared" si="0">IF($H$3=0,0,F3/$H$3)</x:f>
+        <x:v>0.16666666666666666</x:v>
       </x:c>
       <x:c r="G4" s="32" t="n">
-        <x:f t="shared" si="0">G3/$H$3</x:f>
-        <x:v>0.05785123966942149</x:v>
+        <x:f t="shared" si="0">IF($H$3=0,0,G3/$H$3)</x:f>
+        <x:v>0.056910569105691054</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="14" customFormat="1" ht="21.200000762939453" customHeight="1"/>
@@ -4146,25 +4092,25 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="43"/>
-      <x:c r="E8" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F8" s="104">
+      <x:c r="E8" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F8" s="542">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G8" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J8" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="105">
+      <x:c r="G8" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J8" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="543">
         <x:v>8</x:v>
       </x:c>
       <x:c r="L8" s="82"/>
@@ -4180,25 +4126,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="43"/>
-      <x:c r="E9" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F9" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G9" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I9" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="105">
+      <x:c r="E9" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F9" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="543">
         <x:v>6</x:v>
       </x:c>
       <x:c r="L9" s="82"/>
@@ -4214,25 +4160,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
-      <x:c r="E10" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G10" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I10" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J10" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="105">
+      <x:c r="E10" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G10" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="543">
         <x:v>5</x:v>
       </x:c>
       <x:c r="L10" s="82"/>
@@ -4248,25 +4194,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="43"/>
-      <x:c r="E11" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G11" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J11" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="105">
+      <x:c r="E11" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="543">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L11" s="82"/>
@@ -4282,25 +4228,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="43"/>
-      <x:c r="E12" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F12" s="104">
+      <x:c r="E12" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F12" s="542">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G12" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J12" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="105">
+      <x:c r="G12" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="543">
         <x:v>6</x:v>
       </x:c>
       <x:c r="L12" s="82"/>
@@ -4316,25 +4262,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
-      <x:c r="E13" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F13" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G13" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I13" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="105">
+      <x:c r="E13" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G13" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="543">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L13" s="82"/>
@@ -4350,25 +4296,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
-      <x:c r="E14" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F14" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G14" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J14" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="105">
+      <x:c r="E14" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G14" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="543">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L14" s="82"/>
@@ -4384,25 +4330,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
-      <x:c r="E15" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F15" s="104">
+      <x:c r="E15" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F15" s="542">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G15" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J15" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="105">
+      <x:c r="G15" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="543">
         <x:v>7</x:v>
       </x:c>
       <x:c r="L15" s="82"/>
@@ -4418,25 +4364,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
-      <x:c r="E16" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G16" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J16" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="105">
+      <x:c r="E16" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G16" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="543">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L16" s="82"/>
@@ -4452,25 +4398,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="43"/>
-      <x:c r="E17" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G17" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J17" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="105">
+      <x:c r="E17" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="543">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L17" s="82"/>
@@ -4486,25 +4432,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
-      <x:c r="E18" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F18" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G18" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I18" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J18" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K18" s="105">
+      <x:c r="E18" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G18" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="543">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L18" s="82"/>
@@ -4520,25 +4466,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="D19" s="43"/>
-      <x:c r="E19" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G19" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J19" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K19" s="105">
+      <x:c r="E19" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G19" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="543">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L19" s="82"/>
@@ -4554,25 +4500,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="D20" s="43"/>
-      <x:c r="E20" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F20" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G20" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I20" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K20" s="105">
+      <x:c r="E20" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="543">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L20" s="38"/>
@@ -4588,25 +4534,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D21" s="43"/>
-      <x:c r="E21" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F21" s="104">
+      <x:c r="E21" s="542">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F21" s="542">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G21" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I21" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K21" s="105">
+      <x:c r="G21" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="542">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="542">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K21" s="543">
         <x:v>6</x:v>
       </x:c>
       <x:c r="L21" s="38"/>
@@ -4622,25 +4568,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="84"/>
-      <x:c r="E22" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F22" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G22" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J22" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K22" s="98" t="n">
+      <x:c r="E22" s="545">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="545">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="545">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="545">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="545">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22" s="545">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="545" t="n">
         <x:f>SUM(E22:J22)</x:f>
         <x:v>4</x:v>
       </x:c>
@@ -4657,25 +4603,25 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="109"/>
-      <x:c r="E23" s="130">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F23" s="130">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G23" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I23" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J23" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K23" s="131" t="n">
+      <x:c r="E23" s="546">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="546">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G23" s="546">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="546">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="546">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J23" s="546">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" s="547" t="n">
         <x:f>SUM(E23:J23)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -4692,1836 +4638,1840 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D24" s="136"/>
-      <x:c r="E24" s="137">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F24" s="137">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G24" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H24" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I24" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J24" s="137">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K24" s="140" t="n">
+      <x:c r="E24" s="537">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F24" s="537">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="537">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" s="537">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="537">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="537">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K24" s="548" t="n">
         <x:f>SUM(E24:J24)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="L24" s="118"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="145" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B25" s="145"/>
-      <x:c r="C25" s="145"/>
-      <x:c r="D25" s="145"/>
+      <x:c r="A25" s="145" t="str">
+        <x:v>남부</x:v>
+      </x:c>
+      <x:c r="B25" s="145" t="str">
+        <x:v>평택고덕국제화계획지구 Abc-14BL 공동주택 신축공사</x:v>
+      </x:c>
+      <x:c r="C25" s="145" t="str">
+        <x:v>(주)제일타워공영</x:v>
+      </x:c>
+      <x:c r="D25" s="145" t="str">
+        <x:v>원청사: (주)비에스한양</x:v>
+      </x:c>
       <x:c r="E25" s="538" t="n">
-        <x:f>SUM(E8:E24)</x:f>
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="538" t="n">
-        <x:f>SUM(F8:F24)</x:f>
-        <x:v>37</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G25" s="538" t="n">
-        <x:f>SUM(G8:G24)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="538" t="n">
-        <x:f>SUM(H8:H24)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="538" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="538" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" s="539" t="n">
+        <x:f>SUM(E25:J25)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I25" s="538" t="n">
-        <x:f>SUM(I8:I24)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="J25" s="538" t="n">
-        <x:f>SUM(J8:J24)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K25" s="539" t="n">
-        <x:f>SUM(K8:K24)</x:f>
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="L25" s="119"/>
+      <x:c r="L25" s="119" t="str">
+        <x:v>현장 소재지 평택시 / 원본 조합원 소속 중부지부</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="38" t="s">
-        <x:v>26</x:v>
+      <x:c r="A26" s="38" t="str">
+        <x:v>남부지부 소계</x:v>
       </x:c>
       <x:c r="B26" s="38"/>
       <x:c r="C26" s="38"/>
       <x:c r="D26" s="38"/>
-      <x:c r="E26" s="150" t="n">
-        <x:f>IF($K$25=0,0,E25/$K$25)</x:f>
-        <x:v>0.26582278481012656</x:v>
-      </x:c>
-      <x:c r="F26" s="150" t="n">
-        <x:f>IF($K$25=0,0,F25/$K$25)</x:f>
-        <x:v>0.46835443037974683</x:v>
-      </x:c>
-      <x:c r="G26" s="150" t="n">
-        <x:f>IF($K$25=0,0,G25/$K$25)</x:f>
-        <x:v>0.02531645569620253</x:v>
-      </x:c>
-      <x:c r="H26" s="150" t="n">
-        <x:f>IF($K$25=0,0,H25/$K$25)</x:f>
-        <x:v>0.05063291139240506</x:v>
-      </x:c>
-      <x:c r="I26" s="150" t="n">
-        <x:f>IF($K$25=0,0,I25/$K$25)</x:f>
-        <x:v>0.1518987341772152</x:v>
-      </x:c>
-      <x:c r="J26" s="150" t="n">
-        <x:f>IF($K$25=0,0,J25/$K$25)</x:f>
-        <x:v>0.0379746835443038</x:v>
-      </x:c>
-      <x:c r="K26" s="150" t="n">
-        <x:f>IF($K$25=0,0,K25/$K$25)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E26" s="540" t="n">
+        <x:f>SUM(E8:E25)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F26" s="540" t="n">
+        <x:f>SUM(F8:F25)</x:f>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G26" s="540" t="n">
+        <x:f>SUM(G8:G25)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H26" s="540" t="n">
+        <x:f>SUM(H8:H25)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I26" s="540" t="n">
+        <x:f>SUM(I8:I25)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J26" s="540" t="n">
+        <x:f>SUM(J8:J25)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K26" s="540" t="n">
+        <x:f>SUM(K8:K25)</x:f>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="L26" s="38"/>
     </x:row>
     <x:row r="27" s="14" customFormat="1">
-      <x:c r="A27" s="86" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B27" s="86" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C27" s="86" t="s">
-        <x:v>63</x:v>
-      </x:c>
+      <x:c r="A27" s="86" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B27" s="86"/>
+      <x:c r="C27" s="86"/>
       <x:c r="D27" s="86"/>
-      <x:c r="E27" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F27" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G27" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J27" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K27" s="164">
+      <x:c r="E27" s="150" t="n">
+        <x:f>IF($K$26=0,0,E26/$K$26)</x:f>
+        <x:v>0.26506024096385544</x:v>
+      </x:c>
+      <x:c r="F27" s="150" t="n">
+        <x:f>IF($K$26=0,0,F26/$K$26)</x:f>
+        <x:v>0.46987951807228917</x:v>
+      </x:c>
+      <x:c r="G27" s="150" t="n">
+        <x:f>IF($K$26=0,0,G26/$K$26)</x:f>
+        <x:v>0.024096385542168676</x:v>
+      </x:c>
+      <x:c r="H27" s="150" t="n">
+        <x:f>IF($K$26=0,0,H26/$K$26)</x:f>
+        <x:v>0.04819277108433735</x:v>
+      </x:c>
+      <x:c r="I27" s="150" t="n">
+        <x:f>IF($K$26=0,0,I26/$K$26)</x:f>
+        <x:v>0.1566265060240964</x:v>
+      </x:c>
+      <x:c r="J27" s="150" t="n">
+        <x:f>IF($K$26=0,0,J26/$K$26)</x:f>
+        <x:v>0.03614457831325301</x:v>
+      </x:c>
+      <x:c r="K27" s="150" t="n">
+        <x:f>IF($K$26=0,0,K26/$K$26)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L27" s="86"/>
+    </x:row>
+    <x:row r="28" s="14" customFormat="1" ht="17.25">
+      <x:c r="A28" s="83" t="str">
+        <x:v>남서</x:v>
+      </x:c>
+      <x:c r="B28" s="84" t="str">
+        <x:v>남양우미린</x:v>
+      </x:c>
+      <x:c r="C28" s="84" t="str">
+        <x:v>뉴월드타워 주식회사</x:v>
+      </x:c>
+      <x:c r="D28" s="84"/>
+      <x:c r="E28" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F28" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="545" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L27" s="86"/>
-    </x:row>
-    <x:row r="28" s="14" customFormat="1" ht="17.25">
-      <x:c r="A28" s="83" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B28" s="84" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C28" s="84" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D28" s="84"/>
-      <x:c r="E28" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F28" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G28" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J28" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K28" s="98">
+      <x:c r="L28" s="84"/>
+    </x:row>
+    <x:row r="29" s="14" customFormat="1" ht="17.25">
+      <x:c r="A29" s="108" t="str">
+        <x:v>남서</x:v>
+      </x:c>
+      <x:c r="B29" s="109" t="str">
+        <x:v>화성비봉 지역주택조합 아파트 신축공사</x:v>
+      </x:c>
+      <x:c r="C29" s="109" t="str">
+        <x:v>주식회사 삼진타워</x:v>
+      </x:c>
+      <x:c r="D29" s="109"/>
+      <x:c r="E29" s="549" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" s="546" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="546" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="546" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="546" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J29" s="546" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K29" s="547" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L28" s="84"/>
-    </x:row>
-    <x:row r="29" s="14" customFormat="1" ht="17.25">
-      <x:c r="A29" s="108" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B29" s="109" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C29" s="109" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D29" s="109"/>
-      <x:c r="E29" s="134">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F29" s="130">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="130">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="130">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K29" s="131">
+      <x:c r="L29" s="109"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="120" t="str">
+        <x:v>남서</x:v>
+      </x:c>
+      <x:c r="B30" s="120" t="str">
+        <x:v>오산세교2지구 M1블록 민간임대 주상복합 신축공사</x:v>
+      </x:c>
+      <x:c r="C30" s="120" t="str">
+        <x:v>(주)남산공영</x:v>
+      </x:c>
+      <x:c r="D30" s="121"/>
+      <x:c r="E30" s="550" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="550" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="550" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="550" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="550" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="550" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K30" s="548" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L29" s="109"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="120" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B30" s="120" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C30" s="120" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D30" s="121"/>
-      <x:c r="E30" s="141">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F30" s="141">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30" s="141">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="141">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I30" s="141">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J30" s="141">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K30" s="140" t="n">
-        <x:f>SUM(E30:J30)</x:f>
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L30" s="120"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="151" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B31" s="151" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C31" s="151" t="s">
-        <x:v>63</x:v>
+      <x:c r="A31" s="151" t="str">
+        <x:v>남서</x:v>
+      </x:c>
+      <x:c r="B31" s="151" t="str">
+        <x:v>오산 AMK R&amp;D</x:v>
+      </x:c>
+      <x:c r="C31" s="151" t="str">
+        <x:v>신우개발(주)</x:v>
       </x:c>
       <x:c r="D31" s="151"/>
-      <x:c r="E31" s="152">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F31" s="152">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G31" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H31" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I31" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J31" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K31" s="149">
-        <x:v>8</x:v>
+      <x:c r="E31" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H31" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="539" t="n">
+        <x:f>SUM(E31:J31)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L31" s="119"/>
     </x:row>
     <x:row r="32" s="14" customFormat="1">
-      <x:c r="A32" s="153" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B32" s="153"/>
-      <x:c r="C32" s="153"/>
+      <x:c r="A32" s="153" t="str">
+        <x:v>남서</x:v>
+      </x:c>
+      <x:c r="B32" s="153" t="str">
+        <x:v>오산세교우미린레이크시티</x:v>
+      </x:c>
+      <x:c r="C32" s="153" t="str">
+        <x:v>뉴월드타워 주식회사</x:v>
+      </x:c>
       <x:c r="D32" s="153"/>
       <x:c r="E32" s="540" t="n">
-        <x:f>SUM(E27:E31)</x:f>
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F32" s="540" t="n">
-        <x:f>SUM(F27:F31)</x:f>
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G32" s="540" t="n">
-        <x:f>SUM(G27:G31)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H32" s="540" t="n">
-        <x:f>SUM(H27:H31)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="540" t="n">
-        <x:f>SUM(I27:I31)</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J32" s="540" t="n">
-        <x:f>SUM(J27:J31)</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K32" s="541" t="n">
-        <x:f>SUM(K27:K31)</x:f>
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L32" s="38"/>
     </x:row>
     <x:row r="33" s="14" customFormat="1">
-      <x:c r="A33" s="38" t="s">
-        <x:v>26</x:v>
+      <x:c r="A33" s="38" t="str">
+        <x:v>남서지부 소계</x:v>
       </x:c>
       <x:c r="B33" s="38"/>
       <x:c r="C33" s="38"/>
       <x:c r="D33" s="38"/>
-      <x:c r="E33" s="150" t="n">
-        <x:f>IF($K$32=0,0,E32/$K$32)</x:f>
+      <x:c r="E33" s="540" t="n">
+        <x:f>SUM(E28:E32)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F33" s="540" t="n">
+        <x:f>SUM(F28:F32)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G33" s="540" t="n">
+        <x:f>SUM(G28:G32)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="540" t="n">
+        <x:f>SUM(H28:H32)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="540" t="n">
+        <x:f>SUM(I28:I32)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J33" s="540" t="n">
+        <x:f>SUM(J28:J32)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K33" s="540" t="n">
+        <x:f>SUM(K28:K32)</x:f>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L33" s="38"/>
+    </x:row>
+    <x:row r="34" s="14" customFormat="1" ht="17.25">
+      <x:c r="A34" s="83" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B34" s="84"/>
+      <x:c r="C34" s="84"/>
+      <x:c r="D34" s="84"/>
+      <x:c r="E34" s="565" t="n">
+        <x:f>IF($K$33=0,0,E33/$K$33)</x:f>
         <x:v>0.2857142857142857</x:v>
       </x:c>
-      <x:c r="F33" s="150" t="n">
-        <x:f>IF($K$32=0,0,F32/$K$32)</x:f>
+      <x:c r="F34" s="565" t="n">
+        <x:f>IF($K$33=0,0,F33/$K$33)</x:f>
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="G33" s="150" t="n">
-        <x:f>IF($K$32=0,0,G32/$K$32)</x:f>
+      <x:c r="G34" s="565" t="n">
+        <x:f>IF($K$33=0,0,G33/$K$33)</x:f>
         <x:v>0.047619047619047616</x:v>
       </x:c>
-      <x:c r="H33" s="150" t="n">
-        <x:f>IF($K$32=0,0,H32/$K$32)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I33" s="150" t="n">
-        <x:f>IF($K$32=0,0,I32/$K$32)</x:f>
+      <x:c r="H34" s="565" t="n">
+        <x:f>IF($K$33=0,0,H33/$K$33)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="565" t="n">
+        <x:f>IF($K$33=0,0,I33/$K$33)</x:f>
         <x:v>0.14285714285714285</x:v>
       </x:c>
-      <x:c r="J33" s="150" t="n">
-        <x:f>IF($K$32=0,0,J32/$K$32)</x:f>
+      <x:c r="J34" s="565" t="n">
+        <x:f>IF($K$33=0,0,J33/$K$33)</x:f>
         <x:v>0.19047619047619047</x:v>
       </x:c>
-      <x:c r="K33" s="150" t="n">
-        <x:f>IF($K$32=0,0,K32/$K$32)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L33" s="38"/>
-    </x:row>
-    <x:row r="34" s="14" customFormat="1" ht="17.25">
-      <x:c r="A34" s="83" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B34" s="84" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C34" s="84" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D34" s="84" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E34" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G34" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K34" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="84" t="s">
-        <x:v>75</x:v>
-      </x:c>
+      <x:c r="K34" s="565" t="n">
+        <x:f>IF($K$33=0,0,K33/$K$33)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L34" s="84"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="108" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B35" s="110" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C35" s="110" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D35" s="110"/>
-      <x:c r="E35" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F35" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G35" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J35" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K35" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L35" s="110"/>
+      <x:c r="A35" s="108" t="str">
+        <x:v>동부</x:v>
+      </x:c>
+      <x:c r="B35" s="110" t="str">
+        <x:v>이천한양</x:v>
+      </x:c>
+      <x:c r="C35" s="110" t="str">
+        <x:v>주식회사 현성건설</x:v>
+      </x:c>
+      <x:c r="D35" s="110" t="str">
+        <x:v>현성</x:v>
+      </x:c>
+      <x:c r="E35" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="98" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G35" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="98" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K35" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="110" t="str">
+        <x:v>통계제외</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="115" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B36" s="115" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C36" s="115" t="s">
-        <x:v>78</x:v>
+      <x:c r="A36" s="115" t="str">
+        <x:v>동부</x:v>
+      </x:c>
+      <x:c r="B36" s="115" t="str">
+        <x:v>요진건설</x:v>
+      </x:c>
+      <x:c r="C36" s="115" t="str">
+        <x:v>주식회사 한산타워</x:v>
       </x:c>
       <x:c r="D36" s="115"/>
-      <x:c r="E36" s="137">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F36" s="137">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G36" s="137"/>
-      <x:c r="H36" s="137"/>
-      <x:c r="I36" s="137"/>
-      <x:c r="J36" s="137">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K36" s="140">
+      <x:c r="E36" s="537" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F36" s="537" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" s="548" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L36" s="118"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="151" t="str">
+        <x:v>동부</x:v>
+      </x:c>
+      <x:c r="B37" s="151" t="str">
+        <x:v>홍문2지구 공동주택</x:v>
+      </x:c>
+      <x:c r="C37" s="151" t="str">
+        <x:v>(주)한진</x:v>
+      </x:c>
+      <x:c r="D37" s="151"/>
+      <x:c r="E37" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F37" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="551"/>
+      <x:c r="H37" s="551"/>
+      <x:c r="I37" s="551"/>
+      <x:c r="J37" s="551" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K37" s="539" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L36" s="118"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="151" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B37" s="151" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C37" s="151" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D37" s="151"/>
-      <x:c r="E37" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F37" s="152">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G37" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K37" s="149" t="n">
-        <x:f>SUM(E37:J37)</x:f>
+      <x:c r="L37" s="119"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="154" t="str">
+        <x:v>동부</x:v>
+      </x:c>
+      <x:c r="B38" s="154" t="str">
+        <x:v>이천 증포5지구 칸타빌 에듀파크 신축공사</x:v>
+      </x:c>
+      <x:c r="C38" s="154" t="str">
+        <x:v>국제산업렌탈(주)</x:v>
+      </x:c>
+      <x:c r="D38" s="154"/>
+      <x:c r="E38" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F38" s="542" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G38" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38" s="543" t="n">
+        <x:f>SUM(E38:J38)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L37" s="119"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="154" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B38" s="154" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C38" s="154" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D38" s="154"/>
-      <x:c r="E38" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F38" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G38" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K38" s="105">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L38" s="82"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="43" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B39" s="43"/>
-      <x:c r="C39" s="43"/>
+      <x:c r="A39" s="43" t="str">
+        <x:v>동부</x:v>
+      </x:c>
+      <x:c r="B39" s="43" t="str">
+        <x:v>경안2지구 도시개발사업 주상복합 신축공사</x:v>
+      </x:c>
+      <x:c r="C39" s="43" t="str">
+        <x:v>(주)예림타워</x:v>
+      </x:c>
       <x:c r="D39" s="88"/>
       <x:c r="E39" s="542" t="n">
-        <x:f>SUM(E35:E38)</x:f>
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="542" t="n">
-        <x:f>SUM(F35:F38)</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="542" t="n">
-        <x:f>SUM(G35:G38)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="542" t="n">
-        <x:f>SUM(H35:H38)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="542" t="n">
-        <x:f>SUM(I35:I38)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="542" t="n">
-        <x:f>SUM(J35:J38)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K39" s="543" t="n">
-        <x:f>SUM(K35:K38)</x:f>
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L39" s="82"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="43" t="s">
-        <x:v>26</x:v>
+      <x:c r="A40" s="43" t="str">
+        <x:v>동부지부 소계</x:v>
       </x:c>
       <x:c r="B40" s="43"/>
       <x:c r="C40" s="43"/>
       <x:c r="D40" s="43"/>
-      <x:c r="E40" s="102" t="n">
-        <x:f>IF($K$39=0,0,E39/$K$39)</x:f>
+      <x:c r="E40" s="542" t="n">
+        <x:f>SUM(E36:E39)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F40" s="542" t="n">
+        <x:f>SUM(F36:F39)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G40" s="542" t="n">
+        <x:f>SUM(G36:G39)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="542" t="n">
+        <x:f>SUM(H36:H39)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="542" t="n">
+        <x:f>SUM(I36:I39)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="542" t="n">
+        <x:f>SUM(J36:J39)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K40" s="543" t="n">
+        <x:f>SUM(K36:K39)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L40" s="82"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="43" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B41" s="43"/>
+      <x:c r="C41" s="43"/>
+      <x:c r="D41" s="43"/>
+      <x:c r="E41" s="102" t="n">
+        <x:f>IF($K$40=0,0,E40/$K$40)</x:f>
         <x:v>0.36363636363636365</x:v>
       </x:c>
-      <x:c r="F40" s="102" t="n">
-        <x:f>IF($K$39=0,0,F39/$K$39)</x:f>
+      <x:c r="F41" s="102" t="n">
+        <x:f>IF($K$40=0,0,F40/$K$40)</x:f>
         <x:v>0.45454545454545453</x:v>
       </x:c>
-      <x:c r="G40" s="102" t="n">
-        <x:f>IF($K$39=0,0,G39/$K$39)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="102" t="n">
-        <x:f>IF($K$39=0,0,H39/$K$39)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="102" t="n">
-        <x:f>IF($K$39=0,0,I39/$K$39)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="102" t="n">
-        <x:f>IF($K$39=0,0,J39/$K$39)</x:f>
+      <x:c r="G41" s="102" t="n">
+        <x:f>IF($K$40=0,0,G40/$K$40)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="102" t="n">
+        <x:f>IF($K$40=0,0,H40/$K$40)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="102" t="n">
+        <x:f>IF($K$40=0,0,I40/$K$40)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="102" t="n">
+        <x:f>IF($K$40=0,0,J40/$K$40)</x:f>
         <x:v>0.18181818181818182</x:v>
       </x:c>
-      <x:c r="K40" s="103" t="n">
-        <x:f>IF($K$39=0,0,K39/$K$39)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L40" s="82"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="43" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B41" s="43" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C41" s="43" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D41" s="43"/>
-      <x:c r="E41" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F41" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G41" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I41" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J41" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K41" s="105">
-        <x:v>2</x:v>
+      <x:c r="K41" s="103" t="n">
+        <x:f>IF($K$40=0,0,K40/$K$40)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L41" s="82"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="43" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B42" s="43" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C42" s="43" t="s">
-        <x:v>53</x:v>
+      <x:c r="A42" s="43" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B42" s="43" t="str">
+        <x:v>안산프로젝트팀부크(현대건설)</x:v>
+      </x:c>
+      <x:c r="C42" s="43" t="str">
+        <x:v>주식회사 한불타워</x:v>
       </x:c>
       <x:c r="D42" s="43"/>
-      <x:c r="E42" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F42" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G42" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I42" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J42" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K42" s="105">
+      <x:c r="E42" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F42" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" s="543" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L42" s="82"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="38" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B43" s="38" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C43" s="38" t="s">
-        <x:v>87</x:v>
+      <x:c r="A43" s="38" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B43" s="38" t="str">
+        <x:v>안산글로벌클라우드(삼성물산)</x:v>
+      </x:c>
+      <x:c r="C43" s="38" t="str">
+        <x:v>정호개발주식회사</x:v>
       </x:c>
       <x:c r="D43" s="38"/>
-      <x:c r="E43" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F43" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G43" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I43" s="164">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J43" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K43" s="164">
+      <x:c r="E43" s="540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F43" s="540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I43" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J43" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43" s="540" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L43" s="38"/>
+    </x:row>
+    <x:row r="44" s="14" customFormat="1">
+      <x:c r="A44" s="38" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B44" s="38" t="str">
+        <x:v>하중지구 한신공영</x:v>
+      </x:c>
+      <x:c r="C44" s="38" t="str">
+        <x:v>(주)신화중공업</x:v>
+      </x:c>
+      <x:c r="D44" s="38"/>
+      <x:c r="E44" s="540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F44" s="540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="540" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J44" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K44" s="540" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L43" s="38"/>
-    </x:row>
-    <x:row r="44" s="14" customFormat="1">
-      <x:c r="A44" s="38" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B44" s="38" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C44" s="38" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D44" s="38"/>
-      <x:c r="E44" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F44" s="164">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G44" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H44" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I44" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J44" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K44" s="164">
+      <x:c r="L44" s="38"/>
+    </x:row>
+    <x:row r="45" s="14" customFormat="1" ht="17.25">
+      <x:c r="A45" s="83" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B45" s="84" t="str">
+        <x:v>하중지구 양우건설</x:v>
+      </x:c>
+      <x:c r="C45" s="84" t="str">
+        <x:v>(주)진성타워</x:v>
+      </x:c>
+      <x:c r="D45" s="84"/>
+      <x:c r="E45" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" s="545" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G45" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I45" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J45" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K45" s="545" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L44" s="38"/>
-    </x:row>
-    <x:row r="45" s="14" customFormat="1" ht="17.25">
-      <x:c r="A45" s="83" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B45" s="84" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C45" s="84" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D45" s="84"/>
-      <x:c r="E45" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F45" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G45" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H45" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I45" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J45" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K45" s="98">
+      <x:c r="L45" s="84"/>
+    </x:row>
+    <x:row r="46" ht="17.25">
+      <x:c r="A46" s="43" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B46" s="38" t="str">
+        <x:v>시흥거모지구 S-2BL,B-2BL(대방산업개발)</x:v>
+      </x:c>
+      <x:c r="C46" s="38" t="str">
+        <x:v>주식회사 우정타워</x:v>
+      </x:c>
+      <x:c r="D46" s="38"/>
+      <x:c r="E46" s="552" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F46" s="552" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G46" s="552" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="552" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I46" s="552" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J46" s="552" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K46" s="553" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L45" s="84"/>
-    </x:row>
-    <x:row r="46" ht="17.25">
-      <x:c r="A46" s="43" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B46" s="38" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C46" s="38" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D46" s="38"/>
-      <x:c r="E46" s="99">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F46" s="99">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G46" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H46" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I46" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J46" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K46" s="100">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L46" s="38"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="108" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B47" s="108" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C47" s="108" t="s">
-        <x:v>94</x:v>
+      <x:c r="A47" s="108" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B47" s="108" t="str">
+        <x:v>배곧서울대학교병원</x:v>
+      </x:c>
+      <x:c r="C47" s="108" t="str">
+        <x:v>(주)타워링</x:v>
       </x:c>
       <x:c r="D47" s="108"/>
-      <x:c r="E47" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F47" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G47" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H47" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I47" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J47" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K47" s="132">
+      <x:c r="E47" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F47" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I47" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J47" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K47" s="554" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L47" s="111"/>
+    </x:row>
+    <x:row r="48" s="14" customFormat="1" ht="17.25">
+      <x:c r="A48" s="115" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B48" s="115" t="str">
+        <x:v>시흥하중 A-1BL 공동주택 건설공사</x:v>
+      </x:c>
+      <x:c r="C48" s="115" t="str">
+        <x:v>(주)규람타워렌탈</x:v>
+      </x:c>
+      <x:c r="D48" s="121"/>
+      <x:c r="E48" s="537" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F48" s="537" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I48" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J48" s="537" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K48" s="548" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L47" s="111"/>
-    </x:row>
-    <x:row r="48" s="14" customFormat="1" ht="17.25">
-      <x:c r="A48" s="115" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B48" s="115" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C48" s="115" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D48" s="121"/>
-      <x:c r="E48" s="137">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F48" s="137">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G48" s="137">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H48" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I48" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J48" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K48" s="140">
+      <x:c r="L48" s="118"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="151" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B49" s="151" t="str">
+        <x:v>시흥시 거모지구 B-1블록 공동주택 신축공사</x:v>
+      </x:c>
+      <x:c r="C49" s="151" t="str">
+        <x:v>주식회사 필웍스</x:v>
+      </x:c>
+      <x:c r="D49" s="155"/>
+      <x:c r="E49" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F49" s="551" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G49" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H49" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I49" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49" s="539" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L48" s="118"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="151" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B49" s="151" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C49" s="151" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D49" s="155"/>
-      <x:c r="E49" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F49" s="152">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G49" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I49" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J49" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K49" s="149">
+      <x:c r="L49" s="119"/>
+    </x:row>
+    <x:row r="50" ht="29.25">
+      <x:c r="A50" s="154" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B50" s="154" t="str">
+        <x:v>시흥거모 B-6BL 모아엘가&amp;대광로제비앙 공동주택 신축공사</x:v>
+      </x:c>
+      <x:c r="C50" s="154" t="str">
+        <x:v>(주)금강건기</x:v>
+      </x:c>
+      <x:c r="D50" s="156"/>
+      <x:c r="E50" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F50" s="555" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G50" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H50" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I50" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J50" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50" s="543" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L49" s="119"/>
-    </x:row>
-    <x:row r="50" ht="29.25">
-      <x:c r="A50" s="154" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B50" s="154" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C50" s="154" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D50" s="156"/>
-      <x:c r="E50" s="181">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F50" s="181">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G50" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H50" s="181">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I50" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J50" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K50" s="105" t="n">
-        <x:f>SUM(E50:J50)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L50" s="82" t="s">
-        <x:v>101</x:v>
-      </x:c>
+      <x:c r="L50" s="82"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="43" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B51" s="43"/>
-      <x:c r="C51" s="43"/>
+      <x:c r="A51" s="43" t="str">
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B51" s="43" t="str">
+        <x:v>시화MTV 지하주차장</x:v>
+      </x:c>
+      <x:c r="C51" s="43" t="str">
+        <x:v>(주)우리기계산업</x:v>
+      </x:c>
       <x:c r="D51" s="43"/>
       <x:c r="E51" s="542" t="n">
-        <x:f>SUM(E41:E50)</x:f>
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F51" s="542" t="n">
-        <x:f>SUM(F41:F50)</x:f>
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G51" s="542" t="n">
-        <x:f>SUM(G41:G50)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="542" t="n">
-        <x:f>SUM(H41:H50)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="542" t="n">
-        <x:f>SUM(I41:I50)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J51" s="542" t="n">
-        <x:f>SUM(J41:J50)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K51" s="543" t="n">
-        <x:f>SUM(K41:K50)</x:f>
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L51" s="82"/>
+        <x:f>SUM(E51:J51)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L51" s="82" t="str">
+        <x:v>원청사: 강산건설(주)</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="43" t="s">
-        <x:v>26</x:v>
+      <x:c r="A52" s="43" t="str">
+        <x:v>서부지부 소계</x:v>
       </x:c>
       <x:c r="B52" s="43"/>
       <x:c r="C52" s="43"/>
       <x:c r="D52" s="43"/>
-      <x:c r="E52" s="102" t="n">
-        <x:f>IF($K$51=0,0,E51/$K$51)</x:f>
+      <x:c r="E52" s="542" t="n">
+        <x:f>SUM(E42:E51)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F52" s="542" t="n">
+        <x:f>SUM(F42:F51)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G52" s="542" t="n">
+        <x:f>SUM(G42:G51)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" s="542" t="n">
+        <x:f>SUM(H42:H51)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I52" s="542" t="n">
+        <x:f>SUM(I42:I51)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J52" s="542" t="n">
+        <x:f>SUM(J42:J51)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K52" s="543" t="n">
+        <x:f>SUM(K42:K51)</x:f>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L52" s="82"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="43" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B53" s="43"/>
+      <x:c r="C53" s="43"/>
+      <x:c r="D53" s="43"/>
+      <x:c r="E53" s="102" t="n">
+        <x:f>IF($K$52=0,0,E52/$K$52)</x:f>
         <x:v>0.2727272727272727</x:v>
       </x:c>
-      <x:c r="F52" s="102" t="n">
-        <x:f>IF($K$51=0,0,F51/$K$51)</x:f>
+      <x:c r="F53" s="102" t="n">
+        <x:f>IF($K$52=0,0,F52/$K$52)</x:f>
         <x:v>0.42424242424242425</x:v>
       </x:c>
-      <x:c r="G52" s="102" t="n">
-        <x:f>IF($K$51=0,0,G51/$K$51)</x:f>
+      <x:c r="G53" s="102" t="n">
+        <x:f>IF($K$52=0,0,G52/$K$52)</x:f>
         <x:v>0.030303030303030304</x:v>
       </x:c>
-      <x:c r="H52" s="102" t="n">
-        <x:f>IF($K$51=0,0,H51/$K$51)</x:f>
+      <x:c r="H53" s="102" t="n">
+        <x:f>IF($K$52=0,0,H52/$K$52)</x:f>
         <x:v>0.030303030303030304</x:v>
       </x:c>
-      <x:c r="I52" s="102" t="n">
-        <x:f>IF($K$51=0,0,I51/$K$51)</x:f>
+      <x:c r="I53" s="102" t="n">
+        <x:f>IF($K$52=0,0,I52/$K$52)</x:f>
         <x:v>0.18181818181818182</x:v>
       </x:c>
-      <x:c r="J52" s="102" t="n">
-        <x:f>IF($K$51=0,0,J51/$K$51)</x:f>
+      <x:c r="J53" s="102" t="n">
+        <x:f>IF($K$52=0,0,J52/$K$52)</x:f>
         <x:v>0.06060606060606061</x:v>
       </x:c>
-      <x:c r="K52" s="103" t="n">
-        <x:f>IF($K$51=0,0,K51/$K$51)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L52" s="82"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="43" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B53" s="43" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C53" s="43" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D53" s="43"/>
-      <x:c r="E53" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F53" s="104">
+      <x:c r="K53" s="103" t="n">
+        <x:f>IF($K$52=0,0,K52/$K$52)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L53" s="82"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="43" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B54" s="43" t="str">
+        <x:v>군포시 SGC건설</x:v>
+      </x:c>
+      <x:c r="C54" s="43" t="str">
+        <x:v>(주)한백산업</x:v>
+      </x:c>
+      <x:c r="D54" s="43"/>
+      <x:c r="E54" s="542" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F54" s="542" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G53" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H53" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I53" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J53" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K53" s="105">
+      <x:c r="G54" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I54" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J54" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54" s="543" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L53" s="82"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="43" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B54" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C54" s="43" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D54" s="43"/>
-      <x:c r="E54" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F54" s="104">
+      <x:c r="L54" s="82"/>
+    </x:row>
+    <x:row r="55" s="14" customFormat="1" ht="17.25">
+      <x:c r="A55" s="43" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B55" s="43" t="str">
+        <x:v>관양동 DL이앤씨</x:v>
+      </x:c>
+      <x:c r="C55" s="43" t="str">
+        <x:v>(주)한백산업</x:v>
+      </x:c>
+      <x:c r="D55" s="43"/>
+      <x:c r="E55" s="542" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F55" s="542" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G54" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H54" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I54" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J54" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K54" s="105">
+      <x:c r="G55" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J55" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="543" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L54" s="82"/>
-    </x:row>
-    <x:row r="55" s="14" customFormat="1" ht="17.25">
-      <x:c r="A55" s="43" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B55" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C55" s="43" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D55" s="43"/>
-      <x:c r="E55" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F55" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G55" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I55" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J55" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K55" s="105">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L55" s="38"/>
     </x:row>
     <x:row r="56" s="14" customFormat="1">
-      <x:c r="A56" s="89" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B56" s="89" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C56" s="89" t="s">
-        <x:v>49</x:v>
+      <x:c r="A56" s="89" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B56" s="89" t="str">
+        <x:v>관양동 DL이앤씨</x:v>
+      </x:c>
+      <x:c r="C56" s="89" t="str">
+        <x:v>벽산중기산업주식회사</x:v>
       </x:c>
       <x:c r="D56" s="70"/>
-      <x:c r="E56" s="165">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F56" s="165">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G56" s="165">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="165">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I56" s="165">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J56" s="165">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K56" s="165">
+      <x:c r="E56" s="556" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F56" s="556" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="556" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="556" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I56" s="556" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J56" s="556" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K56" s="556" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L56" s="70"/>
     </x:row>
     <x:row r="57" s="14" customFormat="1" ht="17.25">
-      <x:c r="A57" s="83" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B57" s="84" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C57" s="84" t="s">
-        <x:v>110</x:v>
+      <x:c r="A57" s="83" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B57" s="84" t="str">
+        <x:v>의왕청계 시티건설</x:v>
+      </x:c>
+      <x:c r="C57" s="84" t="str">
+        <x:v>주식회사 우정타워</x:v>
       </x:c>
       <x:c r="D57" s="84"/>
-      <x:c r="E57" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F57" s="98">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G57" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H57" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I57" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J57" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K57" s="98">
+      <x:c r="E57" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F57" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I57" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J57" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K57" s="545" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L57" s="84"/>
+    </x:row>
+    <x:row r="58" ht="17.25">
+      <x:c r="A58" s="43" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B58" s="38" t="str">
+        <x:v>과천 태왕</x:v>
+      </x:c>
+      <x:c r="C58" s="38" t="str">
+        <x:v>주식회사 비엠케이</x:v>
+      </x:c>
+      <x:c r="D58" s="38"/>
+      <x:c r="E58" s="552" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F58" s="552" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G58" s="552" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H58" s="552" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I58" s="552" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J58" s="552" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K58" s="553" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L57" s="84"/>
-    </x:row>
-    <x:row r="58" ht="17.25">
-      <x:c r="A58" s="43" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B58" s="38" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C58" s="38" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D58" s="38"/>
-      <x:c r="E58" s="99">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F58" s="99">
+      <x:c r="L58" s="38"/>
+    </x:row>
+    <x:row r="59" s="14" customFormat="1" ht="17.25">
+      <x:c r="A59" s="108" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B59" s="108" t="str">
+        <x:v>과천 주암동 디에이치 아델스타(현대건설)</x:v>
+      </x:c>
+      <x:c r="C59" s="108" t="str">
+        <x:v>(주)국영타워랜드</x:v>
+      </x:c>
+      <x:c r="D59" s="108"/>
+      <x:c r="E59" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F59" s="545" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G58" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I58" s="99">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J58" s="99">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K58" s="100">
+      <x:c r="G59" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H59" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I59" s="545" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J59" s="545" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K59" s="554" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L58" s="38"/>
-    </x:row>
-    <x:row r="59" s="14" customFormat="1" ht="17.25">
-      <x:c r="A59" s="108" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B59" s="108" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C59" s="108" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D59" s="108"/>
-      <x:c r="E59" s="98">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F59" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G59" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H59" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I59" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J59" s="98">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K59" s="132">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L59" s="111"/>
     </x:row>
     <x:row r="60" s="14" customFormat="1" ht="17.25">
-      <x:c r="A60" s="115" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B60" s="115" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C60" s="115" t="s">
-        <x:v>110</x:v>
+      <x:c r="A60" s="115" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B60" s="115" t="str">
+        <x:v>안양 샘병원</x:v>
+      </x:c>
+      <x:c r="C60" s="115" t="str">
+        <x:v>주식회사 가람타워</x:v>
       </x:c>
       <x:c r="D60" s="115"/>
-      <x:c r="E60" s="137">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F60" s="137">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G60" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H60" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I60" s="137">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J60" s="137">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K60" s="140">
+      <x:c r="E60" s="537" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F60" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G60" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I60" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J60" s="537" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K60" s="548" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L60" s="118"/>
+    </x:row>
+    <x:row r="61" s="14" customFormat="1" ht="17.25">
+      <x:c r="A61" s="151" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B61" s="151" t="str">
+        <x:v>안양 박달동 신안아파트 재건축(현대산업개발)</x:v>
+      </x:c>
+      <x:c r="C61" s="151" t="str">
+        <x:v>주식회사 비엠케이</x:v>
+      </x:c>
+      <x:c r="D61" s="151"/>
+      <x:c r="E61" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F61" s="551" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G61" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I61" s="551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J61" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K61" s="539" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L60" s="118"/>
-    </x:row>
-    <x:row r="61" s="14" customFormat="1" ht="17.25">
-      <x:c r="A61" s="151" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B61" s="151" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C61" s="151" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D61" s="151"/>
-      <x:c r="E61" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F61" s="152">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G61" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I61" s="152">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J61" s="152">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K61" s="149">
+      <x:c r="L61" s="119"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="157" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B62" s="157" t="str">
+        <x:v>안양역세권지구 재개발정비사업(현대산업개발)</x:v>
+      </x:c>
+      <x:c r="C62" s="157" t="str">
+        <x:v>오투기계산업(주)</x:v>
+      </x:c>
+      <x:c r="D62" s="156"/>
+      <x:c r="E62" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F62" s="555" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G62" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I62" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J62" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K62" s="543" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L61" s="119"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="157" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B62" s="157" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C62" s="157" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D62" s="156"/>
-      <x:c r="E62" s="181">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F62" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G62" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I62" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J62" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K62" s="105" t="n">
-        <x:f>SUM(E62:J62)</x:f>
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L62" s="87"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="43" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B63" s="43"/>
-      <x:c r="C63" s="43"/>
+      <x:c r="A63" s="43" t="str">
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B63" s="43" t="str">
+        <x:v>관양동 오피스텔 신축공사</x:v>
+      </x:c>
+      <x:c r="C63" s="43" t="str">
+        <x:v>(주)유건설 (단종계약)</x:v>
+      </x:c>
       <x:c r="D63" s="88"/>
       <x:c r="E63" s="542" t="n">
-        <x:f>SUM(E53:E62)</x:f>
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F63" s="542" t="n">
-        <x:f>SUM(F53:F62)</x:f>
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G63" s="542" t="n">
-        <x:f>SUM(G53:G62)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="542" t="n">
-        <x:f>SUM(H53:H62)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I63" s="542" t="n">
-        <x:f>SUM(I53:I62)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J63" s="542" t="n">
-        <x:f>SUM(J53:J62)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K63" s="543" t="n">
-        <x:f>SUM(K53:K62)</x:f>
-        <x:v>38</x:v>
+        <x:f>SUM(E63:J63)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L63" s="82"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="43" t="s">
-        <x:v>26</x:v>
+      <x:c r="A64" s="43" t="str">
+        <x:v>북서지부 소계</x:v>
       </x:c>
       <x:c r="B64" s="43"/>
       <x:c r="C64" s="43"/>
       <x:c r="D64" s="43"/>
-      <x:c r="E64" s="102" t="n">
-        <x:f>IF($K$63=0,0,E63/$K$63)</x:f>
+      <x:c r="E64" s="542" t="n">
+        <x:f>SUM(E54:E63)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F64" s="542" t="n">
+        <x:f>SUM(F54:F63)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G64" s="542" t="n">
+        <x:f>SUM(G54:G63)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H64" s="542" t="n">
+        <x:f>SUM(H54:H63)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I64" s="542" t="n">
+        <x:f>SUM(I54:I63)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J64" s="542" t="n">
+        <x:f>SUM(J54:J63)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K64" s="543" t="n">
+        <x:f>SUM(K54:K63)</x:f>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L64" s="82"/>
+    </x:row>
+    <x:row r="65" s="14" customFormat="1" ht="17.25">
+      <x:c r="A65" s="43" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B65" s="43"/>
+      <x:c r="C65" s="43"/>
+      <x:c r="D65" s="43"/>
+      <x:c r="E65" s="102" t="n">
+        <x:f>IF($K$64=0,0,E64/$K$64)</x:f>
         <x:v>0.3157894736842105</x:v>
       </x:c>
-      <x:c r="F64" s="102" t="n">
-        <x:f>IF($K$63=0,0,F63/$K$63)</x:f>
+      <x:c r="F65" s="102" t="n">
+        <x:f>IF($K$64=0,0,F64/$K$64)</x:f>
         <x:v>0.4473684210526316</x:v>
       </x:c>
-      <x:c r="G64" s="102" t="n">
-        <x:f>IF($K$63=0,0,G63/$K$63)</x:f>
+      <x:c r="G65" s="102" t="n">
+        <x:f>IF($K$64=0,0,G64/$K$64)</x:f>
         <x:v>0.05263157894736842</x:v>
       </x:c>
-      <x:c r="H64" s="102" t="n">
-        <x:f>IF($K$63=0,0,H63/$K$63)</x:f>
+      <x:c r="H65" s="102" t="n">
+        <x:f>IF($K$64=0,0,H64/$K$64)</x:f>
         <x:v>0.02631578947368421</x:v>
       </x:c>
-      <x:c r="I64" s="102" t="n">
-        <x:f>IF($K$63=0,0,I63/$K$63)</x:f>
+      <x:c r="I65" s="102" t="n">
+        <x:f>IF($K$64=0,0,I64/$K$64)</x:f>
         <x:v>0.15789473684210525</x:v>
       </x:c>
-      <x:c r="J64" s="102" t="n">
-        <x:f>IF($K$63=0,0,J63/$K$63)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K64" s="103" t="n">
-        <x:f>IF($K$63=0,0,K63/$K$63)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L64" s="82"/>
-    </x:row>
-    <x:row r="65" s="14" customFormat="1" ht="17.25">
-      <x:c r="A65" s="43" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B65" s="43" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C65" s="43" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D65" s="43"/>
-      <x:c r="E65" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F65" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G65" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H65" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I65" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J65" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K65" s="105">
+      <x:c r="J65" s="102" t="n">
+        <x:f>IF($K$64=0,0,J64/$K$64)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K65" s="103" t="n">
+        <x:f>IF($K$64=0,0,K64/$K$64)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L65" s="38"/>
+    </x:row>
+    <x:row r="66" s="14" customFormat="1" ht="17.25">
+      <x:c r="A66" s="43" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B66" s="43" t="str">
+        <x:v>양지 대우 원클러스터</x:v>
+      </x:c>
+      <x:c r="C66" s="43" t="str">
+        <x:v>(주)규람타워렌탈</x:v>
+      </x:c>
+      <x:c r="D66" s="43"/>
+      <x:c r="E66" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F66" s="542" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G66" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I66" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J66" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="543" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L65" s="38"/>
-    </x:row>
-    <x:row r="66" s="14" customFormat="1" ht="17.25">
-      <x:c r="A66" s="43" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B66" s="43" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C66" s="43" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D66" s="43"/>
-      <x:c r="E66" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F66" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G66" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H66" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I66" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J66" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K66" s="105">
+      <x:c r="L66" s="38"/>
+    </x:row>
+    <x:row r="67" s="14" customFormat="1" ht="17.25">
+      <x:c r="A67" s="43" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B67" s="43" t="str">
+        <x:v>양지 SM경남 아너스빌</x:v>
+      </x:c>
+      <x:c r="C67" s="43" t="str">
+        <x:v>주식회사 비엠케이</x:v>
+      </x:c>
+      <x:c r="D67" s="43"/>
+      <x:c r="E67" s="542" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F67" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67" s="542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I67" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J67" s="542" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="543" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L66" s="38"/>
-    </x:row>
-    <x:row r="67" s="14" customFormat="1" ht="17.25">
-      <x:c r="A67" s="43" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B67" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C67" s="43" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D67" s="43"/>
-      <x:c r="E67" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F67" s="104">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G67" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H67" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I67" s="104">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J67" s="104">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K67" s="105">
+      <x:c r="L67" s="38"/>
+    </x:row>
+    <x:row r="68" s="14" customFormat="1">
+      <x:c r="A68" s="38" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B68" s="38" t="str">
+        <x:v>역북 푸르지오 클루센트(대우건설)</x:v>
+      </x:c>
+      <x:c r="C68" s="38" t="str">
+        <x:v>벽산중기산업주식회사</x:v>
+      </x:c>
+      <x:c r="D68" s="38"/>
+      <x:c r="E68" s="540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F68" s="540" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G68" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I68" s="540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J68" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K68" s="540" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L67" s="38"/>
-    </x:row>
-    <x:row r="68" s="14" customFormat="1">
-      <x:c r="A68" s="38" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B68" s="38" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C68" s="38" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D68" s="38" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E68" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F68" s="164">
+      <x:c r="L68" s="38"/>
+    </x:row>
+    <x:row r="69" s="14" customFormat="1">
+      <x:c r="A69" s="90" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B69" s="90" t="str">
+        <x:v>고림 대광로제비앙</x:v>
+      </x:c>
+      <x:c r="C69" s="90" t="str">
+        <x:v>주식회사 현성건설</x:v>
+      </x:c>
+      <x:c r="D69" s="90" t="str">
+        <x:v>현성</x:v>
+      </x:c>
+      <x:c r="E69" s="557" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F69" s="557" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G68" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H68" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I68" s="164">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J68" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K68" s="164">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L68" s="38" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" s="14" customFormat="1">
-      <x:c r="A69" s="90" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B69" s="90" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C69" s="90" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D69" s="90"/>
-      <x:c r="E69" s="106">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F69" s="106">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G69" s="106">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H69" s="106">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I69" s="106">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J69" s="106">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K69" s="106">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L69" s="90"/>
+      <x:c r="G69" s="557" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H69" s="557" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I69" s="557" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J69" s="557" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K69" s="557" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L69" s="90" t="str">
+        <x:v>통계제외</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" s="14" customFormat="1" ht="17.25">
-      <x:c r="A70" s="69" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B70" s="69" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C70" s="69" t="s">
-        <x:v>126</x:v>
+      <x:c r="A70" s="69" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B70" s="69" t="str">
+        <x:v>백암 오뚜기물류센타</x:v>
+      </x:c>
+      <x:c r="C70" s="69" t="str">
+        <x:v>주식회사 가람타워</x:v>
       </x:c>
       <x:c r="D70" s="69"/>
-      <x:c r="E70" s="166">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F70" s="166">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G70" s="166">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H70" s="166">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I70" s="166">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J70" s="166">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" s="166">
-        <x:v>1</x:v>
+      <x:c r="E70" s="534" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F70" s="534" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G70" s="534" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H70" s="534" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I70" s="534" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J70" s="534" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K70" s="534" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L70" s="69"/>
     </x:row>
     <x:row r="71" s="14" customFormat="1" ht="17.25">
-      <x:c r="A71" s="91" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B71" s="91" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C71" s="91" t="s">
-        <x:v>37</x:v>
+      <x:c r="A71" s="91" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B71" s="91" t="str">
+        <x:v>마평동 여성복지회관</x:v>
+      </x:c>
+      <x:c r="C71" s="91" t="str">
+        <x:v>(주)무기타워렌탈</x:v>
       </x:c>
       <x:c r="D71" s="91"/>
-      <x:c r="E71" s="167">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F71" s="167">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G71" s="167">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H71" s="167">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I71" s="167">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J71" s="167">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K71" s="167">
+      <x:c r="E71" s="544" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F71" s="544" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G71" s="544" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H71" s="544" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I71" s="544" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J71" s="544" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="544" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L71" s="92"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="93" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B72" s="93" t="str">
+        <x:v>용인 라온프라이빗</x:v>
+      </x:c>
+      <x:c r="C72" s="93" t="str">
+        <x:v>(주)우성건설기계</x:v>
+      </x:c>
+      <x:c r="D72" s="93"/>
+      <x:c r="E72" s="558" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F72" s="558" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G72" s="558" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72" s="558" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" s="558" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J72" s="558" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="558" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L71" s="92"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="93" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B72" s="93" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C72" s="93" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D72" s="93"/>
-      <x:c r="E72" s="101">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F72" s="101">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G72" s="101">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H72" s="101">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I72" s="101">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J72" s="101">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K72" s="101">
+      <x:c r="L72" s="94"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="112" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B73" s="112" t="str">
+        <x:v>용인덕성 AI데이터센터 신축공사</x:v>
+      </x:c>
+      <x:c r="C73" s="112" t="str">
+        <x:v>(주)타워랜드</x:v>
+      </x:c>
+      <x:c r="D73" s="112"/>
+      <x:c r="E73" s="559" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F73" s="559" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G73" s="559" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H73" s="559" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I73" s="559" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J73" s="559" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="559" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L72" s="94"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="112" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B73" s="112" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C73" s="112" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D73" s="112" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E73" s="133">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F73" s="133">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G73" s="133">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H73" s="133">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I73" s="133">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J73" s="133">
+      <x:c r="L73" s="113"/>
+    </x:row>
+    <x:row r="74" s="14" customFormat="1">
+      <x:c r="A74" s="122" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B74" s="122" t="str">
+        <x:v>용인클러스터 상생협력시설(기숙사 1차)</x:v>
+      </x:c>
+      <x:c r="C74" s="122" t="str">
+        <x:v>(주)규람타워렌탈</x:v>
+      </x:c>
+      <x:c r="D74" s="122" t="str">
+        <x:v>원철규(미정3)</x:v>
+      </x:c>
+      <x:c r="E74" s="560" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F74" s="560" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G74" s="560" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H74" s="560" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I74" s="560" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J74" s="560" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K73" s="133">
+      <x:c r="K74" s="560" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L73" s="113"/>
-    </x:row>
-    <x:row r="74" s="14" customFormat="1">
-      <x:c r="A74" s="122" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B74" s="122" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C74" s="122" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D74" s="122"/>
-      <x:c r="E74" s="142">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F74" s="142">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G74" s="142">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H74" s="142">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I74" s="142">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J74" s="142">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K74" s="142">
+      <x:c r="L74" s="123"/>
+    </x:row>
+    <x:row r="75" s="14" customFormat="1">
+      <x:c r="A75" s="158" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B75" s="158" t="str">
+        <x:v>수지자이에디시온</x:v>
+      </x:c>
+      <x:c r="C75" s="158" t="str">
+        <x:v>(주)한진</x:v>
+      </x:c>
+      <x:c r="D75" s="158"/>
+      <x:c r="E75" s="561" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F75" s="561" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G75" s="561" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H75" s="561" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I75" s="561" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J75" s="561" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="561" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L74" s="123"/>
-    </x:row>
-    <x:row r="75" s="14" customFormat="1">
-      <x:c r="A75" s="158" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B75" s="158" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C75" s="158" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D75" s="158"/>
-      <x:c r="E75" s="159">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F75" s="159">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G75" s="159">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H75" s="159">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I75" s="159">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J75" s="159">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K75" s="159">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L75" s="124"/>
     </x:row>
     <x:row r="76" s="14" customFormat="1">
-      <x:c r="A76" s="160" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B76" s="160" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C76" s="160" t="s">
-        <x:v>135</x:v>
+      <x:c r="A76" s="160" t="str">
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B76" s="160" t="str">
+        <x:v>기흥변전소</x:v>
+      </x:c>
+      <x:c r="C76" s="160" t="str">
+        <x:v>(주)대원타워렌탈</x:v>
       </x:c>
       <x:c r="D76" s="160"/>
-      <x:c r="E76" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F76" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G76" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H76" s="181">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I76" s="181">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J76" s="181">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K76" s="159" t="n">
-        <x:f>SUM(E76:J76)</x:f>
-        <x:v>3</x:v>
+      <x:c r="E76" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F76" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G76" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H76" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I76" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J76" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76" s="561" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L76" s="90"/>
     </x:row>
@@ -6530,14 +6480,14 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B77" s="69" t="str">
-        <x:v>용인클라우드</x:v>
+        <x:v>한양립스</x:v>
       </x:c>
       <x:c r="C77" s="69" t="str">
-        <x:v>(주)성광엔지니어링</x:v>
+        <x:v>(주)제이에스글로벌산업</x:v>
       </x:c>
       <x:c r="D77" s="69"/>
       <x:c r="E77" s="534" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F77" s="534" t="n">
         <x:v>0</x:v>
@@ -6546,125 +6496,126 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="534" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I77" s="534" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J77" s="534" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K77" s="534" t="n">
         <x:f>SUM(E77:J77)</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L77" s="69"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="91" t="str">
-        <x:v>용인지부 소계</x:v>
-      </x:c>
-      <x:c r="B78" s="91"/>
-      <x:c r="C78" s="91"/>
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B78" s="91" t="str">
+        <x:v>용인클라우드</x:v>
+      </x:c>
+      <x:c r="C78" s="91" t="str">
+        <x:v>(주)성광엔지니어링</x:v>
+      </x:c>
       <x:c r="D78" s="91"/>
       <x:c r="E78" s="544" t="n">
-        <x:f>SUM(E65:E67,E69:E77)</x:f>
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F78" s="544" t="n">
-        <x:f>SUM(F65:F67,F69:F77)</x:f>
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G78" s="544" t="n">
-        <x:f>SUM(G65:G67,G69:G77)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="544" t="n">
-        <x:f>SUM(H65:H67,H69:H77)</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I78" s="544" t="n">
-        <x:f>SUM(I65:I67,I69:I77)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J78" s="544" t="n">
-        <x:f>SUM(J65:J67,J69:J77)</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K78" s="544" t="n">
-        <x:f>SUM(K65:K67,K69:K77)</x:f>
-        <x:v>35</x:v>
+        <x:f>SUM(E78:J78)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L78" s="91"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="93" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>용인지부 소계</x:v>
       </x:c>
       <x:c r="B79" s="93"/>
       <x:c r="C79" s="93"/>
       <x:c r="D79" s="93"/>
-      <x:c r="E79" s="535" t="n">
-        <x:f>IF($K$78=0,0,E78/$K$78)</x:f>
-        <x:v>0.2857142857142857</x:v>
-      </x:c>
-      <x:c r="F79" s="535" t="n">
-        <x:f>IF($K$78=0,0,F78/$K$78)</x:f>
-        <x:v>0.3142857142857143</x:v>
-      </x:c>
-      <x:c r="G79" s="535" t="n">
-        <x:f>IF($K$78=0,0,G78/$K$78)</x:f>
-        <x:v>0.02857142857142857</x:v>
-      </x:c>
-      <x:c r="H79" s="535" t="n">
-        <x:f>IF($K$78=0,0,H78/$K$78)</x:f>
-        <x:v>0.11428571428571428</x:v>
-      </x:c>
-      <x:c r="I79" s="535" t="n">
-        <x:f>IF($K$78=0,0,I78/$K$78)</x:f>
-        <x:v>0.17142857142857143</x:v>
-      </x:c>
-      <x:c r="J79" s="535" t="n">
-        <x:f>IF($K$78=0,0,J78/$K$78)</x:f>
-        <x:v>0.08571428571428572</x:v>
-      </x:c>
-      <x:c r="K79" s="535" t="n">
-        <x:f>IF($K$78=0,0,K78/$K$78)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E79" s="558" t="n">
+        <x:f>SUM(E66:E68,E70:E78)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F79" s="558" t="n">
+        <x:f>SUM(F66:F68,F70:F78)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G79" s="558" t="n">
+        <x:f>SUM(G66:G68,G70:G78)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H79" s="558" t="n">
+        <x:f>SUM(H66:H68,H70:H78)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I79" s="558" t="n">
+        <x:f>SUM(I66:I68,I70:I78)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J79" s="558" t="n">
+        <x:f>SUM(J66:J68,J70:J78)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K79" s="558" t="n">
+        <x:f>SUM(K66:K68,K70:K78)</x:f>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L79" s="93"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="114" t="str">
-        <x:v>중부</x:v>
-      </x:c>
-      <x:c r="B80" s="114" t="str">
-        <x:v>당수동 한신</x:v>
-      </x:c>
-      <x:c r="C80" s="114" t="str">
-        <x:v>주식회사월드타워</x:v>
-      </x:c>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B80" s="114"/>
+      <x:c r="C80" s="114"/>
       <x:c r="D80" s="114"/>
-      <x:c r="E80" s="135" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F80" s="135" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G80" s="135" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H80" s="135" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I80" s="135" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J80" s="135" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K80" s="135" t="n">
-        <x:v>5</x:v>
+      <x:c r="E80" s="566" t="n">
+        <x:f>IF($K$79=0,0,E79/$K$79)</x:f>
+        <x:v>0.2857142857142857</x:v>
+      </x:c>
+      <x:c r="F80" s="566" t="n">
+        <x:f>IF($K$79=0,0,F79/$K$79)</x:f>
+        <x:v>0.3142857142857143</x:v>
+      </x:c>
+      <x:c r="G80" s="566" t="n">
+        <x:f>IF($K$79=0,0,G79/$K$79)</x:f>
+        <x:v>0.02857142857142857</x:v>
+      </x:c>
+      <x:c r="H80" s="566" t="n">
+        <x:f>IF($K$79=0,0,H79/$K$79)</x:f>
+        <x:v>0.11428571428571428</x:v>
+      </x:c>
+      <x:c r="I80" s="566" t="n">
+        <x:f>IF($K$79=0,0,I79/$K$79)</x:f>
+        <x:v>0.17142857142857143</x:v>
+      </x:c>
+      <x:c r="J80" s="566" t="n">
+        <x:f>IF($K$79=0,0,J79/$K$79)</x:f>
+        <x:v>0.08571428571428572</x:v>
+      </x:c>
+      <x:c r="K80" s="566" t="n">
+        <x:f>IF($K$79=0,0,K79/$K$79)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L80" s="114"/>
     </x:row>
@@ -6673,32 +6624,32 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B81" s="125" t="str">
-        <x:v>당수동 한라</x:v>
+        <x:v>당수동 한신</x:v>
       </x:c>
       <x:c r="C81" s="125" t="str">
-        <x:v>벽산중기산업주식회사</x:v>
+        <x:v>주식회사월드타워</x:v>
       </x:c>
       <x:c r="D81" s="125"/>
-      <x:c r="E81" s="143" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F81" s="143" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G81" s="143" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H81" s="143" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I81" s="143" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J81" s="143" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K81" s="143" t="n">
-        <x:v>4</x:v>
+      <x:c r="E81" s="562" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F81" s="562" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G81" s="562" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81" s="562" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I81" s="562" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J81" s="562" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K81" s="562" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L81" s="125"/>
     </x:row>
@@ -6707,31 +6658,31 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B82" s="161" t="str">
-        <x:v>당수동 계룡</x:v>
+        <x:v>당수동 한라</x:v>
       </x:c>
       <x:c r="C82" s="161" t="str">
-        <x:v>주식회사 화성건기</x:v>
+        <x:v>벽산중기산업주식회사</x:v>
       </x:c>
       <x:c r="D82" s="161"/>
-      <x:c r="E82" s="162" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F82" s="162" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G82" s="162" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H82" s="162" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I82" s="162" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J82" s="162" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K82" s="162" t="n">
+      <x:c r="E82" s="563" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F82" s="563" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G82" s="563" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H82" s="563" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I82" s="563" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J82" s="563" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K82" s="563" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L82" s="126"/>
@@ -6741,32 +6692,32 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B83" s="163" t="str">
-        <x:v>영화동 두산</x:v>
+        <x:v>당수동 계룡</x:v>
       </x:c>
       <x:c r="C83" s="163" t="str">
-        <x:v>(주)야후건기</x:v>
+        <x:v>주식회사 화성건기</x:v>
       </x:c>
       <x:c r="D83" s="163"/>
-      <x:c r="E83" s="181" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F83" s="181" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G83" s="181" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H83" s="181" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I83" s="181" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J83" s="181" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K83" s="182" t="n">
-        <x:v>3</x:v>
+      <x:c r="E83" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F83" s="555" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I83" s="555" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J83" s="555" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83" s="564" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -6775,109 +6726,143 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>수원 친환경 에너지 개선공사 주기기 구매</x:v>
+        <x:v>영화동 두산</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>신우개발(주)</x:v>
+        <x:v>(주)야후건기</x:v>
       </x:c>
       <x:c r="D84"/>
-      <x:c r="E84" s="107" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F84" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G84" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H84" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I84" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J84" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K84" s="107" t="n">
-        <x:f>SUM(E84:J84)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E84" s="536" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F84" s="536" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="536" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="536" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84" s="536" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J84" s="536" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K84" s="536" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
-        <x:v>중부지부 소계</x:v>
-      </x:c>
-      <x:c r="B85"/>
-      <x:c r="C85"/>
+        <x:v>중부</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>수원 친환경 에너지 개선공사 주기기 구매</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>신우개발(주)</x:v>
+      </x:c>
       <x:c r="D85"/>
       <x:c r="E85" s="536" t="n">
-        <x:f>SUM(E80:E84)</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F85" s="536" t="n">
-        <x:f>SUM(F80:F84)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G85" s="536" t="n">
-        <x:f>SUM(G80:G84)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="536" t="n">
-        <x:f>SUM(H80:H84)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="536" t="n">
-        <x:f>SUM(I80:I84)</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J85" s="536" t="n">
-        <x:f>SUM(J80:J84)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K85" s="536" t="n">
-        <x:f>SUM(K80:K84)</x:f>
-        <x:v>17</x:v>
+        <x:f>SUM(E85:J85)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>중부지부 소계</x:v>
       </x:c>
       <x:c r="B86"/>
       <x:c r="C86"/>
       <x:c r="D86"/>
-      <x:c r="E86" s="95" t="n">
-        <x:f>IF($K$85=0,0,E85/$K$85)</x:f>
+      <x:c r="E86" s="536" t="n">
+        <x:f>SUM(E81:E85)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F86" s="536" t="n">
+        <x:f>SUM(F81:F85)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G86" s="536" t="n">
+        <x:f>SUM(G81:G85)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H86" s="536" t="n">
+        <x:f>SUM(H81:H85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I86" s="536" t="n">
+        <x:f>SUM(I81:I85)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J86" s="536" t="n">
+        <x:f>SUM(J81:J85)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K86" s="536" t="n">
+        <x:f>SUM(K81:K85)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87" s="95" t="n">
+        <x:f>IF($K$86=0,0,E86/$K$86)</x:f>
         <x:v>0.29411764705882354</x:v>
       </x:c>
-      <x:c r="F86" s="95" t="n">
-        <x:f>IF($K$85=0,0,F85/$K$85)</x:f>
+      <x:c r="F87" s="95" t="n">
+        <x:f>IF($K$86=0,0,F86/$K$86)</x:f>
         <x:v>0.35294117647058826</x:v>
       </x:c>
-      <x:c r="G86" s="95" t="n">
-        <x:f>IF($K$85=0,0,G85/$K$85)</x:f>
+      <x:c r="G87" s="95" t="n">
+        <x:f>IF($K$86=0,0,G86/$K$86)</x:f>
         <x:v>0.058823529411764705</x:v>
       </x:c>
-      <x:c r="H86" s="95" t="n">
-        <x:f>IF($K$85=0,0,H85/$K$85)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I86" s="95" t="n">
-        <x:f>IF($K$85=0,0,I85/$K$85)</x:f>
+      <x:c r="H87" s="95" t="n">
+        <x:f>IF($K$86=0,0,H86/$K$86)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I87" s="95" t="n">
+        <x:f>IF($K$86=0,0,I86/$K$86)</x:f>
         <x:v>0.29411764705882354</x:v>
       </x:c>
-      <x:c r="J86" s="95" t="n">
-        <x:f>IF($K$85=0,0,J85/$K$85)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K86" s="95" t="n">
-        <x:f>IF($K$85=0,0,K85/$K$85)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L86"/>
+      <x:c r="J87" s="95" t="n">
+        <x:f>IF($K$86=0,0,J86/$K$86)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K87" s="95" t="n">
+        <x:f>IF($K$86=0,0,K86/$K$86)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L87"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6899,7 +6884,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="187" t="s">
-        <x:v>136</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B1" s="188"/>
       <x:c r="C1" s="188"/>
@@ -6913,10 +6898,10 @@
     </x:row>
     <x:row r="2" s="14" customFormat="1" ht="21.200000762939453" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
         <x:v>2</x:v>
@@ -6934,18 +6919,18 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H2" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="J2" s="36" t="s">
-        <x:v>140</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="11">
         <x:v>3</x:v>
@@ -6977,7 +6962,7 @@
     </x:row>
     <x:row r="4" s="14" customFormat="1" ht="21.200000762939453" customHeight="1">
       <x:c r="A4" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B4" s="11">
         <x:v>3</x:v>
@@ -7106,7 +7091,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="11">
         <x:v>2</x:v>
@@ -7304,7 +7289,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="11">
         <x:v>3</x:v>
@@ -7336,7 +7321,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="11">
         <x:v>1</x:v>
@@ -7432,7 +7417,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B18" s="11">
         <x:v>1</x:v>
@@ -7528,7 +7513,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B21" s="11">
         <x:v>2</x:v>
@@ -7560,7 +7545,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="11">
         <x:v>1</x:v>
@@ -7592,7 +7577,7 @@
     </x:row>
     <x:row r="23" s="14" customFormat="1" ht="21.200000762939453" customHeight="1">
       <x:c r="A23" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="128">
         <x:v>2</x:v>
@@ -7659,7 +7644,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="11">
         <x:v>1</x:v>
@@ -7691,7 +7676,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B26" s="11">
         <x:v>1</x:v>
@@ -7787,7 +7772,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B29" s="11">
         <x:v>1</x:v>
@@ -7851,7 +7836,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B31" s="11">
         <x:v>1</x:v>
@@ -7883,7 +7868,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B32" s="11">
         <x:v>1</x:v>
@@ -7915,7 +7900,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="12" t="s">
-        <x:v>129</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B33" s="11">
         <x:v>1</x:v>
@@ -7947,7 +7932,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B34" s="11">
         <x:v>2</x:v>
@@ -7981,7 +7966,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B35" s="11">
         <x:v>1</x:v>
@@ -8013,7 +7998,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B36">
         <x:v>2</x:v>
@@ -8046,7 +8031,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
-        <x:v>96</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B37">
         <x:v>1</x:v>
@@ -8078,7 +8063,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
-        <x:v>67</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B38">
         <x:v>1</x:v>
@@ -8110,7 +8095,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
-        <x:v>98</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B39">
         <x:v>1</x:v>
@@ -8142,7 +8127,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="s">
-        <x:v>117</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B40">
         <x:v>1</x:v>
@@ -8174,7 +8159,7 @@
     </x:row>
     <x:row r="41" s="14" customFormat="1" ht="22.350000381469727" customHeight="1">
       <x:c r="A41" s="39" t="s">
-        <x:v>135</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B41">
         <x:v>1</x:v>
@@ -8271,6 +8256,40 @@
       <x:c r="J43" s="95" t="n">
         <x:f>IF(I43=0,0,C43/I43)</x:f>
         <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>(주)제일타워공영</x:v>
+      </x:c>
+      <x:c r="B44" s="536" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C44" s="536" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D44" s="536" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E44" s="536" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" s="536" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G44" s="536" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="536" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="536" t="n">
+        <x:f>SUM(C44:H44)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J44" s="95" t="n">
+        <x:f>IF(I44=0,0,C44/I44)</x:f>
+        <x:v>0.25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8296,7 +8315,7 @@
   <x:sheetData>
     <x:row r="1" s="14" customFormat="1" ht="20.100000381469727" customHeight="1">
       <x:c r="A1" s="189" t="s">
-        <x:v>143</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B1" s="184"/>
       <x:c r="C1" s="184"/>
@@ -8309,7 +8328,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="191" t="s">
-        <x:v>144</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B2" s="184"/>
       <x:c r="C2" s="184"/>
@@ -8322,7 +8341,7 @@
     </x:row>
     <x:row r="4" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A4" s="190" t="s">
-        <x:v>145</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B4" s="184"/>
       <x:c r="C4" s="184"/>
@@ -8335,19 +8354,19 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="15" t="s">
-        <x:v>146</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>147</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>148</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D5" s="15" t="s">
-        <x:v>149</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E5" s="15" t="s">
-        <x:v>150</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F5" s="15" t="s">
         <x:v>7</x:v>
@@ -8381,7 +8400,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="s">
-        <x:v>151</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="35" t="n">
         <x:f>B6/A6</x:f>
@@ -8406,7 +8425,7 @@
     </x:row>
     <x:row r="9" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A9" s="190" t="s">
-        <x:v>152</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B9" s="184"/>
       <x:c r="C9" s="184"/>
@@ -8419,31 +8438,31 @@
     </x:row>
     <x:row r="10" s="14" customFormat="1" ht="37.5" customHeight="1">
       <x:c r="A10" s="18" t="s">
-        <x:v>153</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B10" s="18" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="18" t="s">
-        <x:v>154</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D10" s="18" t="s">
-        <x:v>147</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E10" s="18" t="s">
-        <x:v>148</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
-        <x:v>155</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G10" s="18" t="s">
-        <x:v>150</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H10" s="18" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="I10" s="18" t="s">
-        <x:v>156</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -8451,7 +8470,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="20" t="s">
-        <x:v>157</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C11" s="21">
         <x:v>36</x:v>
@@ -8472,7 +8491,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I11" s="23" t="s">
-        <x:v>158</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -8480,7 +8499,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B12" s="25" t="s">
-        <x:v>159</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C12" s="26">
         <x:v>34</x:v>
@@ -8501,7 +8520,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I12" s="28" t="s">
-        <x:v>160</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -8509,7 +8528,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B13" s="20" t="s">
-        <x:v>161</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C13" s="21">
         <x:v>10</x:v>
@@ -8530,7 +8549,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="23" t="s">
-        <x:v>162</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -8538,7 +8557,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B14" s="25" t="s">
-        <x:v>163</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C14" s="26">
         <x:v>14</x:v>
@@ -8559,7 +8578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8567,7 +8586,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B15" s="20" t="s">
-        <x:v>165</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C15" s="21">
         <x:v>5</x:v>
@@ -8588,7 +8607,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8596,7 +8615,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B16" s="25" t="s">
-        <x:v>166</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C16" s="26">
         <x:v>3</x:v>
@@ -8617,7 +8636,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="28" t="s">
-        <x:v>167</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -8625,7 +8644,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="20" t="s">
-        <x:v>168</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C17" s="21">
         <x:v>15</x:v>
@@ -8646,7 +8665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="23" t="s">
-        <x:v>169</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8654,7 +8673,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="25" t="s">
-        <x:v>170</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C18" s="26">
         <x:v>5</x:v>
@@ -8675,7 +8694,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="28" t="s">
-        <x:v>171</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8683,7 +8702,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B19" s="20" t="s">
-        <x:v>172</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C19" s="21">
         <x:v>2</x:v>
@@ -8704,7 +8723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I19" s="23" t="s">
-        <x:v>173</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="14" customFormat="1" ht="14.449999809265137" customHeight="1">
@@ -8712,7 +8731,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="25" t="s">
-        <x:v>174</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C20" s="26">
         <x:v>6</x:v>
@@ -8733,13 +8752,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I20" s="28" t="s">
-        <x:v>164</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="14" customFormat="1" ht="14.449999809265137" customHeight="1">
       <x:c r="A21" s="29"/>
       <x:c r="B21" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C21" s="31" t="n">
         <x:f t="shared" ref="C21:H21" si="1">SUM(C11:C20)</x:f>
@@ -8795,7 +8814,7 @@
   <x:sheetData>
     <x:row r="1" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A1" s="192" t="s">
-        <x:v>176</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B1" s="193"/>
       <x:c r="C1" s="193"/>
@@ -8809,10 +8828,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B2" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2" s="40" t="s">
         <x:v>14</x:v>
@@ -8827,7 +8846,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G2" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H2" s="40" t="s">
         <x:v>6</x:v>
@@ -8856,10 +8875,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="41" t="s">
-        <x:v>180</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C4" s="43" t="s">
-        <x:v>181</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D4" s="42">
         <x:v>5</x:v>
@@ -8951,7 +8970,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="194" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B9" s="193"/>
       <x:c r="C9" s="193"/>
@@ -8995,7 +9014,7 @@
     </x:row>
     <x:row r="11" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A11" s="192" t="s">
-        <x:v>183</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B11" s="193"/>
       <x:c r="C11" s="193"/>
@@ -9009,10 +9028,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B12" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C12" s="40" t="s">
         <x:v>14</x:v>
@@ -9027,7 +9046,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G12" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H12" s="40" t="s">
         <x:v>6</x:v>
@@ -9041,13 +9060,13 @@
     </x:row>
     <x:row r="13" ht="17.25">
       <x:c r="A13" s="41" t="s">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="41" t="s">
-        <x:v>184</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C13" s="43" t="s">
-        <x:v>185</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D13" s="42">
         <x:v>4</x:v>
@@ -9074,10 +9093,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="42" t="s">
-        <x:v>186</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C14" s="43" t="s">
-        <x:v>187</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D14" s="42">
         <x:v>8</x:v>
@@ -9163,7 +9182,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="194" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B17" s="193"/>
       <x:c r="C17" s="193"/>
@@ -9207,7 +9226,7 @@
     </x:row>
     <x:row r="19" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A19" s="192" t="s">
-        <x:v>188</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B19" s="193"/>
       <x:c r="C19" s="193"/>
@@ -9221,10 +9240,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B20" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C20" s="40" t="s">
         <x:v>14</x:v>
@@ -9239,7 +9258,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G20" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H20" s="40" t="s">
         <x:v>6</x:v>
@@ -9280,10 +9299,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="41" t="s">
-        <x:v>189</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C23" s="43" t="s">
-        <x:v>190</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D23" s="42">
         <x:v>7</x:v>
@@ -9307,13 +9326,13 @@
     </x:row>
     <x:row r="24" ht="17.25">
       <x:c r="A24" s="42" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="41" t="s">
-        <x:v>191</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C24" s="43" t="s">
-        <x:v>99</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D24" s="42">
         <x:v>3</x:v>
@@ -9340,10 +9359,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="41" t="s">
-        <x:v>192</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C25" s="43" t="s">
-        <x:v>193</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D25" s="42">
         <x:v>4</x:v>
@@ -9370,10 +9389,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="41" t="s">
-        <x:v>194</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C26" s="43" t="s">
-        <x:v>195</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D26" s="42">
         <x:v>2</x:v>
@@ -9429,7 +9448,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="194" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B28" s="193"/>
       <x:c r="C28" s="193"/>
@@ -9473,7 +9492,7 @@
     </x:row>
     <x:row r="30" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A30" s="192" t="s">
-        <x:v>196</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B30" s="193"/>
       <x:c r="C30" s="193"/>
@@ -9487,10 +9506,10 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B31" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C31" s="40" t="s">
         <x:v>14</x:v>
@@ -9505,7 +9524,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H31" s="40" t="s">
         <x:v>6</x:v>
@@ -9552,10 +9571,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
-        <x:v>197</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C33" s="43" t="s">
-        <x:v>198</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D33" s="42">
         <x:v>5</x:v>
@@ -9594,10 +9613,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B35" s="41" t="s">
-        <x:v>199</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C35" s="43" t="s">
-        <x:v>200</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D35" s="42">
         <x:v>2</x:v>
@@ -9624,10 +9643,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B36" s="41" t="s">
-        <x:v>180</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C36" s="43" t="s">
-        <x:v>201</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D36" s="42">
         <x:v>2</x:v>
@@ -9654,10 +9673,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B37" s="42" t="s">
-        <x:v>197</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C37" s="43" t="s">
-        <x:v>202</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D37" s="42">
         <x:v>4</x:v>
@@ -9713,7 +9732,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="194" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B39" s="193"/>
       <x:c r="C39" s="193"/>
@@ -9757,7 +9776,7 @@
     </x:row>
     <x:row r="41" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A41" s="192" t="s">
-        <x:v>203</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B41" s="193"/>
       <x:c r="C41" s="193"/>
@@ -9771,10 +9790,10 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B42" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C42" s="40" t="s">
         <x:v>14</x:v>
@@ -9789,7 +9808,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G42" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H42" s="40" t="s">
         <x:v>6</x:v>
@@ -9803,13 +9822,13 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="41" t="s">
-        <x:v>107</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B43" s="38" t="s">
-        <x:v>194</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C43" s="38" t="s">
-        <x:v>204</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D43" s="49">
         <x:v>4</x:v>
@@ -9833,13 +9852,13 @@
     </x:row>
     <x:row r="44" ht="17.25">
       <x:c r="A44" s="41" t="s">
-        <x:v>141</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B44" s="41" t="s">
-        <x:v>205</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C44" s="43" t="s">
-        <x:v>206</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D44" s="42">
         <x:v>4</x:v>
@@ -9896,10 +9915,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B46" s="41" t="s">
-        <x:v>207</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C46" s="43" t="s">
-        <x:v>208</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D46" s="42">
         <x:v>5</x:v>
@@ -9955,7 +9974,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="194" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B48" s="193"/>
       <x:c r="C48" s="193"/>
@@ -9999,7 +10018,7 @@
     </x:row>
     <x:row r="50" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A50" s="192" t="s">
-        <x:v>209</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B50" s="193"/>
       <x:c r="C50" s="193"/>
@@ -10013,10 +10032,10 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B51" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C51" s="40" t="s">
         <x:v>14</x:v>
@@ -10031,7 +10050,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G51" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H51" s="40" t="s">
         <x:v>6</x:v>
@@ -10045,13 +10064,13 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="42" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B52" s="38" t="s">
-        <x:v>207</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C52" s="38" t="s">
-        <x:v>210</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D52" s="49">
         <x:v>4</x:v>
@@ -10078,10 +10097,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B53" s="42" t="s">
-        <x:v>211</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C53" s="43" t="s">
-        <x:v>212</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D53" s="42">
         <x:v>6</x:v>
@@ -10105,13 +10124,13 @@
     </x:row>
     <x:row r="54" ht="17.25">
       <x:c r="A54" s="41" t="s">
-        <x:v>113</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B54" s="42" t="s">
-        <x:v>213</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C54" s="43" t="s">
-        <x:v>214</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D54" s="42">
         <x:v>1</x:v>
@@ -10135,13 +10154,13 @@
     </x:row>
     <x:row r="55" ht="17.25">
       <x:c r="A55" s="42" t="s">
-        <x:v>142</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="41" t="s">
-        <x:v>215</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C55" s="43" t="s">
-        <x:v>216</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D55" s="42">
         <x:v>3</x:v>
@@ -10168,10 +10187,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B56" s="42" t="s">
-        <x:v>217</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C56" s="43" t="s">
-        <x:v>218</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D56" s="42">
         <x:v>2</x:v>
@@ -10195,13 +10214,13 @@
     </x:row>
     <x:row r="57" ht="17.25">
       <x:c r="A57" s="41" t="s">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B57" s="41" t="s">
-        <x:v>219</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C57" s="43" t="s">
-        <x:v>220</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D57" s="42">
         <x:v>4</x:v>
@@ -10225,13 +10244,13 @@
     </x:row>
     <x:row r="58" ht="17.25">
       <x:c r="A58" s="42" t="s">
-        <x:v>105</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B58" s="41" t="s">
-        <x:v>221</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C58" s="43" t="s">
-        <x:v>222</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D58" s="42">
         <x:v>7</x:v>
@@ -10255,13 +10274,13 @@
     </x:row>
     <x:row r="59" ht="17.25">
       <x:c r="A59" s="42" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B59" s="42" t="s">
-        <x:v>197</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C59" s="43" t="s">
-        <x:v>223</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D59" s="42">
         <x:v>4</x:v>
@@ -10285,13 +10304,13 @@
     </x:row>
     <x:row r="60" ht="17.25">
       <x:c r="A60" s="41" t="s">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B60" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C60" s="43" t="s">
-        <x:v>225</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D60" s="42">
         <x:v>6</x:v>
@@ -10315,13 +10334,13 @@
     </x:row>
     <x:row r="61" ht="17.25">
       <x:c r="A61" s="41" t="s">
-        <x:v>107</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B61" s="41" t="s">
-        <x:v>226</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C61" s="43" t="s">
-        <x:v>227</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D61" s="42">
         <x:v>2</x:v>
@@ -10348,10 +10367,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="42" t="s">
-        <x:v>228</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C62" s="43" t="s">
-        <x:v>229</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D62" s="42">
         <x:v>3</x:v>
@@ -10437,7 +10456,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="194" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B65" s="193"/>
       <x:c r="C65" s="193"/>
@@ -10481,7 +10500,7 @@
     </x:row>
     <x:row r="67" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A67" s="192" t="s">
-        <x:v>230</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B67" s="193"/>
       <x:c r="C67" s="193"/>
@@ -10495,10 +10514,10 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="40" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B68" s="40" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C68" s="40" t="s">
         <x:v>14</x:v>
@@ -10513,7 +10532,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G68" s="40" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H68" s="40" t="s">
         <x:v>6</x:v>
@@ -10539,13 +10558,13 @@
     </x:row>
     <x:row r="70" ht="17.25">
       <x:c r="A70" s="41" t="s">
-        <x:v>107</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="42" t="s">
-        <x:v>197</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C70" s="43" t="s">
-        <x:v>231</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D70" s="42">
         <x:v>4</x:v>
@@ -10569,13 +10588,13 @@
     </x:row>
     <x:row r="71" ht="17.25">
       <x:c r="A71" s="41" t="s">
-        <x:v>232</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B71" s="41" t="s">
-        <x:v>233</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C71" s="43" t="s">
-        <x:v>234</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D71" s="42">
         <x:v>1</x:v>
@@ -10602,10 +10621,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B72" s="51" t="s">
-        <x:v>235</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C72" s="51" t="s">
-        <x:v>133</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D72" s="52">
         <x:v>1</x:v>
@@ -10629,13 +10648,13 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="48" t="s">
-        <x:v>135</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B73" s="48" t="s">
-        <x:v>236</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C73" s="48" t="s">
-        <x:v>134</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D73" s="53">
         <x:v>3</x:v>
@@ -10691,7 +10710,7 @@
     </x:row>
     <x:row r="75" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A75" s="56" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B75" s="48"/>
       <x:c r="C75" s="48"/>
@@ -10723,7 +10742,7 @@
     </x:row>
     <x:row r="76" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A76" s="198" t="s">
-        <x:v>237</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B76" s="193"/>
       <x:c r="C76" s="193"/>
@@ -10737,10 +10756,10 @@
     </x:row>
     <x:row r="77" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A77" s="57" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B77" s="58" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C77" s="58" t="s">
         <x:v>14</x:v>
@@ -10755,7 +10774,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G77" s="59" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H77" s="59" t="s">
         <x:v>6</x:v>
@@ -10772,10 +10791,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B78" s="38" t="s">
-        <x:v>184</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C78" s="38" t="s">
-        <x:v>238</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D78" s="50">
         <x:v>4</x:v>
@@ -10799,13 +10818,13 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="42" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="38" t="s">
-        <x:v>180</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C79" s="38" t="s">
-        <x:v>91</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D79" s="50">
         <x:v>2</x:v>
@@ -10832,10 +10851,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B80" s="41" t="s">
-        <x:v>239</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C80" s="43" t="s">
-        <x:v>240</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D80" s="42">
         <x:v>3</x:v>
@@ -10862,10 +10881,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="41" t="s">
-        <x:v>241</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C81" s="43" t="s">
-        <x:v>242</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D81" s="42">
         <x:v>5</x:v>
@@ -10892,10 +10911,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B82" s="41" t="s">
-        <x:v>243</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C82" s="43" t="s">
-        <x:v>244</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D82" s="42">
         <x:v>3</x:v>
@@ -10934,10 +10953,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B84" s="41" t="s">
-        <x:v>245</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C84" s="43" t="s">
-        <x:v>246</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D84" s="42">
         <x:v>3</x:v>
@@ -11005,7 +11024,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="48" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B87" s="48"/>
       <x:c r="C87" s="48"/>
@@ -11049,7 +11068,7 @@
     </x:row>
     <x:row r="89" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A89" s="198" t="s">
-        <x:v>247</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B89" s="193"/>
       <x:c r="C89" s="193"/>
@@ -11063,10 +11082,10 @@
     </x:row>
     <x:row r="90" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A90" s="59" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B90" s="58" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C90" s="58" t="s">
         <x:v>14</x:v>
@@ -11081,7 +11100,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G90" s="59" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H90" s="59" t="s">
         <x:v>6</x:v>
@@ -11098,10 +11117,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B91" s="38" t="s">
-        <x:v>248</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C91" s="38" t="s">
-        <x:v>249</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D91" s="65">
         <x:v>6</x:v>
@@ -11122,18 +11141,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J91" s="44" t="s">
-        <x:v>250</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="42" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B92" s="38" t="s">
-        <x:v>251</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C92" s="38" t="s">
-        <x:v>252</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D92" s="50">
         <x:v>4</x:v>
@@ -11157,13 +11176,13 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="42" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B93" s="41" t="s">
-        <x:v>253</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C93" s="43" t="s">
-        <x:v>254</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D93" s="42">
         <x:v>4</x:v>
@@ -11187,13 +11206,13 @@
     </x:row>
     <x:row r="94" s="14" customFormat="1" ht="21.200000762939453" customHeight="1">
       <x:c r="A94" s="42" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B94" s="41" t="s">
-        <x:v>255</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C94" s="43" t="s">
-        <x:v>130</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D94" s="42">
         <x:v>5</x:v>
@@ -11214,7 +11233,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J94" s="68" t="s">
-        <x:v>256</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="17.25">
@@ -11222,7 +11241,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B95" s="41" t="s">
-        <x:v>248</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C95" s="43" t="s">
         <x:v>54</x:v>
@@ -11246,18 +11265,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J95" s="44" t="s">
-        <x:v>257</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="41" t="s">
-        <x:v>129</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B96" s="42" t="s">
-        <x:v>199</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C96" s="43" t="s">
-        <x:v>258</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D96" s="42">
         <x:v>4</x:v>
@@ -11281,13 +11300,13 @@
     </x:row>
     <x:row r="97" ht="17.25">
       <x:c r="A97" s="41" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B97" s="41" t="s">
-        <x:v>259</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C97" s="43" t="s">
-        <x:v>64</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D97" s="42">
         <x:v>5</x:v>
@@ -11308,18 +11327,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J97" s="44" t="s">
-        <x:v>257</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="17.25">
       <x:c r="A98" s="42" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B98" s="41" t="s">
-        <x:v>260</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C98" s="43" t="s">
-        <x:v>261</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D98" s="42">
         <x:v>1</x:v>
@@ -11343,13 +11362,13 @@
     </x:row>
     <x:row r="99" s="14" customFormat="1" ht="31.700000762939453" customHeight="1">
       <x:c r="A99" s="60" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B99" s="48" t="s">
-        <x:v>262</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C99" s="48" t="s">
-        <x:v>132</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D99" s="53">
         <x:v>3</x:v>
@@ -11373,13 +11392,13 @@
     </x:row>
     <x:row r="100" ht="18">
       <x:c r="A100" s="60" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B100" s="44" t="s">
-        <x:v>263</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C100" s="44" t="s">
-        <x:v>68</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D100" s="53">
         <x:v>1</x:v>
@@ -11432,12 +11451,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="J101" s="61" t="s">
-        <x:v>264</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A102" s="48" t="s">
-        <x:v>182</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B102" s="48"/>
       <x:c r="C102" s="48"/>
@@ -11481,7 +11500,7 @@
     </x:row>
     <x:row r="104" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A104" s="72" t="s">
-        <x:v>265</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B104" s="44"/>
       <x:c r="C104" s="44"/>
@@ -11495,10 +11514,10 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="59" t="s">
-        <x:v>177</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B105" s="57" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C105" s="57" t="s">
         <x:v>14</x:v>
@@ -11513,7 +11532,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G105" s="59" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H105" s="59" t="s">
         <x:v>6</x:v>
@@ -11527,13 +11546,13 @@
     </x:row>
     <x:row r="106" ht="30">
       <x:c r="A106" s="42" t="s">
-        <x:v>98</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B106" s="41" t="s">
-        <x:v>266</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C106" s="43" t="s">
-        <x:v>97</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D106" s="42">
         <x:v>4</x:v>
@@ -11557,13 +11576,13 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="42" t="s">
-        <x:v>267</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B107" s="41" t="s">
-        <x:v>268</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C107" s="43" t="s">
-        <x:v>95</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D107" s="42">
         <x:v>4</x:v>
@@ -11590,10 +11609,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B108" s="41" t="s">
-        <x:v>269</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C108" s="43" t="s">
-        <x:v>79</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D108" s="42">
         <x:v>3</x:v>
@@ -11617,13 +11636,13 @@
     </x:row>
     <x:row r="109" ht="21">
       <x:c r="A109" s="60" t="s">
-        <x:v>270</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B109" s="44" t="s">
-        <x:v>251</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C109" s="44" t="s">
-        <x:v>66</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D109" s="53">
         <x:v>4</x:v>
@@ -11644,7 +11663,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J109" s="69" t="s">
-        <x:v>257</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="18.75">
@@ -11652,7 +11671,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B110" s="44" t="s">
-        <x:v>271</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C110" s="44" t="s">
         <x:v>55</x:v>
@@ -11682,7 +11701,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="129" t="s">
-        <x:v>272</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C111" s="129" t="s">
         <x:v>57</x:v>
@@ -11709,13 +11728,13 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="173" t="s">
-        <x:v>63</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B112" s="173" t="s">
-        <x:v>248</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C112" s="173" t="s">
-        <x:v>70</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D112" s="174">
         <x:v>8</x:v>
@@ -11742,7 +11761,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B113" s="175" t="s">
-        <x:v>205</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C113" s="175" t="s">
         <x:v>59</x:v>
@@ -11772,10 +11791,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B114" s="176" t="s">
-        <x:v>273</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C114" s="176" t="s">
-        <x:v>80</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="D114" s="178">
         <x:v>2</x:v>
@@ -11831,69 +11850,101 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="str">
-        <x:v>합계</x:v>
-      </x:c>
-      <x:c r="B116"/>
-      <x:c r="C116"/>
+        <x:v>(주)제일타워공영</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>(주)비에스한양</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>평택고덕국제화계획지구 Abc-14BL 공동주택 신축공사</x:v>
+      </x:c>
       <x:c r="D116" s="536" t="n">
-        <x:f>SUM(D106:D115)</x:f>
-        <x:v>39</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E116" s="536" t="n">
-        <x:f>SUM(E106:E115)</x:f>
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F116" s="536" t="n">
-        <x:f>SUM(F106:F115)</x:f>
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G116" s="536" t="n">
-        <x:f>SUM(G106:G115)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H116" s="536" t="n">
-        <x:f>SUM(H106:H115)</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I116" s="536" t="n">
-        <x:f>SUM(I106:I115)</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J116" t="str">
-        <x:v>※ 미정 4대 아직 미반영 (인력 확정 시 비율 변동)</x:v>
+        <x:v>2026-10-19 입사 / 평택시 소재 / 남부지부 통계</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" t="str">
-        <x:v>비율 (총대수=100%)</x:v>
+        <x:v>합계</x:v>
       </x:c>
       <x:c r="B117"/>
       <x:c r="C117"/>
-      <x:c r="D117" s="95" t="n">
-        <x:f>IF($D$116=0,0,D116/$D$116)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E117" s="95" t="n">
-        <x:f>IF($D$116=0,0,E116/$D$116)</x:f>
-        <x:v>0.3076923076923077</x:v>
-      </x:c>
-      <x:c r="F117" s="95" t="n">
-        <x:f>IF($D$116=0,0,F116/$D$116)</x:f>
-        <x:v>0.46153846153846156</x:v>
-      </x:c>
-      <x:c r="G117" s="95" t="n">
-        <x:f>IF($D$116=0,0,G116/$D$116)</x:f>
-        <x:v>0.05128205128205128</x:v>
-      </x:c>
-      <x:c r="H117" s="95" t="n">
-        <x:f>IF($D$116=0,0,H116/$D$116)</x:f>
-        <x:v>0.07692307692307693</x:v>
-      </x:c>
-      <x:c r="I117" s="95" t="n">
-        <x:f>IF($D$116=0,0,I116/$D$116)</x:f>
-        <x:v>0.10256410256410256</x:v>
-      </x:c>
-      <x:c r="J117"/>
+      <x:c r="D117" s="536" t="n">
+        <x:f>SUM(D106:D116)</x:f>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E117" s="536" t="n">
+        <x:f>SUM(E106:E116)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F117" s="536" t="n">
+        <x:f>SUM(F106:F116)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G117" s="536" t="n">
+        <x:f>SUM(G106:G116)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H117" s="536" t="n">
+        <x:f>SUM(H106:H116)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I117" s="536" t="n">
+        <x:f>SUM(I106:I116)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>※ 미정 4대 (인력 확정 전), 다른 월 기록 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>비율 (총대수=100%)</x:v>
+      </x:c>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118" s="95" t="n">
+        <x:f>IF($D$117=0,0,D117/$D$117)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E118" s="95" t="n">
+        <x:f>IF($D$117=0,0,E117/$D$117)</x:f>
+        <x:v>0.3023255813953488</x:v>
+      </x:c>
+      <x:c r="F118" s="95" t="n">
+        <x:f>IF($D$117=0,0,F117/$D$117)</x:f>
+        <x:v>0.46511627906976744</x:v>
+      </x:c>
+      <x:c r="G118" s="95" t="n">
+        <x:f>IF($D$117=0,0,G117/$D$117)</x:f>
+        <x:v>0.046511627906976744</x:v>
+      </x:c>
+      <x:c r="H118" s="95" t="n">
+        <x:f>IF($D$117=0,0,H117/$D$117)</x:f>
+        <x:v>0.09302325581395349</x:v>
+      </x:c>
+      <x:c r="I118" s="95" t="n">
+        <x:f>IF($D$117=0,0,I117/$D$117)</x:f>
+        <x:v>0.09302325581395349</x:v>
+      </x:c>
+      <x:c r="J118"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13010,6 +13061,6 @@
     <x:mergeCell ref="A50:T50"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d21ef3d2014b63"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R543fe3a1e9d14d29"/>
 </x:worksheet>
 </file>
--- a/채용비율.xlsx
+++ b/채용비율.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="R18e2c7b35ebc4b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="Rced23fef3ee34d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R779f681e3b924cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="Rec1dc501b23d4f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="Rca341112db5746e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R5c9c935ed2524f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="Rfc663a5d642d466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R0edd6f89b1404632"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R12334caa288e4275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="R38b22b69230a4bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="R540df1e068564c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R1502547d0e704be1"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="가평군">#REF!</x:definedName>
@@ -3420,7 +3420,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R542693acb9e64902"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28387466bdaa4d04"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3673,10 +3673,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C3" s="567" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D3" s="567">
-        <x:v>8</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D3" s="567" t="n">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="567">
         <x:v>10</x:v>
@@ -3685,7 +3685,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="G3" s="567" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="567" t="n">
         <x:f>SUM(B3:G3)</x:f>
@@ -3705,11 +3705,11 @@
       </x:c>
       <x:c r="C4" s="32" t="n">
         <x:f>IF($H$3=0,0,C3/$H$3)</x:f>
-        <x:v>0.41338582677165353</x:v>
+        <x:v>0.41732283464566927</x:v>
       </x:c>
       <x:c r="D4" s="32" t="n">
         <x:f>IF($H$3=0,0,D3/$H$3)</x:f>
-        <x:v>0.031496062992125984</x:v>
+        <x:v>0.03543307086614173</x:v>
       </x:c>
       <x:c r="E4" s="32" t="n">
         <x:f>IF($H$3=0,0,E3/$H$3)</x:f>
@@ -3721,7 +3721,7 @@
       </x:c>
       <x:c r="G4" s="32" t="n">
         <x:f>IF($H$3=0,0,G3/$H$3)</x:f>
-        <x:v>0.06692913385826772</x:v>
+        <x:v>0.05905511811023622</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="14" customFormat="1" ht="21.200000762939453" customHeight="1"/>
@@ -5531,10 +5531,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F49" s="537" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G49" s="537" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H49" s="537" t="n">
         <x:v>0</x:v>
@@ -5543,7 +5543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" s="537" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K49" s="548" t="n">
         <x:v>4</x:v>
@@ -5668,11 +5668,11 @@
       </x:c>
       <x:c r="F53" s="542" t="n">
         <x:f>SUM(F43:F52)</x:f>
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G53" s="542" t="n">
         <x:f>SUM(G43:G52)</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H53" s="542" t="n">
         <x:f>SUM(H43:H52)</x:f>
@@ -5684,7 +5684,7 @@
       </x:c>
       <x:c r="J53" s="542" t="n">
         <x:f>SUM(J43:J52)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K53" s="543" t="n">
         <x:f>SUM(K43:K52)</x:f>
@@ -5705,11 +5705,11 @@
       </x:c>
       <x:c r="F54" s="102" t="n">
         <x:f>IF($K$53=0,0,F53/$K$53)</x:f>
-        <x:v>0.42424242424242425</x:v>
+        <x:v>0.45454545454545453</x:v>
       </x:c>
       <x:c r="G54" s="102" t="n">
         <x:f>IF($K$53=0,0,G53/$K$53)</x:f>
-        <x:v>0.030303030303030304</x:v>
+        <x:v>0.06060606060606061</x:v>
       </x:c>
       <x:c r="H54" s="102" t="n">
         <x:f>IF($K$53=0,0,H53/$K$53)</x:f>
@@ -5721,7 +5721,7 @@
       </x:c>
       <x:c r="J54" s="102" t="n">
         <x:f>IF($K$53=0,0,J53/$K$53)</x:f>
-        <x:v>0.06060606060606061</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K54" s="103" t="n">
         <x:f>IF($K$53=0,0,K53/$K$53)</x:f>
@@ -7350,20 +7350,20 @@
       <x:c r="C14" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D14" s="11">
+      <x:c r="D14" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="11">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H14" s="11">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="I14" s="9">
         <x:v>13</x:v>
@@ -13153,6 +13153,6 @@
     <x:mergeCell ref="A50:T50"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R908552091d66411f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36959f28259d4d9c"/>
 </x:worksheet>
 </file>
--- a/채용비율.xlsx
+++ b/채용비율.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="Rfc663a5d642d466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R0edd6f89b1404632"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R12334caa288e4275"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="R38b22b69230a4bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="R540df1e068564c24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R1502547d0e704be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="R3e1053f457d943fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R3df2097710f24f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R0e3bd4c6d0c840d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="Rab0994875a9b4b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="Rc725e3da583e4bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R3c5b08d230cb40d0"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="가평군">#REF!</x:definedName>
@@ -408,9 +408,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">삼성p5 그린동</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">합 계</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">1월 채용 현황</x:t>
@@ -3420,7 +3417,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28387466bdaa4d04"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf9e9f69380ed4c77"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8427,25 +8424,25 @@
     <x:row r="6">
       <x:c r="A6" s="16" t="n">
         <x:f t="shared" ref="A6:F6" si="0">SUM(C11:C20)</x:f>
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B6" s="16">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="n">
         <x:f t="shared" si="0"/>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C6" s="16">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="n">
         <x:f t="shared" si="0"/>
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D6" s="16">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="n">
         <x:f t="shared" si="0"/>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E6" s="16">
+      <x:c r="E6" s="16" t="n">
         <x:f t="shared" si="0"/>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F6" s="16">
+      <x:c r="F6" s="16" t="n">
         <x:f t="shared" si="0"/>
         <x:v>13</x:v>
       </x:c>
@@ -8455,24 +8452,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="35" t="n">
-        <x:f>B6/A6</x:f>
-        <x:v>0.36153846153846153</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="C7" s="35" t="n">
-        <x:f>C6/A6</x:f>
-        <x:v>0.4307692307692308</x:v>
+        <x:v>0.4318181818181818</x:v>
       </x:c>
       <x:c r="D7" s="35" t="n">
-        <x:f>D6/A6</x:f>
-        <x:v>0.015384615384615385</x:v>
+        <x:v>0.015151515151515152</x:v>
       </x:c>
       <x:c r="E7" s="35" t="n">
-        <x:f>E6/A6</x:f>
-        <x:v>0.09230769230769231</x:v>
+        <x:v>0.09090909090909091</x:v>
       </x:c>
       <x:c r="F7" s="35" t="n">
-        <x:f>F6/A6</x:f>
-        <x:v>0.1</x:v>
+        <x:v>0.09848484848484848</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
@@ -8808,37 +8800,65 @@
       </x:c>
     </x:row>
     <x:row r="21" s="14" customFormat="1" ht="14.449999809265137" customHeight="1">
-      <x:c r="A21" s="29"/>
-      <x:c r="B21" s="30" t="s">
-        <x:v>120</x:v>
+      <x:c r="A21" s="29" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B21" s="30" t="str">
+        <x:v>기흥 NRD-K2 복합동 신축공사</x:v>
       </x:c>
       <x:c r="C21" s="31" t="n">
         <x:f t="shared" ref="C21:H21" si="1">SUM(C11:C20)</x:f>
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D21" s="31">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E21" s="31">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="31" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F21" s="31">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="31" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G21" s="31">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="31" t="n">
         <x:f t="shared" si="1"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="n">
+        <x:f t="shared" si="1"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="29" t="str">
+        <x:v>신규 현장 · 신우개발(주) / 삼성이앤에이(주)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" s="14" customFormat="1" ht="14.449999809265137" customHeight="1">
+      <x:c r="A22"/>
+      <x:c r="B22" t="str">
+        <x:v>합 계</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H21" s="31">
-        <x:f t="shared" si="1"/>
+      <x:c r="H22" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="I21" s="29"/>
-    </x:row>
-    <x:row r="22" s="14" customFormat="1" ht="14.449999809265137" customHeight="1"/>
+      <x:c r="I22"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
@@ -8866,7 +8886,7 @@
   <x:sheetData>
     <x:row r="1" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A1" s="192" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B1" s="193"/>
       <x:c r="C1" s="193"/>
@@ -8880,10 +8900,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B2" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C2" s="40" t="s">
         <x:v>14</x:v>
@@ -8898,7 +8918,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G2" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H2" s="40" t="s">
         <x:v>6</x:v>
@@ -8927,10 +8947,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="41" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C4" s="43" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="C4" s="43" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="D4" s="42">
         <x:v>5</x:v>
@@ -9022,7 +9042,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="194" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B9" s="193"/>
       <x:c r="C9" s="193"/>
@@ -9066,7 +9086,7 @@
     </x:row>
     <x:row r="11" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A11" s="192" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B11" s="193"/>
       <x:c r="C11" s="193"/>
@@ -9080,10 +9100,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B12" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C12" s="40" t="s">
         <x:v>14</x:v>
@@ -9098,7 +9118,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G12" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H12" s="40" t="s">
         <x:v>6</x:v>
@@ -9115,10 +9135,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="41" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C13" s="43" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="C13" s="43" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="D13" s="42">
         <x:v>4</x:v>
@@ -9145,10 +9165,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="42" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="C14" s="43" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="D14" s="42">
         <x:v>8</x:v>
@@ -9234,7 +9254,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="194" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B17" s="193"/>
       <x:c r="C17" s="193"/>
@@ -9278,7 +9298,7 @@
     </x:row>
     <x:row r="19" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A19" s="192" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B19" s="193"/>
       <x:c r="C19" s="193"/>
@@ -9292,10 +9312,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B20" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B20" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C20" s="40" t="s">
         <x:v>14</x:v>
@@ -9310,7 +9330,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G20" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H20" s="40" t="s">
         <x:v>6</x:v>
@@ -9351,10 +9371,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="41" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C23" s="43" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="C23" s="43" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="D23" s="42">
         <x:v>7</x:v>
@@ -9381,10 +9401,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="41" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C24" s="43" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="C24" s="43" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="D24" s="42">
         <x:v>3</x:v>
@@ -9411,10 +9431,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="41" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C25" s="43" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="C25" s="43" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="D25" s="42">
         <x:v>4</x:v>
@@ -9441,10 +9461,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="41" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C26" s="43" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="C26" s="43" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="D26" s="42">
         <x:v>2</x:v>
@@ -9500,7 +9520,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="194" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B28" s="193"/>
       <x:c r="C28" s="193"/>
@@ -9544,7 +9564,7 @@
     </x:row>
     <x:row r="30" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A30" s="192" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B30" s="193"/>
       <x:c r="C30" s="193"/>
@@ -9558,10 +9578,10 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B31" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B31" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C31" s="40" t="s">
         <x:v>14</x:v>
@@ -9576,7 +9596,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H31" s="40" t="s">
         <x:v>6</x:v>
@@ -9623,10 +9643,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C33" s="43" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="C33" s="43" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="D33" s="42">
         <x:v>5</x:v>
@@ -9665,10 +9685,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B35" s="41" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C35" s="43" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="C35" s="43" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="D35" s="42">
         <x:v>2</x:v>
@@ -9695,10 +9715,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B36" s="41" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C36" s="43" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D36" s="42">
         <x:v>2</x:v>
@@ -9725,10 +9745,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B37" s="42" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C37" s="43" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D37" s="42">
         <x:v>4</x:v>
@@ -9784,7 +9804,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="194" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B39" s="193"/>
       <x:c r="C39" s="193"/>
@@ -9828,7 +9848,7 @@
     </x:row>
     <x:row r="41" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A41" s="192" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B41" s="193"/>
       <x:c r="C41" s="193"/>
@@ -9842,10 +9862,10 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B42" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B42" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C42" s="40" t="s">
         <x:v>14</x:v>
@@ -9860,7 +9880,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G42" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H42" s="40" t="s">
         <x:v>6</x:v>
@@ -9877,10 +9897,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B43" s="38" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C43" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D43" s="49">
         <x:v>4</x:v>
@@ -9907,10 +9927,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B44" s="41" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C44" s="43" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="C44" s="43" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="D44" s="42">
         <x:v>4</x:v>
@@ -9967,10 +9987,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B46" s="41" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C46" s="43" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="C46" s="43" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="D46" s="42">
         <x:v>5</x:v>
@@ -10026,7 +10046,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="194" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B48" s="193"/>
       <x:c r="C48" s="193"/>
@@ -10070,7 +10090,7 @@
     </x:row>
     <x:row r="50" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A50" s="192" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B50" s="193"/>
       <x:c r="C50" s="193"/>
@@ -10084,10 +10104,10 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B51" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B51" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C51" s="40" t="s">
         <x:v>14</x:v>
@@ -10102,7 +10122,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G51" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H51" s="40" t="s">
         <x:v>6</x:v>
@@ -10119,10 +10139,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B52" s="38" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C52" s="38" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D52" s="49">
         <x:v>4</x:v>
@@ -10149,10 +10169,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B53" s="42" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C53" s="43" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="C53" s="43" t="s">
-        <x:v>158</x:v>
       </x:c>
       <x:c r="D53" s="42">
         <x:v>6</x:v>
@@ -10179,10 +10199,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B54" s="42" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C54" s="43" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="C54" s="43" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="D54" s="42">
         <x:v>1</x:v>
@@ -10209,10 +10229,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="41" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C55" s="43" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C55" s="43" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="D55" s="42">
         <x:v>3</x:v>
@@ -10239,10 +10259,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B56" s="42" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C56" s="43" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="C56" s="43" t="s">
-        <x:v>164</x:v>
       </x:c>
       <x:c r="D56" s="42">
         <x:v>2</x:v>
@@ -10269,10 +10289,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B57" s="41" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C57" s="43" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="C57" s="43" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="D57" s="42">
         <x:v>4</x:v>
@@ -10299,10 +10319,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B58" s="41" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C58" s="43" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="C58" s="43" t="s">
-        <x:v>168</x:v>
       </x:c>
       <x:c r="D58" s="42">
         <x:v>7</x:v>
@@ -10329,10 +10349,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B59" s="42" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C59" s="43" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D59" s="42">
         <x:v>4</x:v>
@@ -10359,10 +10379,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B60" s="42" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C60" s="43" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="C60" s="43" t="s">
-        <x:v>171</x:v>
       </x:c>
       <x:c r="D60" s="42">
         <x:v>6</x:v>
@@ -10389,10 +10409,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B61" s="41" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C61" s="43" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="C61" s="43" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="D61" s="42">
         <x:v>2</x:v>
@@ -10419,10 +10439,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="42" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C62" s="43" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="C62" s="43" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="D62" s="42">
         <x:v>3</x:v>
@@ -10508,7 +10528,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="194" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B65" s="193"/>
       <x:c r="C65" s="193"/>
@@ -10552,7 +10572,7 @@
     </x:row>
     <x:row r="67" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A67" s="192" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B67" s="193"/>
       <x:c r="C67" s="193"/>
@@ -10566,10 +10586,10 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="40" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B68" s="40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B68" s="40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C68" s="40" t="s">
         <x:v>14</x:v>
@@ -10584,7 +10604,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G68" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H68" s="40" t="s">
         <x:v>6</x:v>
@@ -10613,10 +10633,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="42" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C70" s="43" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D70" s="42">
         <x:v>4</x:v>
@@ -10640,13 +10660,13 @@
     </x:row>
     <x:row r="71" ht="17.25">
       <x:c r="A71" s="41" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B71" s="41" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="B71" s="41" t="s">
+      <x:c r="C71" s="43" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="C71" s="43" t="s">
-        <x:v>180</x:v>
       </x:c>
       <x:c r="D71" s="42">
         <x:v>1</x:v>
@@ -10673,10 +10693,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B72" s="51" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C72" s="51" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="C72" s="51" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="D72" s="52">
         <x:v>1</x:v>
@@ -10703,10 +10723,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B73" s="48" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C73" s="48" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="C73" s="48" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="D73" s="53">
         <x:v>3</x:v>
@@ -10762,7 +10782,7 @@
     </x:row>
     <x:row r="75" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A75" s="56" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B75" s="48"/>
       <x:c r="C75" s="48"/>
@@ -10794,7 +10814,7 @@
     </x:row>
     <x:row r="76" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A76" s="198" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B76" s="193"/>
       <x:c r="C76" s="193"/>
@@ -10808,10 +10828,10 @@
     </x:row>
     <x:row r="77" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A77" s="57" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B77" s="58" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B77" s="58" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C77" s="58" t="s">
         <x:v>14</x:v>
@@ -10826,7 +10846,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G77" s="59" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H77" s="59" t="s">
         <x:v>6</x:v>
@@ -10843,10 +10863,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B78" s="38" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C78" s="38" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D78" s="50">
         <x:v>4</x:v>
@@ -10873,10 +10893,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="38" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C79" s="38" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D79" s="50">
         <x:v>2</x:v>
@@ -10903,10 +10923,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B80" s="41" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C80" s="43" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="C80" s="43" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="D80" s="42">
         <x:v>3</x:v>
@@ -10933,10 +10953,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="41" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C81" s="43" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="C81" s="43" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="D81" s="42">
         <x:v>5</x:v>
@@ -10963,10 +10983,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B82" s="41" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C82" s="43" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="C82" s="43" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="D82" s="42">
         <x:v>3</x:v>
@@ -11005,10 +11025,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B84" s="41" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C84" s="43" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="C84" s="43" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="D84" s="42">
         <x:v>3</x:v>
@@ -11076,7 +11096,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="48" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B87" s="48"/>
       <x:c r="C87" s="48"/>
@@ -11120,7 +11140,7 @@
     </x:row>
     <x:row r="89" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A89" s="198" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B89" s="193"/>
       <x:c r="C89" s="193"/>
@@ -11134,10 +11154,10 @@
     </x:row>
     <x:row r="90" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A90" s="59" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B90" s="58" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B90" s="58" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C90" s="58" t="s">
         <x:v>14</x:v>
@@ -11152,7 +11172,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G90" s="59" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H90" s="59" t="s">
         <x:v>6</x:v>
@@ -11169,10 +11189,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B91" s="38" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C91" s="38" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="C91" s="38" t="s">
-        <x:v>198</x:v>
       </x:c>
       <x:c r="D91" s="65">
         <x:v>6</x:v>
@@ -11193,7 +11213,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J91" s="44" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -11201,10 +11221,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B92" s="38" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C92" s="38" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="C92" s="38" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="D92" s="50">
         <x:v>4</x:v>
@@ -11231,10 +11251,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B93" s="41" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C93" s="43" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="C93" s="43" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="D93" s="42">
         <x:v>4</x:v>
@@ -11261,10 +11281,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B94" s="41" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C94" s="43" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="C94" s="43" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="D94" s="42">
         <x:v>5</x:v>
@@ -11285,7 +11305,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J94" s="68" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="17.25">
@@ -11293,7 +11313,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B95" s="41" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C95" s="43" t="s">
         <x:v>54</x:v>
@@ -11317,7 +11337,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J95" s="44" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -11325,10 +11345,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B96" s="42" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C96" s="43" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D96" s="42">
         <x:v>4</x:v>
@@ -11355,10 +11375,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B97" s="41" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="C97" s="43" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="C97" s="43" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="D97" s="42">
         <x:v>5</x:v>
@@ -11379,7 +11399,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J97" s="44" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="17.25">
@@ -11387,10 +11407,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B98" s="41" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C98" s="43" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="C98" s="43" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="D98" s="42">
         <x:v>1</x:v>
@@ -11417,10 +11437,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B99" s="48" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C99" s="48" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="C99" s="48" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="D99" s="53">
         <x:v>3</x:v>
@@ -11447,10 +11467,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B100" s="44" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C100" s="44" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="C100" s="44" t="s">
-        <x:v>216</x:v>
       </x:c>
       <x:c r="D100" s="53">
         <x:v>1</x:v>
@@ -11503,12 +11523,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="J101" s="61" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A102" s="48" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B102" s="48"/>
       <x:c r="C102" s="48"/>
@@ -11552,7 +11572,7 @@
     </x:row>
     <x:row r="104" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A104" s="72" t="s">
-        <x:v>218</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B104" s="44"/>
       <x:c r="C104" s="44"/>
@@ -11566,10 +11586,10 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="59" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B105" s="57" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B105" s="57" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C105" s="57" t="s">
         <x:v>14</x:v>
@@ -11584,7 +11604,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G105" s="59" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H105" s="59" t="s">
         <x:v>6</x:v>
@@ -11601,10 +11621,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B106" s="41" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C106" s="43" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="C106" s="43" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="D106" s="42">
         <x:v>4</x:v>
@@ -11628,13 +11648,13 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="42" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B107" s="41" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="B107" s="41" t="s">
+      <x:c r="C107" s="43" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="C107" s="43" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="D107" s="42">
         <x:v>4</x:v>
@@ -11661,10 +11681,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B108" s="41" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C108" s="43" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="C108" s="43" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="D108" s="42">
         <x:v>3</x:v>
@@ -11688,13 +11708,13 @@
     </x:row>
     <x:row r="109" ht="21">
       <x:c r="A109" s="60" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B109" s="44" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C109" s="44" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B109" s="44" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="C109" s="44" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="D109" s="53">
         <x:v>4</x:v>
@@ -11715,7 +11735,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J109" s="69" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="18.75">
@@ -11723,7 +11743,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B110" s="44" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C110" s="44" t="s">
         <x:v>55</x:v>
@@ -11753,7 +11773,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="129" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C111" s="129" t="s">
         <x:v>57</x:v>
@@ -11783,10 +11803,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B112" s="173" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C112" s="173" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D112" s="174">
         <x:v>8</x:v>
@@ -11813,7 +11833,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B113" s="175" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C113" s="175" t="s">
         <x:v>59</x:v>
@@ -11843,10 +11863,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B114" s="176" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C114" s="176" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="C114" s="176" t="s">
-        <x:v>232</x:v>
       </x:c>
       <x:c r="D114" s="178">
         <x:v>2</x:v>
@@ -13153,6 +13173,6 @@
     <x:mergeCell ref="A50:T50"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36959f28259d4d9c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4bed8e122bc4f5c"/>
 </x:worksheet>
 </file>
--- a/채용비율.xlsx
+++ b/채용비율.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="R3e1053f457d943fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R3df2097710f24f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R0e3bd4c6d0c840d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="Rab0994875a9b4b60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="Rc725e3da583e4bda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R3c5b08d230cb40d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="Rf9a42abcac194542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R575daa7d0bb2459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R51d5626cf6584477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="R375fd11df0e240ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="Ra1f275c8a34d4eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R118a5c739999476d"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="가평군">#REF!</x:definedName>
@@ -381,9 +381,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">p4 복합동(배정완료)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">기흥 NRD K2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">민주식 010-4870-9982</x:t>
@@ -3417,7 +3414,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf9e9f69380ed4c77"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0991f3956ad24826"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8424,15 +8421,15 @@
     <x:row r="6">
       <x:c r="A6" s="16" t="n">
         <x:f t="shared" ref="A6:F6" si="0">SUM(C11:C20)</x:f>
-        <x:v>132</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f t="shared" si="0"/>
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C6" s="16" t="n">
         <x:f t="shared" si="0"/>
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="16" t="n">
         <x:f t="shared" si="0"/>
@@ -8444,7 +8441,7 @@
       </x:c>
       <x:c r="F6" s="16" t="n">
         <x:f t="shared" si="0"/>
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -8452,19 +8449,19 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="35" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0.35507246376811596</x:v>
       </x:c>
       <x:c r="C7" s="35" t="n">
-        <x:v>0.4318181818181818</x:v>
+        <x:v>0.427536231884058</x:v>
       </x:c>
       <x:c r="D7" s="35" t="n">
-        <x:v>0.015151515151515152</x:v>
+        <x:v>0.014492753623188406</x:v>
       </x:c>
       <x:c r="E7" s="35" t="n">
-        <x:v>0.09090909090909091</x:v>
+        <x:v>0.08695652173913043</x:v>
       </x:c>
       <x:c r="F7" s="35" t="n">
-        <x:v>0.09848484848484848</x:v>
+        <x:v>0.11594202898550725</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
@@ -8658,29 +8655,29 @@
       <x:c r="A16" s="24">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B16" s="25" t="s">
+      <x:c r="B16" s="25" t="str">
+        <x:v>기흥 NRD FAB동</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="28" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="C16" s="26">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="27">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E16" s="27">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="27">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="27">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="27">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="28" t="s">
-        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -8688,7 +8685,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="20" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C17" s="21">
         <x:v>15</x:v>
@@ -8709,7 +8706,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="23" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8717,7 +8714,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="25" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C18" s="26">
         <x:v>5</x:v>
@@ -8738,7 +8735,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="28" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8746,28 +8743,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B19" s="20" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C19" s="21">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D19" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="23" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="C19" s="21">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="22">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="22">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" s="22">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="22">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="22">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="23" t="s">
-        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="14" customFormat="1" ht="14.449999809265137" customHeight="1">
@@ -8775,7 +8772,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="25" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C20" s="26">
         <x:v>6</x:v>
@@ -8808,7 +8805,7 @@
       </x:c>
       <x:c r="C21" s="31" t="n">
         <x:f t="shared" ref="C21:H21" si="1">SUM(C11:C20)</x:f>
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D21" s="31" t="n">
         <x:f t="shared" si="1"/>
@@ -8816,7 +8813,7 @@
       </x:c>
       <x:c r="E21" s="31" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="31" t="n">
         <x:f t="shared" si="1"/>
@@ -8828,7 +8825,7 @@
       </x:c>
       <x:c r="H21" s="31" t="n">
         <x:f t="shared" si="1"/>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I21" s="29" t="str">
         <x:v>신규 현장 · 신우개발(주) / 삼성이앤에이(주)</x:v>
@@ -8840,13 +8837,13 @@
         <x:v>합 계</x:v>
       </x:c>
       <x:c r="C22" t="n">
-        <x:v>132</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D22" t="n">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E22" t="n">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F22" t="n">
         <x:v>2</x:v>
@@ -8855,7 +8852,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H22" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I22"/>
     </x:row>
@@ -8886,7 +8883,7 @@
   <x:sheetData>
     <x:row r="1" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A1" s="192" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B1" s="193"/>
       <x:c r="C1" s="193"/>
@@ -8900,10 +8897,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B2" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C2" s="40" t="s">
         <x:v>14</x:v>
@@ -8918,7 +8915,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G2" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H2" s="40" t="s">
         <x:v>6</x:v>
@@ -8947,10 +8944,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="41" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C4" s="43" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="C4" s="43" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="D4" s="42">
         <x:v>5</x:v>
@@ -9042,7 +9039,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="194" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B9" s="193"/>
       <x:c r="C9" s="193"/>
@@ -9086,7 +9083,7 @@
     </x:row>
     <x:row r="11" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A11" s="192" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B11" s="193"/>
       <x:c r="C11" s="193"/>
@@ -9100,10 +9097,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B12" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C12" s="40" t="s">
         <x:v>14</x:v>
@@ -9118,7 +9115,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G12" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H12" s="40" t="s">
         <x:v>6</x:v>
@@ -9135,10 +9132,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="41" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C13" s="43" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C13" s="43" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="D13" s="42">
         <x:v>4</x:v>
@@ -9165,10 +9162,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="42" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="C14" s="43" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="D14" s="42">
         <x:v>8</x:v>
@@ -9254,7 +9251,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="194" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B17" s="193"/>
       <x:c r="C17" s="193"/>
@@ -9298,7 +9295,7 @@
     </x:row>
     <x:row r="19" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A19" s="192" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B19" s="193"/>
       <x:c r="C19" s="193"/>
@@ -9312,10 +9309,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B20" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B20" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C20" s="40" t="s">
         <x:v>14</x:v>
@@ -9330,7 +9327,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G20" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H20" s="40" t="s">
         <x:v>6</x:v>
@@ -9371,10 +9368,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="41" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C23" s="43" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="C23" s="43" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="D23" s="42">
         <x:v>7</x:v>
@@ -9401,10 +9398,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="41" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C24" s="43" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="C24" s="43" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="D24" s="42">
         <x:v>3</x:v>
@@ -9431,10 +9428,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="41" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C25" s="43" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="C25" s="43" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="D25" s="42">
         <x:v>4</x:v>
@@ -9461,10 +9458,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="41" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C26" s="43" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="C26" s="43" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="D26" s="42">
         <x:v>2</x:v>
@@ -9520,7 +9517,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="194" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B28" s="193"/>
       <x:c r="C28" s="193"/>
@@ -9564,7 +9561,7 @@
     </x:row>
     <x:row r="30" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A30" s="192" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B30" s="193"/>
       <x:c r="C30" s="193"/>
@@ -9578,10 +9575,10 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B31" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B31" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C31" s="40" t="s">
         <x:v>14</x:v>
@@ -9596,7 +9593,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H31" s="40" t="s">
         <x:v>6</x:v>
@@ -9643,10 +9640,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C33" s="43" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="C33" s="43" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="D33" s="42">
         <x:v>5</x:v>
@@ -9685,10 +9682,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B35" s="41" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C35" s="43" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="C35" s="43" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="D35" s="42">
         <x:v>2</x:v>
@@ -9715,10 +9712,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B36" s="41" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C36" s="43" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D36" s="42">
         <x:v>2</x:v>
@@ -9745,10 +9742,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B37" s="42" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C37" s="43" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D37" s="42">
         <x:v>4</x:v>
@@ -9804,7 +9801,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="194" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B39" s="193"/>
       <x:c r="C39" s="193"/>
@@ -9848,7 +9845,7 @@
     </x:row>
     <x:row r="41" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A41" s="192" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B41" s="193"/>
       <x:c r="C41" s="193"/>
@@ -9862,10 +9859,10 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B42" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B42" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C42" s="40" t="s">
         <x:v>14</x:v>
@@ -9880,7 +9877,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G42" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H42" s="40" t="s">
         <x:v>6</x:v>
@@ -9897,10 +9894,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B43" s="38" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C43" s="38" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D43" s="49">
         <x:v>4</x:v>
@@ -9927,10 +9924,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B44" s="41" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C44" s="43" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="C44" s="43" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="D44" s="42">
         <x:v>4</x:v>
@@ -9987,10 +9984,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B46" s="41" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C46" s="43" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="C46" s="43" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="D46" s="42">
         <x:v>5</x:v>
@@ -10046,7 +10043,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="194" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B48" s="193"/>
       <x:c r="C48" s="193"/>
@@ -10090,7 +10087,7 @@
     </x:row>
     <x:row r="50" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A50" s="192" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B50" s="193"/>
       <x:c r="C50" s="193"/>
@@ -10104,10 +10101,10 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B51" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B51" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C51" s="40" t="s">
         <x:v>14</x:v>
@@ -10122,7 +10119,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G51" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H51" s="40" t="s">
         <x:v>6</x:v>
@@ -10139,10 +10136,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B52" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C52" s="38" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D52" s="49">
         <x:v>4</x:v>
@@ -10169,10 +10166,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B53" s="42" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C53" s="43" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="C53" s="43" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="D53" s="42">
         <x:v>6</x:v>
@@ -10199,10 +10196,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B54" s="42" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C54" s="43" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="C54" s="43" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="D54" s="42">
         <x:v>1</x:v>
@@ -10229,10 +10226,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="41" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C55" s="43" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="C55" s="43" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="D55" s="42">
         <x:v>3</x:v>
@@ -10259,10 +10256,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B56" s="42" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C56" s="43" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="C56" s="43" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="D56" s="42">
         <x:v>2</x:v>
@@ -10289,10 +10286,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B57" s="41" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C57" s="43" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="C57" s="43" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="D57" s="42">
         <x:v>4</x:v>
@@ -10319,10 +10316,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B58" s="41" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C58" s="43" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="C58" s="43" t="s">
-        <x:v>167</x:v>
       </x:c>
       <x:c r="D58" s="42">
         <x:v>7</x:v>
@@ -10349,10 +10346,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B59" s="42" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C59" s="43" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D59" s="42">
         <x:v>4</x:v>
@@ -10379,10 +10376,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B60" s="42" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C60" s="43" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="C60" s="43" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="D60" s="42">
         <x:v>6</x:v>
@@ -10409,10 +10406,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B61" s="41" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C61" s="43" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="C61" s="43" t="s">
-        <x:v>172</x:v>
       </x:c>
       <x:c r="D61" s="42">
         <x:v>2</x:v>
@@ -10439,10 +10436,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="42" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C62" s="43" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="C62" s="43" t="s">
-        <x:v>174</x:v>
       </x:c>
       <x:c r="D62" s="42">
         <x:v>3</x:v>
@@ -10528,7 +10525,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="194" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B65" s="193"/>
       <x:c r="C65" s="193"/>
@@ -10572,7 +10569,7 @@
     </x:row>
     <x:row r="67" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A67" s="192" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B67" s="193"/>
       <x:c r="C67" s="193"/>
@@ -10586,10 +10583,10 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B68" s="40" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B68" s="40" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C68" s="40" t="s">
         <x:v>14</x:v>
@@ -10604,7 +10601,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G68" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H68" s="40" t="s">
         <x:v>6</x:v>
@@ -10633,10 +10630,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="42" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C70" s="43" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D70" s="42">
         <x:v>4</x:v>
@@ -10660,13 +10657,13 @@
     </x:row>
     <x:row r="71" ht="17.25">
       <x:c r="A71" s="41" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B71" s="41" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="B71" s="41" t="s">
+      <x:c r="C71" s="43" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="C71" s="43" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="D71" s="42">
         <x:v>1</x:v>
@@ -10693,10 +10690,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B72" s="51" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C72" s="51" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="C72" s="51" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="D72" s="52">
         <x:v>1</x:v>
@@ -10723,10 +10720,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B73" s="48" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C73" s="48" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="C73" s="48" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="D73" s="53">
         <x:v>3</x:v>
@@ -10782,7 +10779,7 @@
     </x:row>
     <x:row r="75" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A75" s="56" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B75" s="48"/>
       <x:c r="C75" s="48"/>
@@ -10814,7 +10811,7 @@
     </x:row>
     <x:row r="76" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A76" s="198" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B76" s="193"/>
       <x:c r="C76" s="193"/>
@@ -10828,10 +10825,10 @@
     </x:row>
     <x:row r="77" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A77" s="57" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B77" s="58" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B77" s="58" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C77" s="58" t="s">
         <x:v>14</x:v>
@@ -10846,7 +10843,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G77" s="59" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H77" s="59" t="s">
         <x:v>6</x:v>
@@ -10863,10 +10860,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B78" s="38" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C78" s="38" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D78" s="50">
         <x:v>4</x:v>
@@ -10893,10 +10890,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="38" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C79" s="38" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D79" s="50">
         <x:v>2</x:v>
@@ -10923,10 +10920,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B80" s="41" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C80" s="43" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="C80" s="43" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="D80" s="42">
         <x:v>3</x:v>
@@ -10953,10 +10950,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="41" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C81" s="43" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="C81" s="43" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="D81" s="42">
         <x:v>5</x:v>
@@ -10983,10 +10980,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B82" s="41" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C82" s="43" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="C82" s="43" t="s">
-        <x:v>192</x:v>
       </x:c>
       <x:c r="D82" s="42">
         <x:v>3</x:v>
@@ -11025,10 +11022,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B84" s="41" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C84" s="43" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="C84" s="43" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="D84" s="42">
         <x:v>3</x:v>
@@ -11096,7 +11093,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="48" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B87" s="48"/>
       <x:c r="C87" s="48"/>
@@ -11140,7 +11137,7 @@
     </x:row>
     <x:row r="89" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A89" s="198" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B89" s="193"/>
       <x:c r="C89" s="193"/>
@@ -11154,10 +11151,10 @@
     </x:row>
     <x:row r="90" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A90" s="59" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B90" s="58" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B90" s="58" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C90" s="58" t="s">
         <x:v>14</x:v>
@@ -11172,7 +11169,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G90" s="59" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H90" s="59" t="s">
         <x:v>6</x:v>
@@ -11189,10 +11186,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B91" s="38" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C91" s="38" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="C91" s="38" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="D91" s="65">
         <x:v>6</x:v>
@@ -11213,7 +11210,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J91" s="44" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -11221,10 +11218,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B92" s="38" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C92" s="38" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="C92" s="38" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="D92" s="50">
         <x:v>4</x:v>
@@ -11251,10 +11248,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B93" s="41" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C93" s="43" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="C93" s="43" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="D93" s="42">
         <x:v>4</x:v>
@@ -11281,10 +11278,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B94" s="41" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C94" s="43" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="C94" s="43" t="s">
-        <x:v>204</x:v>
       </x:c>
       <x:c r="D94" s="42">
         <x:v>5</x:v>
@@ -11305,7 +11302,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J94" s="68" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="17.25">
@@ -11313,7 +11310,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B95" s="41" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C95" s="43" t="s">
         <x:v>54</x:v>
@@ -11337,7 +11334,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J95" s="44" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -11345,10 +11342,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B96" s="42" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C96" s="43" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D96" s="42">
         <x:v>4</x:v>
@@ -11375,10 +11372,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B97" s="41" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C97" s="43" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="C97" s="43" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="D97" s="42">
         <x:v>5</x:v>
@@ -11399,7 +11396,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J97" s="44" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="17.25">
@@ -11407,10 +11404,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B98" s="41" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C98" s="43" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="C98" s="43" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="D98" s="42">
         <x:v>1</x:v>
@@ -11437,10 +11434,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B99" s="48" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C99" s="48" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="C99" s="48" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="D99" s="53">
         <x:v>3</x:v>
@@ -11467,10 +11464,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B100" s="44" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C100" s="44" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="C100" s="44" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="D100" s="53">
         <x:v>1</x:v>
@@ -11523,12 +11520,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="J101" s="61" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="14" customFormat="1" ht="15.399999618530273" customHeight="1">
       <x:c r="A102" s="48" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B102" s="48"/>
       <x:c r="C102" s="48"/>
@@ -11572,7 +11569,7 @@
     </x:row>
     <x:row r="104" s="14" customFormat="1" ht="19.149999618530273" customHeight="1">
       <x:c r="A104" s="72" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B104" s="44"/>
       <x:c r="C104" s="44"/>
@@ -11586,10 +11583,10 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="59" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B105" s="57" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B105" s="57" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C105" s="57" t="s">
         <x:v>14</x:v>
@@ -11604,7 +11601,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G105" s="59" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H105" s="59" t="s">
         <x:v>6</x:v>
@@ -11621,10 +11618,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B106" s="41" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C106" s="43" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="C106" s="43" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="D106" s="42">
         <x:v>4</x:v>
@@ -11648,13 +11645,13 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="42" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B107" s="41" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="B107" s="41" t="s">
+      <x:c r="C107" s="43" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="C107" s="43" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="D107" s="42">
         <x:v>4</x:v>
@@ -11681,10 +11678,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B108" s="41" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="C108" s="43" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="C108" s="43" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="D108" s="42">
         <x:v>3</x:v>
@@ -11708,13 +11705,13 @@
     </x:row>
     <x:row r="109" ht="21">
       <x:c r="A109" s="60" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B109" s="44" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C109" s="44" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="B109" s="44" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C109" s="44" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="D109" s="53">
         <x:v>4</x:v>
@@ -11735,7 +11732,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J109" s="69" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="18.75">
@@ -11743,7 +11740,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B110" s="44" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C110" s="44" t="s">
         <x:v>55</x:v>
@@ -11773,7 +11770,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="129" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C111" s="129" t="s">
         <x:v>57</x:v>
@@ -11803,10 +11800,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B112" s="173" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C112" s="173" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D112" s="174">
         <x:v>8</x:v>
@@ -11833,7 +11830,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B113" s="175" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C113" s="175" t="s">
         <x:v>59</x:v>
@@ -11863,10 +11860,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B114" s="176" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C114" s="176" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="C114" s="176" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="D114" s="178">
         <x:v>2</x:v>
@@ -13173,6 +13170,6 @@
     <x:mergeCell ref="A50:T50"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4bed8e122bc4f5c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24b884fc15174b5f"/>
 </x:worksheet>
 </file>
--- a/채용비율.xlsx
+++ b/채용비율.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="Rf9a42abcac194542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="R575daa7d0bb2459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R51d5626cf6584477"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="R375fd11df0e240ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="Ra1f275c8a34d4eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R118a5c739999476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.26년 전체 소속별 점유율" sheetId="1" r:id="R3bfcfa18851b4020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.각8개지부 현장점유율" sheetId="2" r:id="Ra506fe6d0c294a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.타워사별 점유현황" sheetId="3" r:id="R31fec0e134334b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.반도체현장" sheetId="4" r:id="Rdd9cc5e27810442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.1~9월채용추이" sheetId="5" r:id="R9fbc64cd003e4d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.월별 소속별 채용비율" sheetId="6" r:id="R4e5ecdfe5b234c19"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="가평군">#REF!</x:definedName>
@@ -1524,7 +1524,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="568">
+  <x:cellXfs count="570">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -3188,6 +3188,12 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="45" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="45" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="4">
@@ -3414,7 +3420,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0991f3956ad24826"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf0c9f4501ca14137"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3663,27 +3669,26 @@
       <x:c r="A3" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B3" s="567">
-        <x:v>72</x:v>
+      <x:c r="B3" s="567" t="n">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C3" s="567" t="n">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D3" s="567" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E3" s="567">
+      <x:c r="E3" s="567" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="567">
+      <x:c r="F3" s="567" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="G3" s="567" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H3" s="567" t="n">
-        <x:f>SUM(B3:G3)</x:f>
-        <x:v>254</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="I3" s="9" t="s">
         <x:v>11</x:v>
@@ -3695,27 +3700,27 @@
       </x:c>
       <x:c r="B4" s="32" t="n">
         <x:f>IF($H$3=0,0,B3/$H$3)</x:f>
-        <x:v>0.28346456692913385</x:v>
+        <x:v>0.28294573643410853</x:v>
       </x:c>
       <x:c r="C4" s="32" t="n">
         <x:f>IF($H$3=0,0,C3/$H$3)</x:f>
-        <x:v>0.41732283464566927</x:v>
+        <x:v>0.41472868217054265</x:v>
       </x:c>
       <x:c r="D4" s="32" t="n">
         <x:f>IF($H$3=0,0,D3/$H$3)</x:f>
-        <x:v>0.03543307086614173</x:v>
+        <x:v>0.03488372093023256</x:v>
       </x:c>
       <x:c r="E4" s="32" t="n">
         <x:f>IF($H$3=0,0,E3/$H$3)</x:f>
-        <x:v>0.03937007874015748</x:v>
+        <x:v>0.03875968992248062</x:v>
       </x:c>
       <x:c r="F4" s="32" t="n">
         <x:f>IF($H$3=0,0,F3/$H$3)</x:f>
-        <x:v>0.16535433070866143</x:v>
+        <x:v>0.16279069767441862</x:v>
       </x:c>
       <x:c r="G4" s="32" t="n">
         <x:f>IF($H$3=0,0,G3/$H$3)</x:f>
-        <x:v>0.05905511811023622</x:v>
+        <x:v>0.06589147286821706</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="14" customFormat="1" ht="21.200000762939453" customHeight="1"/>
@@ -4746,109 +4751,111 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="38" t="str">
-        <x:v>남부지부 소계</x:v>
-      </x:c>
-      <x:c r="B27" s="38"/>
-      <x:c r="C27" s="38"/>
-      <x:c r="D27" s="38"/>
+        <x:v>남부</x:v>
+      </x:c>
+      <x:c r="B27" s="38" t="str">
+        <x:v>TERA PROJECT</x:v>
+      </x:c>
+      <x:c r="C27" s="38" t="str">
+        <x:v>(주)규람타워렌탈</x:v>
+      </x:c>
+      <x:c r="D27" s="38" t="str">
+        <x:v>원청사: 두산에너빌리티(주) / 2026-10-21 신규</x:v>
+      </x:c>
       <x:c r="E27" s="540" t="n">
-        <x:f>SUM(E8:E26)</x:f>
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="540" t="n">
-        <x:f>SUM(F8:F26)</x:f>
-        <x:v>41</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="540" t="n">
-        <x:f>SUM(G8:G26)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="540" t="n">
-        <x:f>SUM(H8:H26)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="540" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="540" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K27" s="540" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="I27" s="540" t="n">
-        <x:f>SUM(I8:I26)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J27" s="540" t="n">
-        <x:f>SUM(J8:J26)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K27" s="540" t="n">
-        <x:f>SUM(K8:K26)</x:f>
-        <x:v>87</x:v>
       </x:c>
       <x:c r="L27" s="38"/>
     </x:row>
     <x:row r="28" s="14" customFormat="1">
       <x:c r="A28" s="86" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>남부지부 소계</x:v>
       </x:c>
       <x:c r="B28" s="86"/>
       <x:c r="C28" s="86"/>
       <x:c r="D28" s="86"/>
-      <x:c r="E28" s="150" t="n">
-        <x:f>IF($K$27=0,0,E27/$K$27)</x:f>
-        <x:v>0.26436781609195403</x:v>
-      </x:c>
-      <x:c r="F28" s="150" t="n">
-        <x:f>IF($K$27=0,0,F27/$K$27)</x:f>
-        <x:v>0.47126436781609193</x:v>
-      </x:c>
-      <x:c r="G28" s="150" t="n">
-        <x:f>IF($K$27=0,0,G27/$K$27)</x:f>
-        <x:v>0.022988505747126436</x:v>
-      </x:c>
-      <x:c r="H28" s="150" t="n">
-        <x:f>IF($K$27=0,0,H27/$K$27)</x:f>
-        <x:v>0.04597701149425287</x:v>
-      </x:c>
-      <x:c r="I28" s="150" t="n">
-        <x:f>IF($K$27=0,0,I27/$K$27)</x:f>
-        <x:v>0.16091954022988506</x:v>
-      </x:c>
-      <x:c r="J28" s="150" t="n">
-        <x:f>IF($K$27=0,0,J27/$K$27)</x:f>
-        <x:v>0.034482758620689655</x:v>
-      </x:c>
-      <x:c r="K28" s="150" t="n">
-        <x:f>IF($K$27=0,0,K27/$K$27)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E28" s="540" t="n">
+        <x:f>SUM(E8:E27)</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F28" s="540" t="n">
+        <x:f>SUM(F8:F27)</x:f>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G28" s="540" t="n">
+        <x:f>SUM(G8:G27)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H28" s="540" t="n">
+        <x:f>SUM(H8:H27)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I28" s="540" t="n">
+        <x:f>SUM(I8:I27)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J28" s="540" t="n">
+        <x:f>SUM(J8:J27)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K28" s="540" t="n">
+        <x:f>SUM(K8:K27)</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L28" s="86"/>
     </x:row>
     <x:row r="29" s="14" customFormat="1" ht="17.25">
       <x:c r="A29" s="83" t="str">
-        <x:v>남서</x:v>
-      </x:c>
-      <x:c r="B29" s="84" t="str">
-        <x:v>남양우미린</x:v>
-      </x:c>
-      <x:c r="C29" s="84" t="str">
-        <x:v>뉴월드타워 주식회사</x:v>
-      </x:c>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B29" s="84"/>
+      <x:c r="C29" s="84"/>
       <x:c r="D29" s="84"/>
-      <x:c r="E29" s="545" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F29" s="545" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="545" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="545" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="545" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J29" s="545" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="545" t="n">
-        <x:v>3</x:v>
+      <x:c r="E29" s="565" t="n">
+        <x:f>IF($K$28=0,0,E28/$K$28)</x:f>
+        <x:v>0.26373626373626374</x:v>
+      </x:c>
+      <x:c r="F29" s="565" t="n">
+        <x:f>IF($K$28=0,0,F28/$K$28)</x:f>
+        <x:v>0.46153846153846156</x:v>
+      </x:c>
+      <x:c r="G29" s="565" t="n">
+        <x:f>IF($K$28=0,0,G28/$K$28)</x:f>
+        <x:v>0.02197802197802198</x:v>
+      </x:c>
+      <x:c r="H29" s="565" t="n">
+        <x:f>IF($K$28=0,0,H28/$K$28)</x:f>
+        <x:v>0.04395604395604396</x:v>
+      </x:c>
+      <x:c r="I29" s="565" t="n">
+        <x:f>IF($K$28=0,0,I28/$K$28)</x:f>
+        <x:v>0.15384615384615385</x:v>
+      </x:c>
+      <x:c r="J29" s="565" t="n">
+        <x:f>IF($K$28=0,0,J28/$K$28)</x:f>
+        <x:v>0.054945054945054944</x:v>
+      </x:c>
+      <x:c r="K29" s="565" t="n">
+        <x:f>IF($K$28=0,0,K28/$K$28)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L29" s="84"/>
     </x:row>
@@ -4857,10 +4864,10 @@
         <x:v>남서</x:v>
       </x:c>
       <x:c r="B30" s="109" t="str">
-        <x:v>화성비봉 지역주택조합 아파트 신축공사</x:v>
+        <x:v>남양우미린</x:v>
       </x:c>
       <x:c r="C30" s="109" t="str">
-        <x:v>주식회사 삼진타워</x:v>
+        <x:v>뉴월드타워 주식회사</x:v>
       </x:c>
       <x:c r="D30" s="109"/>
       <x:c r="E30" s="549" t="n">
@@ -4879,10 +4886,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J30" s="546" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K30" s="547" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L30" s="109"/>
     </x:row>
@@ -4891,10 +4898,10 @@
         <x:v>남서</x:v>
       </x:c>
       <x:c r="B31" s="120" t="str">
-        <x:v>오산세교2지구 M1블록 민간임대 주상복합 신축공사</x:v>
+        <x:v>화성비봉 지역주택조합 아파트 신축공사</x:v>
       </x:c>
       <x:c r="C31" s="120" t="str">
-        <x:v>(주)남산공영</x:v>
+        <x:v>주식회사 삼진타워</x:v>
       </x:c>
       <x:c r="D31" s="121"/>
       <x:c r="E31" s="550" t="n">
@@ -4910,13 +4917,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="550" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J31" s="550" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K31" s="548" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L31" s="120"/>
     </x:row>
@@ -4925,17 +4932,17 @@
         <x:v>남서</x:v>
       </x:c>
       <x:c r="B32" s="151" t="str">
-        <x:v>오산 AMK R&amp;D</x:v>
+        <x:v>오산세교2지구 M1블록 민간임대 주상복합 신축공사</x:v>
       </x:c>
       <x:c r="C32" s="151" t="str">
-        <x:v>신우개발(주)</x:v>
+        <x:v>(주)남산공영</x:v>
       </x:c>
       <x:c r="D32" s="151"/>
       <x:c r="E32" s="551" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F32" s="551" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="551" t="n">
         <x:v>0</x:v>
@@ -4947,11 +4954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="551" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K32" s="539" t="n">
-        <x:f>SUM(E32:J32)</x:f>
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L32" s="119"/>
     </x:row>
@@ -4960,142 +4966,140 @@
         <x:v>남서</x:v>
       </x:c>
       <x:c r="B33" s="153" t="str">
-        <x:v>오산세교우미린레이크시티</x:v>
+        <x:v>오산 AMK R&amp;D</x:v>
       </x:c>
       <x:c r="C33" s="153" t="str">
-        <x:v>뉴월드타워 주식회사</x:v>
+        <x:v>신우개발(주)</x:v>
       </x:c>
       <x:c r="D33" s="153"/>
       <x:c r="E33" s="540" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F33" s="540" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="540" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="540" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="540" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="540" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K33" s="541" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L33" s="38"/>
     </x:row>
     <x:row r="34" s="14" customFormat="1">
       <x:c r="A34" s="38" t="str">
-        <x:v>남서지부 소계</x:v>
-      </x:c>
-      <x:c r="B34" s="38"/>
-      <x:c r="C34" s="38"/>
+        <x:v>남서</x:v>
+      </x:c>
+      <x:c r="B34" s="38" t="str">
+        <x:v>오산세교우미린레이크시티</x:v>
+      </x:c>
+      <x:c r="C34" s="38" t="str">
+        <x:v>뉴월드타워 주식회사</x:v>
+      </x:c>
       <x:c r="D34" s="38"/>
       <x:c r="E34" s="540" t="n">
-        <x:f>SUM(E29:E33)</x:f>
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F34" s="540" t="n">
-        <x:f>SUM(F29:F33)</x:f>
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G34" s="540" t="n">
-        <x:f>SUM(G29:G33)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H34" s="540" t="n">
-        <x:f>SUM(H29:H33)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I34" s="540" t="n">
-        <x:f>SUM(I29:I33)</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J34" s="540" t="n">
-        <x:f>SUM(J29:J33)</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K34" s="540" t="n">
-        <x:f>SUM(K29:K33)</x:f>
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L34" s="38"/>
     </x:row>
     <x:row r="35" s="14" customFormat="1" ht="17.25">
       <x:c r="A35" s="83" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>남서지부 소계</x:v>
       </x:c>
       <x:c r="B35" s="84"/>
       <x:c r="C35" s="84"/>
       <x:c r="D35" s="84"/>
-      <x:c r="E35" s="565" t="n">
-        <x:f>IF($K$34=0,0,E34/$K$34)</x:f>
-        <x:v>0.2857142857142857</x:v>
-      </x:c>
-      <x:c r="F35" s="565" t="n">
-        <x:f>IF($K$34=0,0,F34/$K$34)</x:f>
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="G35" s="565" t="n">
-        <x:f>IF($K$34=0,0,G34/$K$34)</x:f>
-        <x:v>0.047619047619047616</x:v>
-      </x:c>
-      <x:c r="H35" s="565" t="n">
-        <x:f>IF($K$34=0,0,H34/$K$34)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="565" t="n">
-        <x:f>IF($K$34=0,0,I34/$K$34)</x:f>
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
-      <x:c r="J35" s="565" t="n">
-        <x:f>IF($K$34=0,0,J34/$K$34)</x:f>
-        <x:v>0.19047619047619047</x:v>
-      </x:c>
-      <x:c r="K35" s="565" t="n">
-        <x:f>IF($K$34=0,0,K34/$K$34)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E35" s="545" t="n">
+        <x:f>SUM(E30:E34)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F35" s="545" t="n">
+        <x:f>SUM(F30:F34)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G35" s="545" t="n">
+        <x:f>SUM(G30:G34)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="545" t="n">
+        <x:f>SUM(H30:H34)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="545" t="n">
+        <x:f>SUM(I30:I34)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J35" s="545" t="n">
+        <x:f>SUM(J30:J34)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K35" s="545" t="n">
+        <x:f>SUM(K30:K34)</x:f>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L35" s="84"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="108" t="str">
-        <x:v>동부</x:v>
-      </x:c>
-      <x:c r="B36" s="110" t="str">
-        <x:v>이천한양</x:v>
-      </x:c>
-      <x:c r="C36" s="110" t="str">
-        <x:v>주식회사 현성건설</x:v>
-      </x:c>
-      <x:c r="D36" s="110" t="str">
-        <x:v>현성</x:v>
-      </x:c>
-      <x:c r="E36" s="98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="98" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G36" s="98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="98" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="98" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K36" s="98" t="n">
-        <x:v>0</x:v>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B36" s="110"/>
+      <x:c r="C36" s="110"/>
+      <x:c r="D36" s="110"/>
+      <x:c r="E36" s="565" t="n">
+        <x:f>IF($K$35=0,0,E35/$K$35)</x:f>
+        <x:v>0.2857142857142857</x:v>
+      </x:c>
+      <x:c r="F36" s="565" t="n">
+        <x:f>IF($K$35=0,0,F35/$K$35)</x:f>
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="G36" s="565" t="n">
+        <x:f>IF($K$35=0,0,G35/$K$35)</x:f>
+        <x:v>0.047619047619047616</x:v>
+      </x:c>
+      <x:c r="H36" s="565" t="n">
+        <x:f>IF($K$35=0,0,H35/$K$35)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="565" t="n">
+        <x:f>IF($K$35=0,0,I35/$K$35)</x:f>
+        <x:v>0.14285714285714285</x:v>
+      </x:c>
+      <x:c r="J36" s="565" t="n">
+        <x:f>IF($K$35=0,0,J35/$K$35)</x:f>
+        <x:v>0.19047619047619047</x:v>
+      </x:c>
+      <x:c r="K36" s="565" t="n">
+        <x:f>IF($K$35=0,0,K35/$K$35)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L36" s="110" t="str">
         <x:v>통계제외</x:v>
@@ -5106,17 +5110,19 @@
         <x:v>동부</x:v>
       </x:c>
       <x:c r="B37" s="115" t="str">
-        <x:v>요진건설</x:v>
+        <x:v>이천한양</x:v>
       </x:c>
       <x:c r="C37" s="115" t="str">
-        <x:v>주식회사 한산타워</x:v>
-      </x:c>
-      <x:c r="D37" s="115"/>
+        <x:v>주식회사 현성건설</x:v>
+      </x:c>
+      <x:c r="D37" s="115" t="str">
+        <x:v>현성</x:v>
+      </x:c>
       <x:c r="E37" s="537" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F37" s="537" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="537" t="n">
         <x:v>0</x:v>
@@ -5128,10 +5134,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="537" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K37" s="548" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="118"/>
     </x:row>
@@ -5140,10 +5146,10 @@
         <x:v>동부</x:v>
       </x:c>
       <x:c r="B38" s="151" t="str">
-        <x:v>홍문2지구 공동주택</x:v>
+        <x:v>요진건설</x:v>
       </x:c>
       <x:c r="C38" s="151" t="str">
-        <x:v>(주)한진</x:v>
+        <x:v>주식회사 한산타워</x:v>
       </x:c>
       <x:c r="D38" s="151"/>
       <x:c r="E38" s="551" t="n">
@@ -5152,14 +5158,20 @@
       <x:c r="F38" s="551" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G38" s="551"/>
-      <x:c r="H38" s="551"/>
-      <x:c r="I38" s="551"/>
+      <x:c r="G38" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="551" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J38" s="551" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K38" s="539" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L38" s="119"/>
     </x:row>
@@ -5168,33 +5180,26 @@
         <x:v>동부</x:v>
       </x:c>
       <x:c r="B39" s="154" t="str">
-        <x:v>이천 증포5지구 칸타빌 에듀파크 신축공사</x:v>
+        <x:v>홍문2지구 공동주택</x:v>
       </x:c>
       <x:c r="C39" s="154" t="str">
-        <x:v>국제산업렌탈(주)</x:v>
+        <x:v>(주)한진</x:v>
       </x:c>
       <x:c r="D39" s="154"/>
       <x:c r="E39" s="542" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="542" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G39" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H39" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="542"/>
+      <x:c r="H39" s="542"/>
+      <x:c r="I39" s="542"/>
       <x:c r="J39" s="542" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K39" s="543" t="n">
-        <x:f>SUM(E39:J39)</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L39" s="82"/>
     </x:row>
@@ -5203,17 +5208,17 @@
         <x:v>동부</x:v>
       </x:c>
       <x:c r="B40" s="43" t="str">
-        <x:v>경안2지구 도시개발사업 주상복합 신축공사</x:v>
+        <x:v>이천 증포5지구 칸타빌 에듀파크 신축공사</x:v>
       </x:c>
       <x:c r="C40" s="43" t="str">
-        <x:v>(주)예림타워</x:v>
+        <x:v>국제산업렌탈(주)</x:v>
       </x:c>
       <x:c r="D40" s="88"/>
       <x:c r="E40" s="542" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F40" s="542" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="542" t="n">
         <x:v>0</x:v>
@@ -5228,115 +5233,115 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K40" s="543" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L40" s="82"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="43" t="str">
-        <x:v>동부지부 소계</x:v>
-      </x:c>
-      <x:c r="B41" s="43"/>
-      <x:c r="C41" s="43"/>
+        <x:v>동부</x:v>
+      </x:c>
+      <x:c r="B41" s="43" t="str">
+        <x:v>경안2지구 도시개발사업 주상복합 신축공사</x:v>
+      </x:c>
+      <x:c r="C41" s="43" t="str">
+        <x:v>(주)예림타워</x:v>
+      </x:c>
       <x:c r="D41" s="43"/>
       <x:c r="E41" s="542" t="n">
-        <x:f>SUM(E37:E40)</x:f>
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F41" s="542" t="n">
-        <x:f>SUM(F37:F40)</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G41" s="542" t="n">
-        <x:f>SUM(G37:G40)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="542" t="n">
-        <x:f>SUM(H37:H40)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="542" t="n">
-        <x:f>SUM(I37:I40)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" s="542" t="n">
-        <x:f>SUM(J37:J40)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K41" s="543" t="n">
-        <x:f>SUM(K37:K40)</x:f>
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L41" s="82"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="43" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>동부지부 소계</x:v>
       </x:c>
       <x:c r="B42" s="43"/>
       <x:c r="C42" s="43"/>
       <x:c r="D42" s="43"/>
-      <x:c r="E42" s="102" t="n">
-        <x:f>IF($K$41=0,0,E41/$K$41)</x:f>
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F42" s="102" t="n">
-        <x:f>IF($K$41=0,0,F41/$K$41)</x:f>
-        <x:v>0.45454545454545453</x:v>
-      </x:c>
-      <x:c r="G42" s="102" t="n">
-        <x:f>IF($K$41=0,0,G41/$K$41)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="102" t="n">
-        <x:f>IF($K$41=0,0,H41/$K$41)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I42" s="102" t="n">
-        <x:f>IF($K$41=0,0,I41/$K$41)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J42" s="102" t="n">
-        <x:f>IF($K$41=0,0,J41/$K$41)</x:f>
-        <x:v>0.18181818181818182</x:v>
-      </x:c>
-      <x:c r="K42" s="103" t="n">
-        <x:f>IF($K$41=0,0,K41/$K$41)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E42" s="542" t="n">
+        <x:f>SUM(E37:E41)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F42" s="542" t="n">
+        <x:f>SUM(F37:F41)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G42" s="542" t="n">
+        <x:f>SUM(G37:G41)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="542" t="n">
+        <x:f>SUM(H37:H41)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="542" t="n">
+        <x:f>SUM(I37:I41)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="542" t="n">
+        <x:f>SUM(J37:J41)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K42" s="543" t="n">
+        <x:f>SUM(K37:K41)</x:f>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L42" s="82"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="43" t="str">
-        <x:v>서부</x:v>
-      </x:c>
-      <x:c r="B43" s="43" t="str">
-        <x:v>안산프로젝트팀부크(현대건설)</x:v>
-      </x:c>
-      <x:c r="C43" s="43" t="str">
-        <x:v>주식회사 한불타워</x:v>
-      </x:c>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B43" s="43"/>
+      <x:c r="C43" s="43"/>
       <x:c r="D43" s="43"/>
-      <x:c r="E43" s="542" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F43" s="542" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G43" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I43" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J43" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K43" s="543" t="n">
-        <x:v>2</x:v>
+      <x:c r="E43" s="102" t="n">
+        <x:f>IF($K$42=0,0,E42/$K$42)</x:f>
+        <x:v>0.36363636363636365</x:v>
+      </x:c>
+      <x:c r="F43" s="102" t="n">
+        <x:f>IF($K$42=0,0,F42/$K$42)</x:f>
+        <x:v>0.6363636363636364</x:v>
+      </x:c>
+      <x:c r="G43" s="102" t="n">
+        <x:f>IF($K$42=0,0,G42/$K$42)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="102" t="n">
+        <x:f>IF($K$42=0,0,H42/$K$42)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I43" s="102" t="n">
+        <x:f>IF($K$42=0,0,I42/$K$42)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J43" s="102" t="n">
+        <x:f>IF($K$42=0,0,J42/$K$42)</x:f>
+        <x:v>0.36363636363636365</x:v>
+      </x:c>
+      <x:c r="K43" s="103" t="n">
+        <x:f>IF($K$42=0,0,K42/$K$42)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L43" s="82"/>
     </x:row>
@@ -5345,10 +5350,10 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B44" s="38" t="str">
-        <x:v>안산글로벌클라우드(삼성물산)</x:v>
+        <x:v>안산프로젝트팀부크(현대건설)</x:v>
       </x:c>
       <x:c r="C44" s="38" t="str">
-        <x:v>정호개발주식회사</x:v>
+        <x:v>주식회사 한불타워</x:v>
       </x:c>
       <x:c r="D44" s="38"/>
       <x:c r="E44" s="540" t="n">
@@ -5379,10 +5384,10 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B45" s="38" t="str">
-        <x:v>하중지구 한신공영</x:v>
+        <x:v>안산글로벌클라우드(삼성물산)</x:v>
       </x:c>
       <x:c r="C45" s="38" t="str">
-        <x:v>(주)신화중공업</x:v>
+        <x:v>정호개발주식회사</x:v>
       </x:c>
       <x:c r="D45" s="38"/>
       <x:c r="E45" s="540" t="n">
@@ -5398,13 +5403,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="540" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J45" s="540" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K45" s="540" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L45" s="38"/>
     </x:row>
@@ -5413,17 +5418,17 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B46" s="84" t="str">
-        <x:v>하중지구 양우건설</x:v>
+        <x:v>하중지구 한신공영</x:v>
       </x:c>
       <x:c r="C46" s="84" t="str">
-        <x:v>(주)진성타워</x:v>
+        <x:v>(주)신화중공업</x:v>
       </x:c>
       <x:c r="D46" s="84"/>
       <x:c r="E46" s="545" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F46" s="545" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G46" s="545" t="n">
         <x:v>0</x:v>
@@ -5432,13 +5437,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="545" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J46" s="545" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K46" s="545" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L46" s="84"/>
     </x:row>
@@ -5447,14 +5452,14 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B47" s="38" t="str">
-        <x:v>시흥거모지구 S-2BL,B-2BL(대방산업개발)</x:v>
+        <x:v>하중지구 양우건설</x:v>
       </x:c>
       <x:c r="C47" s="38" t="str">
-        <x:v>주식회사 우정타워</x:v>
+        <x:v>(주)진성타워</x:v>
       </x:c>
       <x:c r="D47" s="38"/>
       <x:c r="E47" s="552" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F47" s="552" t="n">
         <x:v>2</x:v>
@@ -5466,13 +5471,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I47" s="552" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J47" s="552" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K47" s="553" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L47" s="38"/>
     </x:row>
@@ -5481,17 +5486,17 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B48" s="108" t="str">
-        <x:v>배곧서울대학교병원</x:v>
+        <x:v>시흥거모지구 S-2BL,B-2BL(대방산업개발)</x:v>
       </x:c>
       <x:c r="C48" s="108" t="str">
-        <x:v>(주)타워링</x:v>
+        <x:v>주식회사 우정타워</x:v>
       </x:c>
       <x:c r="D48" s="108"/>
       <x:c r="E48" s="545" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F48" s="545" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G48" s="545" t="n">
         <x:v>0</x:v>
@@ -5500,13 +5505,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="545" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J48" s="545" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K48" s="554" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L48" s="111"/>
     </x:row>
@@ -5515,20 +5520,20 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B49" s="115" t="str">
-        <x:v>시흥하중 A-1BL 공동주택 건설공사</x:v>
+        <x:v>배곧서울대학교병원</x:v>
       </x:c>
       <x:c r="C49" s="115" t="str">
-        <x:v>(주)규람타워렌탈</x:v>
+        <x:v>(주)타워링</x:v>
       </x:c>
       <x:c r="D49" s="121"/>
       <x:c r="E49" s="537" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F49" s="537" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G49" s="537" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="537" t="n">
         <x:v>0</x:v>
@@ -5540,7 +5545,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K49" s="548" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L49" s="118"/>
     </x:row>
@@ -5549,10 +5554,10 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B50" s="151" t="str">
-        <x:v>시흥시 거모지구 B-1블록 공동주택 신축공사</x:v>
+        <x:v>시흥하중 A-1BL 공동주택 건설공사</x:v>
       </x:c>
       <x:c r="C50" s="151" t="str">
-        <x:v>주식회사 필웍스</x:v>
+        <x:v>(주)규람타워렌탈</x:v>
       </x:c>
       <x:c r="D50" s="155"/>
       <x:c r="E50" s="551" t="n">
@@ -5583,10 +5588,10 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B51" s="154" t="str">
-        <x:v>시흥거모 B-6BL 모아엘가&amp;대광로제비앙 공동주택 신축공사</x:v>
+        <x:v>시흥시 거모지구 B-1블록 공동주택 신축공사</x:v>
       </x:c>
       <x:c r="C51" s="154" t="str">
-        <x:v>(주)금강건기</x:v>
+        <x:v>주식회사 필웍스</x:v>
       </x:c>
       <x:c r="D51" s="156"/>
       <x:c r="E51" s="555" t="n">
@@ -5596,13 +5601,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G51" s="555" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H51" s="555" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="555" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J51" s="555" t="n">
         <x:v>0</x:v>
@@ -5617,33 +5622,32 @@
         <x:v>서부</x:v>
       </x:c>
       <x:c r="B52" s="43" t="str">
-        <x:v>시화MTV 지하주차장</x:v>
+        <x:v>시흥거모 B-6BL 모아엘가&amp;대광로제비앙 공동주택 신축공사</x:v>
       </x:c>
       <x:c r="C52" s="43" t="str">
-        <x:v>(주)우리기계산업</x:v>
+        <x:v>(주)금강건기</x:v>
       </x:c>
       <x:c r="D52" s="43"/>
       <x:c r="E52" s="542" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F52" s="542" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G52" s="542" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H52" s="542" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I52" s="542" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J52" s="542" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K52" s="543" t="n">
-        <x:f>SUM(E52:J52)</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L52" s="82" t="str">
         <x:v>원청사: 강산건설(주)</x:v>
@@ -5651,109 +5655,109 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="43" t="str">
-        <x:v>서부지부 소계</x:v>
-      </x:c>
-      <x:c r="B53" s="43"/>
-      <x:c r="C53" s="43"/>
+        <x:v>서부</x:v>
+      </x:c>
+      <x:c r="B53" s="43" t="str">
+        <x:v>시화MTV 지하주차장</x:v>
+      </x:c>
+      <x:c r="C53" s="43" t="str">
+        <x:v>(주)우리기계산업</x:v>
+      </x:c>
       <x:c r="D53" s="43"/>
       <x:c r="E53" s="542" t="n">
-        <x:f>SUM(E43:E52)</x:f>
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F53" s="542" t="n">
-        <x:f>SUM(F43:F52)</x:f>
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G53" s="542" t="n">
-        <x:f>SUM(G43:G52)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="542" t="n">
-        <x:f>SUM(H43:H52)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="542" t="n">
-        <x:f>SUM(I43:I52)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J53" s="542" t="n">
-        <x:f>SUM(J43:J52)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K53" s="543" t="n">
-        <x:f>SUM(K43:K52)</x:f>
-        <x:v>33</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L53" s="82"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="43" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>서부지부 소계</x:v>
       </x:c>
       <x:c r="B54" s="43"/>
       <x:c r="C54" s="43"/>
       <x:c r="D54" s="43"/>
-      <x:c r="E54" s="102" t="n">
-        <x:f>IF($K$53=0,0,E53/$K$53)</x:f>
-        <x:v>0.2727272727272727</x:v>
-      </x:c>
-      <x:c r="F54" s="102" t="n">
-        <x:f>IF($K$53=0,0,F53/$K$53)</x:f>
-        <x:v>0.45454545454545453</x:v>
-      </x:c>
-      <x:c r="G54" s="102" t="n">
-        <x:f>IF($K$53=0,0,G53/$K$53)</x:f>
-        <x:v>0.06060606060606061</x:v>
-      </x:c>
-      <x:c r="H54" s="102" t="n">
-        <x:f>IF($K$53=0,0,H53/$K$53)</x:f>
-        <x:v>0.030303030303030304</x:v>
-      </x:c>
-      <x:c r="I54" s="102" t="n">
-        <x:f>IF($K$53=0,0,I53/$K$53)</x:f>
-        <x:v>0.18181818181818182</x:v>
-      </x:c>
-      <x:c r="J54" s="102" t="n">
-        <x:f>IF($K$53=0,0,J53/$K$53)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K54" s="103" t="n">
-        <x:f>IF($K$53=0,0,K53/$K$53)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E54" s="542" t="n">
+        <x:f>SUM(E44:E53)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F54" s="542" t="n">
+        <x:f>SUM(F44:F53)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G54" s="542" t="n">
+        <x:f>SUM(G44:G53)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H54" s="542" t="n">
+        <x:f>SUM(H44:H53)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I54" s="542" t="n">
+        <x:f>SUM(I44:I53)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J54" s="542" t="n">
+        <x:f>SUM(J44:J53)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54" s="543" t="n">
+        <x:f>SUM(K44:K53)</x:f>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L54" s="82"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="43" t="str">
-        <x:v>북서</x:v>
-      </x:c>
-      <x:c r="B55" s="43" t="str">
-        <x:v>군포시 SGC건설</x:v>
-      </x:c>
-      <x:c r="C55" s="43" t="str">
-        <x:v>(주)한백산업</x:v>
-      </x:c>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B55" s="43"/>
+      <x:c r="C55" s="43"/>
       <x:c r="D55" s="43"/>
-      <x:c r="E55" s="542" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F55" s="542" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G55" s="542" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H55" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I55" s="542" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J55" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K55" s="543" t="n">
-        <x:v>7</x:v>
+      <x:c r="E55" s="102" t="n">
+        <x:f>IF($K$54=0,0,E54/$K$54)</x:f>
+        <x:v>0.2727272727272727</x:v>
+      </x:c>
+      <x:c r="F55" s="102" t="n">
+        <x:f>IF($K$54=0,0,F54/$K$54)</x:f>
+        <x:v>0.45454545454545453</x:v>
+      </x:c>
+      <x:c r="G55" s="102" t="n">
+        <x:f>IF($K$54=0,0,G54/$K$54)</x:f>
+        <x:v>0.06060606060606061</x:v>
+      </x:c>
+      <x:c r="H55" s="102" t="n">
+        <x:f>IF($K$54=0,0,H54/$K$54)</x:f>
+        <x:v>0.030303030303030304</x:v>
+      </x:c>
+      <x:c r="I55" s="102" t="n">
+        <x:f>IF($K$54=0,0,I54/$K$54)</x:f>
+        <x:v>0.18181818181818182</x:v>
+      </x:c>
+      <x:c r="J55" s="102" t="n">
+        <x:f>IF($K$54=0,0,J54/$K$54)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="103" t="n">
+        <x:f>IF($K$54=0,0,K54/$K$54)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L55" s="82"/>
     </x:row>
@@ -5762,7 +5766,7 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B56" s="43" t="str">
-        <x:v>관양동 DL이앤씨</x:v>
+        <x:v>군포시 SGC건설</x:v>
       </x:c>
       <x:c r="C56" s="43" t="str">
         <x:v>(주)한백산업</x:v>
@@ -5775,7 +5779,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G56" s="542" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H56" s="542" t="n">
         <x:v>0</x:v>
@@ -5787,7 +5791,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K56" s="543" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L56" s="38"/>
     </x:row>
@@ -5799,14 +5803,14 @@
         <x:v>관양동 DL이앤씨</x:v>
       </x:c>
       <x:c r="C57" s="89" t="str">
-        <x:v>벽산중기산업주식회사</x:v>
+        <x:v>(주)한백산업</x:v>
       </x:c>
       <x:c r="D57" s="70"/>
       <x:c r="E57" s="556" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F57" s="556" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G57" s="556" t="n">
         <x:v>0</x:v>
@@ -5815,13 +5819,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="556" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J57" s="556" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K57" s="556" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L57" s="70"/>
     </x:row>
@@ -5830,10 +5834,10 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B58" s="84" t="str">
-        <x:v>의왕청계 시티건설</x:v>
+        <x:v>관양동 DL이앤씨</x:v>
       </x:c>
       <x:c r="C58" s="84" t="str">
-        <x:v>주식회사 우정타워</x:v>
+        <x:v>벽산중기산업주식회사</x:v>
       </x:c>
       <x:c r="D58" s="84"/>
       <x:c r="E58" s="545" t="n">
@@ -5864,32 +5868,32 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B59" s="38" t="str">
-        <x:v>과천 태왕</x:v>
+        <x:v>의왕청계 시티건설</x:v>
       </x:c>
       <x:c r="C59" s="38" t="str">
-        <x:v>주식회사 비엠케이</x:v>
+        <x:v>주식회사 우정타워</x:v>
       </x:c>
       <x:c r="D59" s="38"/>
       <x:c r="E59" s="552" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F59" s="552" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G59" s="552" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="552" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="552" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J59" s="552" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K59" s="553" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L59" s="38"/>
     </x:row>
@@ -5898,23 +5902,23 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B60" s="108" t="str">
-        <x:v>과천 주암동 디에이치 아델스타(현대건설)</x:v>
+        <x:v>과천 태왕</x:v>
       </x:c>
       <x:c r="C60" s="108" t="str">
-        <x:v>(주)국영타워랜드</x:v>
+        <x:v>주식회사 비엠케이</x:v>
       </x:c>
       <x:c r="D60" s="108"/>
       <x:c r="E60" s="545" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F60" s="545" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G60" s="545" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H60" s="545" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I60" s="545" t="n">
         <x:v>1</x:v>
@@ -5923,7 +5927,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K60" s="554" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L60" s="111"/>
     </x:row>
@@ -5932,17 +5936,17 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B61" s="115" t="str">
-        <x:v>안양 샘병원</x:v>
+        <x:v>과천 주암동 디에이치 아델스타(현대건설)</x:v>
       </x:c>
       <x:c r="C61" s="115" t="str">
-        <x:v>주식회사 가람타워</x:v>
+        <x:v>(주)국영타워랜드</x:v>
       </x:c>
       <x:c r="D61" s="115"/>
       <x:c r="E61" s="537" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F61" s="537" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G61" s="537" t="n">
         <x:v>0</x:v>
@@ -5951,13 +5955,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I61" s="537" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J61" s="537" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K61" s="548" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L61" s="118"/>
     </x:row>
@@ -5966,17 +5970,17 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B62" s="151" t="str">
-        <x:v>안양 박달동 신안아파트 재건축(현대산업개발)</x:v>
+        <x:v>안양 샘병원</x:v>
       </x:c>
       <x:c r="C62" s="151" t="str">
-        <x:v>주식회사 비엠케이</x:v>
+        <x:v>주식회사 가람타워</x:v>
       </x:c>
       <x:c r="D62" s="151"/>
       <x:c r="E62" s="551" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F62" s="551" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G62" s="551" t="n">
         <x:v>0</x:v>
@@ -5985,13 +5989,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I62" s="551" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J62" s="551" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K62" s="539" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L62" s="119"/>
     </x:row>
@@ -6000,10 +6004,10 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B63" s="157" t="str">
-        <x:v>안양역세권지구 재개발정비사업(현대산업개발)</x:v>
+        <x:v>안양 박달동 신안아파트 재건축(현대산업개발)</x:v>
       </x:c>
       <x:c r="C63" s="157" t="str">
-        <x:v>오투기계산업(주)</x:v>
+        <x:v>주식회사 비엠케이</x:v>
       </x:c>
       <x:c r="D63" s="156"/>
       <x:c r="E63" s="555" t="n">
@@ -6034,17 +6038,17 @@
         <x:v>북서</x:v>
       </x:c>
       <x:c r="B64" s="43" t="str">
-        <x:v>관양동 오피스텔 신축공사</x:v>
+        <x:v>안양역세권지구 재개발정비사업(현대산업개발)</x:v>
       </x:c>
       <x:c r="C64" s="43" t="str">
-        <x:v>(주)유건설 (단종계약)</x:v>
+        <x:v>오투기계산업(주)</x:v>
       </x:c>
       <x:c r="D64" s="88"/>
       <x:c r="E64" s="542" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F64" s="542" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G64" s="542" t="n">
         <x:v>0</x:v>
@@ -6053,122 +6057,121 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I64" s="542" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J64" s="542" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K64" s="543" t="n">
-        <x:f>SUM(E64:J64)</x:f>
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L64" s="82"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="43" t="str">
-        <x:v>북서지부 소계</x:v>
-      </x:c>
-      <x:c r="B65" s="43"/>
-      <x:c r="C65" s="43"/>
+        <x:v>북서</x:v>
+      </x:c>
+      <x:c r="B65" s="43" t="str">
+        <x:v>관양동 오피스텔 신축공사</x:v>
+      </x:c>
+      <x:c r="C65" s="43" t="str">
+        <x:v>(주)유건설 (단종계약)</x:v>
+      </x:c>
       <x:c r="D65" s="43"/>
       <x:c r="E65" s="542" t="n">
-        <x:f>SUM(E55:E64)</x:f>
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F65" s="542" t="n">
-        <x:f>SUM(F55:F64)</x:f>
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G65" s="542" t="n">
-        <x:f>SUM(G55:G64)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="542" t="n">
-        <x:f>SUM(H55:H64)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="542" t="n">
-        <x:f>SUM(I55:I64)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J65" s="542" t="n">
-        <x:f>SUM(J55:J64)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K65" s="543" t="n">
-        <x:f>SUM(K55:K64)</x:f>
-        <x:v>38</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L65" s="82"/>
     </x:row>
     <x:row r="66" s="14" customFormat="1" ht="17.25">
       <x:c r="A66" s="43" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>북서지부 소계</x:v>
       </x:c>
       <x:c r="B66" s="43"/>
       <x:c r="C66" s="43"/>
       <x:c r="D66" s="43"/>
-      <x:c r="E66" s="102" t="n">
-        <x:f>IF($K$65=0,0,E65/$K$65)</x:f>
-        <x:v>0.3157894736842105</x:v>
-      </x:c>
-      <x:c r="F66" s="102" t="n">
-        <x:f>IF($K$65=0,0,F65/$K$65)</x:f>
-        <x:v>0.4473684210526316</x:v>
-      </x:c>
-      <x:c r="G66" s="102" t="n">
-        <x:f>IF($K$65=0,0,G65/$K$65)</x:f>
-        <x:v>0.05263157894736842</x:v>
-      </x:c>
-      <x:c r="H66" s="102" t="n">
-        <x:f>IF($K$65=0,0,H65/$K$65)</x:f>
-        <x:v>0.02631578947368421</x:v>
-      </x:c>
-      <x:c r="I66" s="102" t="n">
-        <x:f>IF($K$65=0,0,I65/$K$65)</x:f>
-        <x:v>0.15789473684210525</x:v>
-      </x:c>
-      <x:c r="J66" s="102" t="n">
-        <x:f>IF($K$65=0,0,J65/$K$65)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K66" s="103" t="n">
-        <x:f>IF($K$65=0,0,K65/$K$65)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E66" s="542" t="n">
+        <x:f>SUM(E56:E65)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F66" s="542" t="n">
+        <x:f>SUM(F56:F65)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G66" s="542" t="n">
+        <x:f>SUM(G56:G65)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H66" s="542" t="n">
+        <x:f>SUM(H56:H65)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I66" s="542" t="n">
+        <x:f>SUM(I56:I65)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J66" s="542" t="n">
+        <x:f>SUM(J56:J65)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="543" t="n">
+        <x:f>SUM(K56:K65)</x:f>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L66" s="38"/>
     </x:row>
     <x:row r="67" s="14" customFormat="1" ht="17.25">
       <x:c r="A67" s="43" t="str">
-        <x:v>용인</x:v>
-      </x:c>
-      <x:c r="B67" s="43" t="str">
-        <x:v>양지 대우 원클러스터</x:v>
-      </x:c>
-      <x:c r="C67" s="43" t="str">
-        <x:v>(주)규람타워렌탈</x:v>
-      </x:c>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B67" s="43"/>
+      <x:c r="C67" s="43"/>
       <x:c r="D67" s="43"/>
-      <x:c r="E67" s="542" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F67" s="542" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G67" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H67" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I67" s="542" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J67" s="542" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K67" s="543" t="n">
-        <x:v>4</x:v>
+      <x:c r="E67" s="102" t="n">
+        <x:f>IF($K$66=0,0,E66/$K$66)</x:f>
+        <x:v>0.3157894736842105</x:v>
+      </x:c>
+      <x:c r="F67" s="102" t="n">
+        <x:f>IF($K$66=0,0,F66/$K$66)</x:f>
+        <x:v>0.4473684210526316</x:v>
+      </x:c>
+      <x:c r="G67" s="102" t="n">
+        <x:f>IF($K$66=0,0,G66/$K$66)</x:f>
+        <x:v>0.05263157894736842</x:v>
+      </x:c>
+      <x:c r="H67" s="102" t="n">
+        <x:f>IF($K$66=0,0,H66/$K$66)</x:f>
+        <x:v>0.02631578947368421</x:v>
+      </x:c>
+      <x:c r="I67" s="102" t="n">
+        <x:f>IF($K$66=0,0,I66/$K$66)</x:f>
+        <x:v>0.15789473684210525</x:v>
+      </x:c>
+      <x:c r="J67" s="102" t="n">
+        <x:f>IF($K$66=0,0,J66/$K$66)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="103" t="n">
+        <x:f>IF($K$66=0,0,K66/$K$66)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L67" s="38"/>
     </x:row>
@@ -6177,26 +6180,26 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B68" s="43" t="str">
-        <x:v>양지 SM경남 아너스빌</x:v>
+        <x:v>양지 대우 원클러스터</x:v>
       </x:c>
       <x:c r="C68" s="43" t="str">
-        <x:v>주식회사 비엠케이</x:v>
+        <x:v>(주)규람타워렌탈</x:v>
       </x:c>
       <x:c r="D68" s="43"/>
       <x:c r="E68" s="542" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F68" s="542" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G68" s="542" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="542" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I68" s="542" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J68" s="542" t="n">
         <x:v>0</x:v>
@@ -6211,26 +6214,26 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B69" s="38" t="str">
-        <x:v>역북 푸르지오 클루센트(대우건설)</x:v>
+        <x:v>양지 SM경남 아너스빌</x:v>
       </x:c>
       <x:c r="C69" s="38" t="str">
-        <x:v>벽산중기산업주식회사</x:v>
+        <x:v>주식회사 비엠케이</x:v>
       </x:c>
       <x:c r="D69" s="38"/>
       <x:c r="E69" s="540" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F69" s="540" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G69" s="540" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="540" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I69" s="540" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J69" s="540" t="n">
         <x:v>0</x:v>
@@ -6245,25 +6248,23 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B70" s="90" t="str">
-        <x:v>고림 대광로제비앙</x:v>
+        <x:v>역북 푸르지오 클루센트(대우건설)</x:v>
       </x:c>
       <x:c r="C70" s="90" t="str">
-        <x:v>주식회사 현성건설</x:v>
-      </x:c>
-      <x:c r="D70" s="90" t="str">
-        <x:v>현성</x:v>
-      </x:c>
+        <x:v>벽산중기산업주식회사</x:v>
+      </x:c>
+      <x:c r="D70" s="90"/>
       <x:c r="E70" s="557" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F70" s="557" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G70" s="557" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="557" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I70" s="557" t="n">
         <x:v>1</x:v>
@@ -6272,7 +6273,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K70" s="557" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L70" s="90" t="str">
         <x:v>통계제외</x:v>
@@ -6283,17 +6284,19 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B71" s="69" t="str">
-        <x:v>백암 오뚜기물류센타</x:v>
+        <x:v>고림 대광로제비앙</x:v>
       </x:c>
       <x:c r="C71" s="69" t="str">
-        <x:v>주식회사 가람타워</x:v>
-      </x:c>
-      <x:c r="D71" s="69"/>
+        <x:v>주식회사 현성건설</x:v>
+      </x:c>
+      <x:c r="D71" s="69" t="str">
+        <x:v>현성</x:v>
+      </x:c>
       <x:c r="E71" s="534" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F71" s="534" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G71" s="534" t="n">
         <x:v>0</x:v>
@@ -6302,13 +6305,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="534" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J71" s="534" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K71" s="534" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L71" s="69"/>
     </x:row>
@@ -6317,10 +6320,10 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B72" s="91" t="str">
-        <x:v>마평동 여성복지회관</x:v>
+        <x:v>백암 오뚜기물류센타</x:v>
       </x:c>
       <x:c r="C72" s="91" t="str">
-        <x:v>(주)무기타워렌탈</x:v>
+        <x:v>주식회사 가람타워</x:v>
       </x:c>
       <x:c r="D72" s="91"/>
       <x:c r="E72" s="544" t="n">
@@ -6333,7 +6336,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H72" s="544" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I72" s="544" t="n">
         <x:v>0</x:v>
@@ -6342,7 +6345,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K72" s="544" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L72" s="92"/>
     </x:row>
@@ -6351,14 +6354,14 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B73" s="93" t="str">
-        <x:v>용인 라온프라이빗</x:v>
+        <x:v>마평동 여성복지회관</x:v>
       </x:c>
       <x:c r="C73" s="93" t="str">
-        <x:v>(주)우성건설기계</x:v>
+        <x:v>(주)무기타워렌탈</x:v>
       </x:c>
       <x:c r="D73" s="93"/>
       <x:c r="E73" s="558" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F73" s="558" t="n">
         <x:v>1</x:v>
@@ -6376,7 +6379,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K73" s="558" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L73" s="94"/>
     </x:row>
@@ -6385,20 +6388,20 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B74" s="112" t="str">
-        <x:v>용인덕성 AI데이터센터 신축공사</x:v>
+        <x:v>용인 라온프라이빗</x:v>
       </x:c>
       <x:c r="C74" s="112" t="str">
-        <x:v>(주)타워랜드</x:v>
+        <x:v>(주)우성건설기계</x:v>
       </x:c>
       <x:c r="D74" s="112"/>
       <x:c r="E74" s="559" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F74" s="559" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G74" s="559" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="559" t="n">
         <x:v>0</x:v>
@@ -6410,7 +6413,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K74" s="559" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L74" s="113"/>
     </x:row>
@@ -6419,34 +6422,32 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B75" s="122" t="str">
-        <x:v>용인클러스터 상생협력시설(기숙사 1차)</x:v>
+        <x:v>용인덕성 AI데이터센터 신축공사</x:v>
       </x:c>
       <x:c r="C75" s="122" t="str">
-        <x:v>(주)규람타워렌탈</x:v>
-      </x:c>
-      <x:c r="D75" s="122" t="str">
-        <x:v>원철규(미정3)</x:v>
-      </x:c>
+        <x:v>(주)타워랜드</x:v>
+      </x:c>
+      <x:c r="D75" s="122"/>
       <x:c r="E75" s="560" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F75" s="560" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G75" s="560" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H75" s="560" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="560" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J75" s="560" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K75" s="560" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L75" s="123"/>
     </x:row>
@@ -6455,17 +6456,19 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B76" s="158" t="str">
-        <x:v>수지자이에디시온</x:v>
+        <x:v>용인클러스터 상생협력시설(기숙사 1차)</x:v>
       </x:c>
       <x:c r="C76" s="158" t="str">
-        <x:v>(주)한진</x:v>
-      </x:c>
-      <x:c r="D76" s="158"/>
+        <x:v>(주)규람타워렌탈</x:v>
+      </x:c>
+      <x:c r="D76" s="158" t="str">
+        <x:v>원철규(미정3)</x:v>
+      </x:c>
       <x:c r="E76" s="561" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F76" s="561" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G76" s="561" t="n">
         <x:v>0</x:v>
@@ -6477,10 +6480,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J76" s="561" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K76" s="561" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L76" s="124"/>
     </x:row>
@@ -6489,17 +6492,17 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B77" s="160" t="str">
-        <x:v>기흥변전소</x:v>
+        <x:v>수지자이에디시온</x:v>
       </x:c>
       <x:c r="C77" s="160" t="str">
-        <x:v>(주)대원타워렌탈</x:v>
+        <x:v>(주)한진</x:v>
       </x:c>
       <x:c r="D77" s="160"/>
       <x:c r="E77" s="555" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F77" s="555" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G77" s="555" t="n">
         <x:v>0</x:v>
@@ -6514,7 +6517,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K77" s="561" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L77" s="90"/>
     </x:row>
@@ -6523,10 +6526,10 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B78" s="69" t="str">
-        <x:v>한양립스</x:v>
+        <x:v>기흥변전소</x:v>
       </x:c>
       <x:c r="C78" s="69" t="str">
-        <x:v>(주)제이에스글로벌산업</x:v>
+        <x:v>(주)대원타워렌탈</x:v>
       </x:c>
       <x:c r="D78" s="69"/>
       <x:c r="E78" s="534" t="n">
@@ -6539,7 +6542,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="534" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I78" s="534" t="n">
         <x:v>1</x:v>
@@ -6548,8 +6551,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K78" s="534" t="n">
-        <x:f>SUM(E78:J78)</x:f>
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L78" s="69"/>
     </x:row>
@@ -6558,35 +6560,32 @@
         <x:v>용인</x:v>
       </x:c>
       <x:c r="B79" s="91" t="str">
-        <x:v>신광교 클라우드 시티 신축공사</x:v>
+        <x:v>한양립스</x:v>
       </x:c>
       <x:c r="C79" s="91" t="str">
-        <x:v>(주)성광엔지니어링</x:v>
-      </x:c>
-      <x:c r="D79" s="91" t="str">
-        <x:v>원청사: 현대엔지니어링(주)</x:v>
-      </x:c>
+        <x:v>(주)제이에스글로벌산업</x:v>
+      </x:c>
+      <x:c r="D79" s="91"/>
       <x:c r="E79" s="544" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F79" s="544" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G79" s="544" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="544" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I79" s="544" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J79" s="544" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K79" s="544" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="K79" s="544" t="n">
-        <x:f>SUM(E79:J79)</x:f>
-        <x:v>5</x:v>
       </x:c>
       <x:c r="L79" s="91" t="str">
         <x:v>2026-10-17 입사 / 현장명 정정 / 총 1→5대 (2026-10-19 명단)</x:v>
@@ -6594,109 +6593,111 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="93" t="str">
-        <x:v>용인지부 소계</x:v>
-      </x:c>
-      <x:c r="B80" s="93"/>
-      <x:c r="C80" s="93"/>
-      <x:c r="D80" s="93"/>
+        <x:v>용인</x:v>
+      </x:c>
+      <x:c r="B80" s="93" t="str">
+        <x:v>신광교 클라우드 시티 신축공사</x:v>
+      </x:c>
+      <x:c r="C80" s="93" t="str">
+        <x:v>(주)성광엔지니어링</x:v>
+      </x:c>
+      <x:c r="D80" s="93" t="str">
+        <x:v>원청사: 현대엔지니어링(주)</x:v>
+      </x:c>
       <x:c r="E80" s="558" t="n">
-        <x:f>SUM(E67:E69,E71:E79)</x:f>
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F80" s="558" t="n">
-        <x:f>SUM(F67:F69,F71:F79)</x:f>
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G80" s="558" t="n">
-        <x:f>SUM(G67:G69,G71:G79)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H80" s="558" t="n">
-        <x:f>SUM(H67:H69,H71:H79)</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I80" s="558" t="n">
-        <x:f>SUM(I67:I69,I71:I79)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J80" s="558" t="n">
-        <x:f>SUM(J67:J69,J71:J79)</x:f>
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K80" s="558" t="n">
-        <x:f>SUM(K67:K69,K71:K79)</x:f>
-        <x:v>39</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L80" s="93"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="114" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>용인지부 소계</x:v>
       </x:c>
       <x:c r="B81" s="114"/>
       <x:c r="C81" s="114"/>
       <x:c r="D81" s="114"/>
-      <x:c r="E81" s="566" t="n">
-        <x:f>IF($K$80=0,0,E80/$K$80)</x:f>
-        <x:v>0.2564102564102564</x:v>
-      </x:c>
-      <x:c r="F81" s="566" t="n">
-        <x:f>IF($K$80=0,0,F80/$K$80)</x:f>
-        <x:v>0.3076923076923077</x:v>
-      </x:c>
-      <x:c r="G81" s="566" t="n">
-        <x:f>IF($K$80=0,0,G80/$K$80)</x:f>
-        <x:v>0.02564102564102564</x:v>
-      </x:c>
-      <x:c r="H81" s="566" t="n">
-        <x:f>IF($K$80=0,0,H80/$K$80)</x:f>
-        <x:v>0.10256410256410256</x:v>
-      </x:c>
-      <x:c r="I81" s="566" t="n">
-        <x:f>IF($K$80=0,0,I80/$K$80)</x:f>
-        <x:v>0.15384615384615385</x:v>
-      </x:c>
-      <x:c r="J81" s="566" t="n">
-        <x:f>IF($K$80=0,0,J80/$K$80)</x:f>
-        <x:v>0.15384615384615385</x:v>
-      </x:c>
-      <x:c r="K81" s="566" t="n">
-        <x:f>IF($K$80=0,0,K80/$K$80)</x:f>
-        <x:v>1</x:v>
+      <x:c r="E81" s="568" t="n">
+        <x:f>SUM(E68:E80)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F81" s="568" t="n">
+        <x:f>SUM(F68:F80)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G81" s="568" t="n">
+        <x:f>SUM(G68:G80)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H81" s="568" t="n">
+        <x:f>SUM(H68:H80)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I81" s="568" t="n">
+        <x:f>SUM(I68:I80)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J81" s="568" t="n">
+        <x:f>SUM(J68:J80)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K81" s="568" t="n">
+        <x:f>SUM(K68:K80)</x:f>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="L81" s="114"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="125" t="str">
-        <x:v>중부</x:v>
-      </x:c>
-      <x:c r="B82" s="125" t="str">
-        <x:v>당수동 한신</x:v>
-      </x:c>
-      <x:c r="C82" s="125" t="str">
-        <x:v>주식회사월드타워</x:v>
-      </x:c>
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B82" s="125"/>
+      <x:c r="C82" s="125"/>
       <x:c r="D82" s="125"/>
-      <x:c r="E82" s="562" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F82" s="562" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G82" s="562" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H82" s="562" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I82" s="562" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J82" s="562" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K82" s="562" t="n">
-        <x:v>5</x:v>
+      <x:c r="E82" s="569" t="n">
+        <x:f>IF($K$81=0,0,E81/$K$81)</x:f>
+        <x:v>0.2564102564102564</x:v>
+      </x:c>
+      <x:c r="F82" s="569" t="n">
+        <x:f>IF($K$81=0,0,F81/$K$81)</x:f>
+        <x:v>0.38461538461538464</x:v>
+      </x:c>
+      <x:c r="G82" s="569" t="n">
+        <x:f>IF($K$81=0,0,G81/$K$81)</x:f>
+        <x:v>0.02564102564102564</x:v>
+      </x:c>
+      <x:c r="H82" s="569" t="n">
+        <x:f>IF($K$81=0,0,H81/$K$81)</x:f>
+        <x:v>0.1282051282051282</x:v>
+      </x:c>
+      <x:c r="I82" s="569" t="n">
+        <x:f>IF($K$81=0,0,I81/$K$81)</x:f>
+        <x:v>0.1794871794871795</x:v>
+      </x:c>
+      <x:c r="J82" s="569" t="n">
+        <x:f>IF($K$81=0,0,J81/$K$81)</x:f>
+        <x:v>0.15384615384615385</x:v>
+      </x:c>
+      <x:c r="K82" s="569" t="n">
+        <x:f>IF($K$81=0,0,K81/$K$81)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L82" s="125"/>
     </x:row>
@@ -6705,10 +6706,10 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B83" s="161" t="str">
-        <x:v>당수동 한라</x:v>
+        <x:v>당수동 한신</x:v>
       </x:c>
       <x:c r="C83" s="161" t="str">
-        <x:v>벽산중기산업주식회사</x:v>
+        <x:v>주식회사월드타워</x:v>
       </x:c>
       <x:c r="D83" s="161"/>
       <x:c r="E83" s="563" t="n">
@@ -6718,19 +6719,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G83" s="563" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="563" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I83" s="563" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J83" s="563" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K83" s="563" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L83" s="126"/>
     </x:row>
@@ -6739,26 +6740,26 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B84" s="163" t="str">
-        <x:v>당수동 계룡</x:v>
+        <x:v>당수동 한라</x:v>
       </x:c>
       <x:c r="C84" s="163" t="str">
-        <x:v>주식회사 화성건기</x:v>
+        <x:v>벽산중기산업주식회사</x:v>
       </x:c>
       <x:c r="D84" s="163"/>
       <x:c r="E84" s="555" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F84" s="555" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G84" s="555" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H84" s="555" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I84" s="555" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J84" s="555" t="n">
         <x:v>0</x:v>
@@ -6773,10 +6774,10 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>영화동 두산</x:v>
+        <x:v>당수동 계룡</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>(주)야후건기</x:v>
+        <x:v>주식회사 화성건기</x:v>
       </x:c>
       <x:c r="D85"/>
       <x:c r="E85" s="536" t="n">
@@ -6792,13 +6793,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="536" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J85" s="536" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K85" s="536" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L85"/>
     </x:row>
@@ -6807,17 +6808,17 @@
         <x:v>중부</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>수원 친환경 에너지 개선공사 주기기 구매</x:v>
+        <x:v>영화동 두산</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>신우개발(주)</x:v>
+        <x:v>(주)야후건기</x:v>
       </x:c>
       <x:c r="D86"/>
       <x:c r="E86" s="536" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F86" s="536" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G86" s="536" t="n">
         <x:v>0</x:v>
@@ -6826,90 +6827,122 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="536" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J86" s="536" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K86" s="536" t="n">
-        <x:f>SUM(E86:J86)</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>중부지부 소계</x:v>
-      </x:c>
-      <x:c r="B87"/>
-      <x:c r="C87"/>
+        <x:v>중부</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>수원 친환경 에너지 개선공사 주기기 구매</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>신우개발(주)</x:v>
+      </x:c>
       <x:c r="D87"/>
       <x:c r="E87" s="536" t="n">
-        <x:f>SUM(E82:E86)</x:f>
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F87" s="536" t="n">
-        <x:f>SUM(F82:F86)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G87" s="536" t="n">
-        <x:f>SUM(G82:G86)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="536" t="n">
-        <x:f>SUM(H82:H86)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="536" t="n">
-        <x:f>SUM(I82:I86)</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J87" s="536" t="n">
-        <x:f>SUM(J82:J86)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K87" s="536" t="n">
-        <x:f>SUM(K82:K86)</x:f>
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>소계퍼센테이지</x:v>
+        <x:v>중부지부 소계</x:v>
       </x:c>
       <x:c r="B88"/>
       <x:c r="C88"/>
       <x:c r="D88"/>
-      <x:c r="E88" s="95" t="n">
-        <x:f>IF($K$87=0,0,E87/$K$87)</x:f>
+      <x:c r="E88" s="536" t="n">
+        <x:f>SUM(E83:E87)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F88" s="536" t="n">
+        <x:f>SUM(F83:F87)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G88" s="536" t="n">
+        <x:f>SUM(G83:G87)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H88" s="536" t="n">
+        <x:f>SUM(H83:H87)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="536" t="n">
+        <x:f>SUM(I83:I87)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J88" s="536" t="n">
+        <x:f>SUM(J83:J87)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K88" s="536" t="n">
+        <x:f>SUM(K83:K87)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>소계퍼센테이지</x:v>
+      </x:c>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89" s="95" t="n">
+        <x:f>IF($K$88=0,0,E88/$K$88)</x:f>
         <x:v>0.29411764705882354</x:v>
       </x:c>
-      <x:c r="F88" s="95" t="n">
-        <x:f>IF($K$87=0,0,F87/$K$87)</x:f>
+      <x:c r="F89" s="95" t="n">
+        <x:f>IF($K$88=0,0,F88/$K$88)</x:f>
         <x:v>0.35294117647058826</x:v>
       </x:c>
-      <x:c r="G88" s="95" t="n">
-        <x:f>IF($K$87=0,0,G87/$K$87)</x:f>
+      <x:c r="G89" s="95" t="n">
+        <x:f>IF($K$88=0,0,G88/$K$88)</x:f>
         <x:v>0.058823529411764705</x:v>
       </x:c>
-      <x:c r="H88" s="95" t="n">
-        <x:f>IF($K$87=0,0,H87/$K$87)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I88" s="95" t="n">
-        <x:f>IF($K$87=0,0,I87/$K$87)</x:f>
+      <x:c r="H89" s="95" t="n">
+        <x:f>IF($K$88=0,0,H88/$K$88)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" s="95" t="n">
+        <x:f>IF($K$88=0,0,I88/$K$88)</x:f>
         <x:v>0.29411764705882354</x:v>
       </x:c>
-      <x:c r="J88" s="95" t="n">
-        <x:f>IF($K$87=0,0,J87/$K$87)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K88" s="95" t="n">
-        <x:f>IF($K$87=0,0,K87/$K$87)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L88"/>
+      <x:c r="J89" s="95" t="n">
+        <x:f>IF($K$88=0,0,J88/$K$88)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K89" s="95" t="n">
+        <x:f>IF($K$88=0,0,K88/$K$88)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7338,32 +7371,33 @@
       <x:c r="A14" s="12" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B14" s="11">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="11">
-        <x:v>3</x:v>
+      <x:c r="B14" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F14" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="11">
+      <x:c r="F14" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I14" s="9">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J14" s="34">
-        <x:v>0.23076923076923081</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I14" s="9" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="34" t="n">
+        <x:f>IF(I14=0,0,C14/I14)</x:f>
+        <x:v>0.23529411764705882</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8421,7 +8455,7 @@
     <x:row r="6">
       <x:c r="A6" s="16" t="n">
         <x:f t="shared" ref="A6:F6" si="0">SUM(C11:C20)</x:f>
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f t="shared" si="0"/>
@@ -8805,7 +8839,7 @@
       </x:c>
       <x:c r="C21" s="31" t="n">
         <x:f t="shared" ref="C21:H21" si="1">SUM(C11:C20)</x:f>
-        <x:v>6</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D21" s="31" t="n">
         <x:f t="shared" si="1"/>
@@ -11991,69 +12025,101 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" t="str">
-        <x:v>합계</x:v>
-      </x:c>
-      <x:c r="B118"/>
-      <x:c r="C118"/>
+        <x:v>(주)규람타워렌탈</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>두산에너빌리티(주)</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>TERA PROJECT</x:v>
+      </x:c>
       <x:c r="D118" s="536" t="n">
-        <x:f>SUM(D106:D117)</x:f>
-        <x:v>51</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E118" s="536" t="n">
-        <x:f>SUM(E106:E117)</x:f>
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F118" s="536" t="n">
-        <x:f>SUM(F106:F117)</x:f>
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G118" s="536" t="n">
-        <x:f>SUM(G106:G117)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="536" t="n">
-        <x:f>SUM(H106:H117)</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="536" t="n">
-        <x:f>SUM(I106:I117)</x:f>
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J118" t="str">
-        <x:v>※ 미정 7대 (확인된 최신 10월 집계), 다른 월 기록 유지</x:v>
+        <x:v>2026-10-21 신규 / 남부지부</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="str">
-        <x:v>비율 (총대수=100%)</x:v>
+        <x:v>합계</x:v>
       </x:c>
       <x:c r="B119"/>
       <x:c r="C119"/>
-      <x:c r="D119" s="95" t="n">
-        <x:f>IF($D$118=0,0,D118/$D$118)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E119" s="95" t="n">
-        <x:f>IF($D$118=0,0,E118/$D$118)</x:f>
-        <x:v>0.27450980392156865</x:v>
-      </x:c>
-      <x:c r="F119" s="95" t="n">
-        <x:f>IF($D$118=0,0,F118/$D$118)</x:f>
-        <x:v>0.45098039215686275</x:v>
-      </x:c>
-      <x:c r="G119" s="95" t="n">
-        <x:f>IF($D$118=0,0,G118/$D$118)</x:f>
-        <x:v>0.0392156862745098</x:v>
-      </x:c>
-      <x:c r="H119" s="95" t="n">
-        <x:f>IF($D$118=0,0,H118/$D$118)</x:f>
-        <x:v>0.09803921568627451</x:v>
-      </x:c>
-      <x:c r="I119" s="95" t="n">
-        <x:f>IF($D$118=0,0,I118/$D$118)</x:f>
-        <x:v>0.13725490196078433</x:v>
-      </x:c>
-      <x:c r="J119"/>
+      <x:c r="D119" s="536" t="n">
+        <x:f>SUM(D106:D118)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E119" s="536" t="n">
+        <x:f>SUM(E106:E118)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F119" s="536" t="n">
+        <x:f>SUM(F106:F118)</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G119" s="536" t="n">
+        <x:f>SUM(G106:G118)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H119" s="536" t="n">
+        <x:f>SUM(H106:H118)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I119" s="536" t="n">
+        <x:f>SUM(I106:I118)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>※ 미정 9대 (10월 신규 현장 합계), 다른 월 기록 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>비율 (총대수=100%)</x:v>
+      </x:c>
+      <x:c r="B120"/>
+      <x:c r="C120"/>
+      <x:c r="D120" s="95" t="n">
+        <x:f>IF($D$119=0,0,D119/$D$119)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E120" s="95" t="n">
+        <x:f>IF($D$119=0,0,E119/$D$119)</x:f>
+        <x:v>0.2727272727272727</x:v>
+      </x:c>
+      <x:c r="F120" s="95" t="n">
+        <x:f>IF($D$119=0,0,F119/$D$119)</x:f>
+        <x:v>0.43636363636363634</x:v>
+      </x:c>
+      <x:c r="G120" s="95" t="n">
+        <x:f>IF($D$119=0,0,G119/$D$119)</x:f>
+        <x:v>0.03636363636363636</x:v>
+      </x:c>
+      <x:c r="H120" s="95" t="n">
+        <x:f>IF($D$119=0,0,H119/$D$119)</x:f>
+        <x:v>0.09090909090909091</x:v>
+      </x:c>
+      <x:c r="I120" s="95" t="n">
+        <x:f>IF($D$119=0,0,I119/$D$119)</x:f>
+        <x:v>0.16363636363636364</x:v>
+      </x:c>
+      <x:c r="J120"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13170,6 +13236,6 @@
     <x:mergeCell ref="A50:T50"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24b884fc15174b5f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92719184f9344aee"/>
 </x:worksheet>
 </file>